--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -19102,10 +19102,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>103552077</v>
+        <v>108350248</v>
       </c>
       <c r="B164" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19137,16 +19137,21 @@
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>368471</v>
+        <v>368438</v>
       </c>
       <c r="R164" t="n">
-        <v>6937590</v>
+        <v>6937579</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -19173,12 +19178,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19205,10 +19210,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>108350248</v>
+        <v>103552077</v>
       </c>
       <c r="B165" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19240,21 +19245,16 @@
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>368438</v>
+        <v>368471</v>
       </c>
       <c r="R165" t="n">
-        <v>6937579</v>
+        <v>6937590</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD165" t="b">

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -19313,10 +19313,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119765744</v>
+        <v>119763342</v>
       </c>
       <c r="B166" t="n">
-        <v>91254</v>
+        <v>57310</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19325,41 +19325,56 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>368547</v>
+        <v>368574</v>
       </c>
       <c r="R166" t="n">
-        <v>6937589</v>
+        <v>6937554</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19383,12 +19398,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19415,10 +19430,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119763342</v>
+        <v>119763370</v>
       </c>
       <c r="B167" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19427,20 +19442,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -19448,20 +19463,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -19532,10 +19536,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119763370</v>
+        <v>119763325</v>
       </c>
       <c r="B168" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19544,20 +19548,20 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -19565,21 +19569,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="I168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>368574</v>
+        <v>368590</v>
       </c>
       <c r="R168" t="n">
-        <v>6937554</v>
+        <v>6937543</v>
       </c>
       <c r="S168" t="n">
         <v>15</v>
@@ -19606,12 +19611,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19638,10 +19643,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119763325</v>
+        <v>119765744</v>
       </c>
       <c r="B169" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19650,46 +19655,41 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>368590</v>
+        <v>368547</v>
       </c>
       <c r="R169" t="n">
-        <v>6937543</v>
+        <v>6937589</v>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -19313,7 +19313,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119763342</v>
+        <v>119763325</v>
       </c>
       <c r="B166" t="n">
         <v>57310</v>
@@ -19347,31 +19347,21 @@
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>368574</v>
+        <v>368590</v>
       </c>
       <c r="R166" t="n">
-        <v>6937554</v>
+        <v>6937543</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -19398,12 +19388,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19430,10 +19420,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119763370</v>
+        <v>119763350</v>
       </c>
       <c r="B167" t="n">
-        <v>57421</v>
+        <v>57310</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19442,20 +19432,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -19463,9 +19453,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="I167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -19536,10 +19537,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119763325</v>
+        <v>119765744</v>
       </c>
       <c r="B168" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19548,46 +19549,41 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>368590</v>
+        <v>368547</v>
       </c>
       <c r="R168" t="n">
-        <v>6937543</v>
+        <v>6937589</v>
       </c>
       <c r="S168" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -19643,10 +19639,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119765744</v>
+        <v>119763370</v>
       </c>
       <c r="B169" t="n">
-        <v>91254</v>
+        <v>57421</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19659,37 +19655,41 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3298</v>
+        <v>103031</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>368547</v>
+        <v>368574</v>
       </c>
       <c r="R169" t="n">
-        <v>6937589</v>
+        <v>6937554</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19713,12 +19713,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD169" t="b">

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -19313,7 +19313,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119763325</v>
+        <v>119763350</v>
       </c>
       <c r="B166" t="n">
         <v>57310</v>
@@ -19347,21 +19347,31 @@
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>368590</v>
+        <v>368574</v>
       </c>
       <c r="R166" t="n">
-        <v>6937543</v>
+        <v>6937554</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -19388,12 +19398,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19420,10 +19430,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119763350</v>
+        <v>119765744</v>
       </c>
       <c r="B167" t="n">
-        <v>57310</v>
+        <v>91254</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19432,56 +19442,41 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>368574</v>
+        <v>368547</v>
       </c>
       <c r="R167" t="n">
-        <v>6937554</v>
+        <v>6937589</v>
       </c>
       <c r="S167" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -19505,12 +19500,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19537,10 +19532,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119765744</v>
+        <v>119763325</v>
       </c>
       <c r="B168" t="n">
-        <v>91254</v>
+        <v>57310</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19549,41 +19544,46 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>368547</v>
+        <v>368590</v>
       </c>
       <c r="R168" t="n">
-        <v>6937589</v>
+        <v>6937543</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -19313,10 +19313,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119763350</v>
+        <v>119763370</v>
       </c>
       <c r="B166" t="n">
-        <v>57310</v>
+        <v>57431</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19325,20 +19325,20 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -19346,20 +19346,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -19430,10 +19419,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119765744</v>
+        <v>119763350</v>
       </c>
       <c r="B167" t="n">
-        <v>91254</v>
+        <v>57320</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19442,41 +19431,56 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>368547</v>
+        <v>368574</v>
       </c>
       <c r="R167" t="n">
-        <v>6937589</v>
+        <v>6937554</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -19500,12 +19504,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19535,7 +19539,7 @@
         <v>119763325</v>
       </c>
       <c r="B168" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19639,10 +19643,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119763370</v>
+        <v>119765744</v>
       </c>
       <c r="B169" t="n">
-        <v>57421</v>
+        <v>91272</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19655,41 +19659,37 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>103031</v>
+        <v>3298</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>368574</v>
+        <v>368547</v>
       </c>
       <c r="R169" t="n">
-        <v>6937554</v>
+        <v>6937589</v>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19713,12 +19713,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD169" t="b">

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -19419,7 +19419,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119763350</v>
+        <v>119763325</v>
       </c>
       <c r="B167" t="n">
         <v>57320</v>
@@ -19453,31 +19453,21 @@
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>368574</v>
+        <v>368590</v>
       </c>
       <c r="R167" t="n">
-        <v>6937554</v>
+        <v>6937543</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -19504,12 +19494,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19536,10 +19526,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119763325</v>
+        <v>119765744</v>
       </c>
       <c r="B168" t="n">
-        <v>57320</v>
+        <v>91272</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19548,46 +19538,41 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>368590</v>
+        <v>368547</v>
       </c>
       <c r="R168" t="n">
-        <v>6937543</v>
+        <v>6937589</v>
       </c>
       <c r="S168" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -19643,10 +19628,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119765744</v>
+        <v>119763350</v>
       </c>
       <c r="B169" t="n">
-        <v>91272</v>
+        <v>57320</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19655,41 +19640,56 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>368547</v>
+        <v>368574</v>
       </c>
       <c r="R169" t="n">
-        <v>6937589</v>
+        <v>6937554</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19713,12 +19713,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD169" t="b">

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -15243,11 +15243,11 @@
         <v>108093901</v>
       </c>
       <c r="B130" t="n">
-        <v>89832</v>
+        <v>91168</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15281,10 +15281,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>368613.5641773602</v>
+        <v>368613</v>
       </c>
       <c r="R130" t="n">
-        <v>6937980.310419838</v>
+        <v>6937980</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -15243,7 +15243,7 @@
         <v>108093901</v>
       </c>
       <c r="B130" t="n">
-        <v>91168</v>
+        <v>91182</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -15243,7 +15243,7 @@
         <v>108093901</v>
       </c>
       <c r="B130" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -15243,7 +15243,7 @@
         <v>108093901</v>
       </c>
       <c r="B130" t="n">
-        <v>91184</v>
+        <v>91185</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -15243,7 +15243,7 @@
         <v>108093901</v>
       </c>
       <c r="B130" t="n">
-        <v>91185</v>
+        <v>91194</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -5908,10 +5908,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124622913</v>
+        <v>124623242</v>
       </c>
       <c r="B48" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5924,34 +5924,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>368781</v>
+        <v>368810</v>
       </c>
       <c r="R48" t="n">
-        <v>6938181</v>
+        <v>6938210</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6219,7 +6224,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124623242</v>
+        <v>124623496</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -6264,10 +6269,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>368810</v>
+        <v>368782</v>
       </c>
       <c r="R51" t="n">
-        <v>6938210</v>
+        <v>6938260</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6326,10 +6331,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124622908</v>
+        <v>124622913</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6342,29 +6347,24 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124623496</v>
+        <v>124622908</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6469,19 +6469,19 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>368782</v>
+        <v>368781</v>
       </c>
       <c r="R53" t="n">
-        <v>6938260</v>
+        <v>6938181</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -17474,10 +17474,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>124627082</v>
+        <v>124627400</v>
       </c>
       <c r="B150" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17490,37 +17490,42 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>368762</v>
+        <v>368733</v>
       </c>
       <c r="R150" t="n">
         <v>6938143</v>
       </c>
       <c r="S150" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17683,10 +17688,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124628575</v>
+        <v>124627646</v>
       </c>
       <c r="B152" t="n">
-        <v>78889</v>
+        <v>91457</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17695,25 +17700,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>864</v>
+        <v>1209</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17723,10 +17728,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>368486</v>
+        <v>368729</v>
       </c>
       <c r="R152" t="n">
-        <v>6938016</v>
+        <v>6938156</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17887,10 +17892,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124627646</v>
+        <v>124628634</v>
       </c>
       <c r="B154" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17899,38 +17904,38 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>368729</v>
+        <v>368486</v>
       </c>
       <c r="R154" t="n">
-        <v>6938156</v>
+        <v>6937968</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17989,10 +17994,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124627400</v>
+        <v>124628575</v>
       </c>
       <c r="B155" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18005,42 +18010,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>368733</v>
+        <v>368486</v>
       </c>
       <c r="R155" t="n">
-        <v>6938143</v>
+        <v>6938016</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124628634</v>
+        <v>124627082</v>
       </c>
       <c r="B156" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18112,21 +18112,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -18136,13 +18136,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>368486</v>
+        <v>368762</v>
       </c>
       <c r="R156" t="n">
-        <v>6937968</v>
+        <v>6938143</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124630092</v>
+        <v>124630509</v>
       </c>
       <c r="B182" t="n">
         <v>74901</v>
@@ -21028,10 +21028,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368556</v>
+        <v>368603</v>
       </c>
       <c r="R182" t="n">
-        <v>6937530</v>
+        <v>6937521</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21090,10 +21090,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124620724</v>
+        <v>124618703</v>
       </c>
       <c r="B183" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21106,37 +21106,37 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Fjällkällan, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368610</v>
+        <v>368568</v>
       </c>
       <c r="R183" t="n">
-        <v>6937558</v>
+        <v>6937489</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21192,10 +21192,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124618703</v>
+        <v>124630092</v>
       </c>
       <c r="B184" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21208,21 +21208,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -21232,13 +21232,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368568</v>
+        <v>368556</v>
       </c>
       <c r="R184" t="n">
-        <v>6937489</v>
+        <v>6937530</v>
       </c>
       <c r="S184" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124618931</v>
+        <v>124619608</v>
       </c>
       <c r="B185" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21306,41 +21306,41 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368571</v>
+        <v>368492</v>
       </c>
       <c r="R185" t="n">
-        <v>6937516</v>
+        <v>6937572</v>
       </c>
       <c r="S185" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124619608</v>
+        <v>124620724</v>
       </c>
       <c r="B188" t="n">
         <v>91030</v>
@@ -21636,17 +21636,17 @@
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368492</v>
+        <v>368610</v>
       </c>
       <c r="R188" t="n">
-        <v>6937572</v>
+        <v>6937558</v>
       </c>
       <c r="S188" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21702,10 +21702,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124630509</v>
+        <v>124618931</v>
       </c>
       <c r="B189" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21714,25 +21714,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -21742,13 +21742,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368603</v>
+        <v>368571</v>
       </c>
       <c r="R189" t="n">
-        <v>6937521</v>
+        <v>6937516</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -6015,10 +6015,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124626137</v>
+        <v>124622913</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6031,39 +6031,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>368833</v>
+        <v>368781</v>
       </c>
       <c r="R49" t="n">
-        <v>6938244</v>
+        <v>6938181</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6122,10 +6117,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124623267</v>
+        <v>124626137</v>
       </c>
       <c r="B50" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6134,38 +6129,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>368810</v>
+        <v>368833</v>
       </c>
       <c r="R50" t="n">
-        <v>6938210</v>
+        <v>6938244</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6224,10 +6224,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124623496</v>
+        <v>124623267</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6236,43 +6236,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>368782</v>
+        <v>368810</v>
       </c>
       <c r="R51" t="n">
-        <v>6938260</v>
+        <v>6938210</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6331,10 +6326,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124622913</v>
+        <v>124622908</v>
       </c>
       <c r="B52" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6347,24 +6342,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124622908</v>
+        <v>124623496</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6469,19 +6469,19 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>368781</v>
+        <v>368782</v>
       </c>
       <c r="R53" t="n">
-        <v>6938181</v>
+        <v>6938260</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -17474,10 +17474,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>124627400</v>
+        <v>124628575</v>
       </c>
       <c r="B150" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17490,42 +17490,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>368733</v>
+        <v>368486</v>
       </c>
       <c r="R150" t="n">
-        <v>6938143</v>
+        <v>6938016</v>
       </c>
       <c r="S150" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17581,10 +17576,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>124622769</v>
+        <v>124627646</v>
       </c>
       <c r="B151" t="n">
-        <v>57513</v>
+        <v>91457</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17593,46 +17588,41 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>368769</v>
+        <v>368729</v>
       </c>
       <c r="R151" t="n">
-        <v>6938164</v>
+        <v>6938156</v>
       </c>
       <c r="S151" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17688,10 +17678,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124627646</v>
+        <v>124628634</v>
       </c>
       <c r="B152" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17700,38 +17690,38 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>368729</v>
+        <v>368486</v>
       </c>
       <c r="R152" t="n">
-        <v>6938156</v>
+        <v>6937968</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17790,10 +17780,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124628358</v>
+        <v>124627400</v>
       </c>
       <c r="B153" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17806,37 +17796,42 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>368522</v>
+        <v>368733</v>
       </c>
       <c r="R153" t="n">
-        <v>6938078</v>
+        <v>6938143</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17892,10 +17887,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124628634</v>
+        <v>124627082</v>
       </c>
       <c r="B154" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17908,21 +17903,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17932,13 +17927,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>368486</v>
+        <v>368762</v>
       </c>
       <c r="R154" t="n">
-        <v>6937968</v>
+        <v>6938143</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17994,10 +17989,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124628575</v>
+        <v>124622769</v>
       </c>
       <c r="B155" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18010,37 +18005,42 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>368486</v>
+        <v>368769</v>
       </c>
       <c r="R155" t="n">
-        <v>6938016</v>
+        <v>6938164</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124627082</v>
+        <v>124628358</v>
       </c>
       <c r="B156" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18112,37 +18112,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>368762</v>
+        <v>368522</v>
       </c>
       <c r="R156" t="n">
-        <v>6938143</v>
+        <v>6938078</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -20988,10 +20988,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124630509</v>
+        <v>124619608</v>
       </c>
       <c r="B182" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21004,37 +21004,37 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368603</v>
+        <v>368492</v>
       </c>
       <c r="R182" t="n">
-        <v>6937521</v>
+        <v>6937572</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21090,10 +21090,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124618703</v>
+        <v>124630092</v>
       </c>
       <c r="B183" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21106,21 +21106,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -21130,13 +21130,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368568</v>
+        <v>368556</v>
       </c>
       <c r="R183" t="n">
-        <v>6937489</v>
+        <v>6937530</v>
       </c>
       <c r="S183" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124630092</v>
+        <v>124630273</v>
       </c>
       <c r="B184" t="n">
         <v>74901</v>
@@ -21232,10 +21232,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368556</v>
+        <v>368585</v>
       </c>
       <c r="R184" t="n">
-        <v>6937530</v>
+        <v>6937532</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124619608</v>
+        <v>124629552</v>
       </c>
       <c r="B185" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21310,21 +21310,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21334,10 +21334,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368492</v>
+        <v>368487</v>
       </c>
       <c r="R185" t="n">
-        <v>6937572</v>
+        <v>6937548</v>
       </c>
       <c r="S185" t="n">
         <v>25</v>
@@ -21396,7 +21396,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124630273</v>
+        <v>124630509</v>
       </c>
       <c r="B186" t="n">
         <v>74901</v>
@@ -21436,10 +21436,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>368585</v>
+        <v>368603</v>
       </c>
       <c r="R186" t="n">
-        <v>6937532</v>
+        <v>6937521</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21498,10 +21498,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124629552</v>
+        <v>124620724</v>
       </c>
       <c r="B187" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21514,37 +21514,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>368487</v>
+        <v>368610</v>
       </c>
       <c r="R187" t="n">
-        <v>6937548</v>
+        <v>6937558</v>
       </c>
       <c r="S187" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21600,10 +21600,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124620724</v>
+        <v>124618931</v>
       </c>
       <c r="B188" t="n">
-        <v>91030</v>
+        <v>79920</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21612,41 +21612,41 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Fjällkällan, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368610</v>
+        <v>368571</v>
       </c>
       <c r="R188" t="n">
-        <v>6937558</v>
+        <v>6937516</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21702,10 +21702,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124618931</v>
+        <v>124618703</v>
       </c>
       <c r="B189" t="n">
-        <v>79920</v>
+        <v>82597</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21714,25 +21714,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -21742,13 +21742,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368571</v>
+        <v>368568</v>
       </c>
       <c r="R189" t="n">
-        <v>6937516</v>
+        <v>6937489</v>
       </c>
       <c r="S189" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -5908,10 +5908,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124623242</v>
+        <v>124623267</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5920,33 +5920,28 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
@@ -6117,7 +6112,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124626137</v>
+        <v>124623242</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6162,10 +6157,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>368833</v>
+        <v>368810</v>
       </c>
       <c r="R50" t="n">
-        <v>6938244</v>
+        <v>6938210</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6224,10 +6219,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124623267</v>
+        <v>124623496</v>
       </c>
       <c r="B51" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6236,38 +6231,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>368810</v>
+        <v>368782</v>
       </c>
       <c r="R51" t="n">
-        <v>6938210</v>
+        <v>6938260</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6326,7 +6326,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124622908</v>
+        <v>124626137</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -6362,19 +6362,19 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>368781</v>
+        <v>368833</v>
       </c>
       <c r="R52" t="n">
-        <v>6938181</v>
+        <v>6938244</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124623496</v>
+        <v>124622908</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6469,19 +6469,19 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>368782</v>
+        <v>368781</v>
       </c>
       <c r="R53" t="n">
-        <v>6938260</v>
+        <v>6938181</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -17474,10 +17474,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>124628575</v>
+        <v>124627646</v>
       </c>
       <c r="B150" t="n">
-        <v>78889</v>
+        <v>91457</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17486,25 +17486,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>864</v>
+        <v>1209</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17514,10 +17514,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>368486</v>
+        <v>368729</v>
       </c>
       <c r="R150" t="n">
-        <v>6938016</v>
+        <v>6938156</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17576,10 +17576,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>124627646</v>
+        <v>124628634</v>
       </c>
       <c r="B151" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17588,38 +17588,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>368729</v>
+        <v>368486</v>
       </c>
       <c r="R151" t="n">
-        <v>6938156</v>
+        <v>6937968</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17678,10 +17678,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124628634</v>
+        <v>124627400</v>
       </c>
       <c r="B152" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17694,37 +17694,42 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>368486</v>
+        <v>368733</v>
       </c>
       <c r="R152" t="n">
-        <v>6937968</v>
+        <v>6938143</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17780,10 +17785,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124627400</v>
+        <v>124627082</v>
       </c>
       <c r="B153" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17796,42 +17801,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>368733</v>
+        <v>368762</v>
       </c>
       <c r="R153" t="n">
         <v>6938143</v>
       </c>
       <c r="S153" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17887,10 +17887,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124627082</v>
+        <v>124628575</v>
       </c>
       <c r="B154" t="n">
-        <v>91299</v>
+        <v>78889</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17903,37 +17903,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>368762</v>
+        <v>368486</v>
       </c>
       <c r="R154" t="n">
-        <v>6938143</v>
+        <v>6938016</v>
       </c>
       <c r="S154" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17989,10 +17989,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124622769</v>
+        <v>124628358</v>
       </c>
       <c r="B155" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18005,42 +18005,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>368769</v>
+        <v>368522</v>
       </c>
       <c r="R155" t="n">
-        <v>6938164</v>
+        <v>6938078</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18096,10 +18091,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124628358</v>
+        <v>124622769</v>
       </c>
       <c r="B156" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18112,37 +18107,42 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>368522</v>
+        <v>368769</v>
       </c>
       <c r="R156" t="n">
-        <v>6938078</v>
+        <v>6938164</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -20988,10 +20988,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124619608</v>
+        <v>124630092</v>
       </c>
       <c r="B182" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21004,37 +21004,37 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368492</v>
+        <v>368556</v>
       </c>
       <c r="R182" t="n">
-        <v>6937572</v>
+        <v>6937530</v>
       </c>
       <c r="S182" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21090,10 +21090,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124630092</v>
+        <v>124618703</v>
       </c>
       <c r="B183" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21106,21 +21106,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -21130,13 +21130,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368556</v>
+        <v>368568</v>
       </c>
       <c r="R183" t="n">
-        <v>6937530</v>
+        <v>6937489</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21192,10 +21192,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124630273</v>
+        <v>124629552</v>
       </c>
       <c r="B184" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21208,37 +21208,37 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368585</v>
+        <v>368487</v>
       </c>
       <c r="R184" t="n">
-        <v>6937532</v>
+        <v>6937548</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124629552</v>
+        <v>124620724</v>
       </c>
       <c r="B185" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21310,37 +21310,37 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368487</v>
+        <v>368610</v>
       </c>
       <c r="R185" t="n">
-        <v>6937548</v>
+        <v>6937558</v>
       </c>
       <c r="S185" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21498,10 +21498,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124620724</v>
+        <v>124630273</v>
       </c>
       <c r="B187" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21514,34 +21514,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Fjällkällan, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>368610</v>
+        <v>368585</v>
       </c>
       <c r="R187" t="n">
-        <v>6937558</v>
+        <v>6937532</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21702,10 +21702,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124618703</v>
+        <v>124619608</v>
       </c>
       <c r="B189" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21718,34 +21718,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368568</v>
+        <v>368492</v>
       </c>
       <c r="R189" t="n">
-        <v>6937489</v>
+        <v>6937572</v>
       </c>
       <c r="S189" t="n">
         <v>25</v>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -5908,10 +5908,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124623267</v>
+        <v>124623242</v>
       </c>
       <c r="B48" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5920,28 +5920,33 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
@@ -6010,10 +6015,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124622913</v>
+        <v>124623496</v>
       </c>
       <c r="B49" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6026,34 +6031,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>368781</v>
+        <v>368782</v>
       </c>
       <c r="R49" t="n">
-        <v>6938181</v>
+        <v>6938260</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6112,10 +6122,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124623242</v>
+        <v>124623267</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6124,33 +6134,28 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
@@ -6219,10 +6224,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124623496</v>
+        <v>124622913</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6235,39 +6240,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>368782</v>
+        <v>368781</v>
       </c>
       <c r="R51" t="n">
-        <v>6938260</v>
+        <v>6938181</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -17474,10 +17474,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>124627646</v>
+        <v>124627082</v>
       </c>
       <c r="B150" t="n">
-        <v>91457</v>
+        <v>91299</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17486,41 +17486,41 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>368729</v>
+        <v>368762</v>
       </c>
       <c r="R150" t="n">
-        <v>6938156</v>
+        <v>6938143</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17576,10 +17576,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>124628634</v>
+        <v>124627646</v>
       </c>
       <c r="B151" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17588,38 +17588,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>368486</v>
+        <v>368729</v>
       </c>
       <c r="R151" t="n">
-        <v>6937968</v>
+        <v>6938156</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17785,10 +17785,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124627082</v>
+        <v>124628358</v>
       </c>
       <c r="B153" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17801,37 +17801,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>368762</v>
+        <v>368522</v>
       </c>
       <c r="R153" t="n">
-        <v>6938143</v>
+        <v>6938078</v>
       </c>
       <c r="S153" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17887,10 +17887,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124628575</v>
+        <v>124628634</v>
       </c>
       <c r="B154" t="n">
-        <v>78889</v>
+        <v>91030</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17903,34 +17903,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
         <v>368486</v>
       </c>
       <c r="R154" t="n">
-        <v>6938016</v>
+        <v>6937968</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17989,10 +17989,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124628358</v>
+        <v>124622769</v>
       </c>
       <c r="B155" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18005,37 +18005,42 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>368522</v>
+        <v>368769</v>
       </c>
       <c r="R155" t="n">
-        <v>6938078</v>
+        <v>6938164</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18091,10 +18096,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124622769</v>
+        <v>124628575</v>
       </c>
       <c r="B156" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18107,42 +18112,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>368769</v>
+        <v>368486</v>
       </c>
       <c r="R156" t="n">
-        <v>6938164</v>
+        <v>6938016</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -20988,10 +20988,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124630092</v>
+        <v>124618931</v>
       </c>
       <c r="B182" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21000,25 +21000,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -21028,13 +21028,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368556</v>
+        <v>368571</v>
       </c>
       <c r="R182" t="n">
-        <v>6937530</v>
+        <v>6937516</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21090,10 +21090,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124618703</v>
+        <v>124619608</v>
       </c>
       <c r="B183" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21106,34 +21106,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368568</v>
+        <v>368492</v>
       </c>
       <c r="R183" t="n">
-        <v>6937489</v>
+        <v>6937572</v>
       </c>
       <c r="S183" t="n">
         <v>25</v>
@@ -21192,10 +21192,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124629552</v>
+        <v>124630273</v>
       </c>
       <c r="B184" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21208,37 +21208,37 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368487</v>
+        <v>368585</v>
       </c>
       <c r="R184" t="n">
-        <v>6937548</v>
+        <v>6937532</v>
       </c>
       <c r="S184" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124620724</v>
+        <v>124629552</v>
       </c>
       <c r="B185" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21310,37 +21310,37 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Fjällkällan, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368610</v>
+        <v>368487</v>
       </c>
       <c r="R185" t="n">
-        <v>6937558</v>
+        <v>6937548</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124630273</v>
+        <v>124630092</v>
       </c>
       <c r="B187" t="n">
         <v>74901</v>
@@ -21538,10 +21538,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>368585</v>
+        <v>368556</v>
       </c>
       <c r="R187" t="n">
-        <v>6937532</v>
+        <v>6937530</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21600,10 +21600,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124618931</v>
+        <v>124620724</v>
       </c>
       <c r="B188" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21612,41 +21612,41 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Fjällkällan, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368571</v>
+        <v>368610</v>
       </c>
       <c r="R188" t="n">
-        <v>6937516</v>
+        <v>6937558</v>
       </c>
       <c r="S188" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21702,10 +21702,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124619608</v>
+        <v>124618703</v>
       </c>
       <c r="B189" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21718,34 +21718,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368492</v>
+        <v>368568</v>
       </c>
       <c r="R189" t="n">
-        <v>6937572</v>
+        <v>6937489</v>
       </c>
       <c r="S189" t="n">
         <v>25</v>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -6015,10 +6015,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124623496</v>
+        <v>124622913</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6031,39 +6031,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>368782</v>
+        <v>368781</v>
       </c>
       <c r="R49" t="n">
-        <v>6938260</v>
+        <v>6938181</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6224,10 +6219,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124622913</v>
+        <v>124623496</v>
       </c>
       <c r="B51" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6240,34 +6235,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>368781</v>
+        <v>368782</v>
       </c>
       <c r="R51" t="n">
-        <v>6938181</v>
+        <v>6938260</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6326,7 +6326,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124626137</v>
+        <v>124622908</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -6362,19 +6362,19 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>368833</v>
+        <v>368781</v>
       </c>
       <c r="R52" t="n">
-        <v>6938244</v>
+        <v>6938181</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124622908</v>
+        <v>124626137</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6469,19 +6469,19 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>368781</v>
+        <v>368833</v>
       </c>
       <c r="R53" t="n">
-        <v>6938181</v>
+        <v>6938244</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -17474,10 +17474,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>124627082</v>
+        <v>124628634</v>
       </c>
       <c r="B150" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17490,21 +17490,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17514,13 +17514,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>368762</v>
+        <v>368486</v>
       </c>
       <c r="R150" t="n">
-        <v>6938143</v>
+        <v>6937968</v>
       </c>
       <c r="S150" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17576,10 +17576,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>124627646</v>
+        <v>124628358</v>
       </c>
       <c r="B151" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17588,25 +17588,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17616,10 +17616,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>368729</v>
+        <v>368522</v>
       </c>
       <c r="R151" t="n">
-        <v>6938156</v>
+        <v>6938078</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17678,10 +17678,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124627400</v>
+        <v>124628575</v>
       </c>
       <c r="B152" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17694,42 +17694,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>368733</v>
+        <v>368486</v>
       </c>
       <c r="R152" t="n">
-        <v>6938143</v>
+        <v>6938016</v>
       </c>
       <c r="S152" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17785,10 +17780,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124628358</v>
+        <v>124622769</v>
       </c>
       <c r="B153" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17801,37 +17796,42 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>368522</v>
+        <v>368769</v>
       </c>
       <c r="R153" t="n">
-        <v>6938078</v>
+        <v>6938164</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17887,10 +17887,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124628634</v>
+        <v>124627646</v>
       </c>
       <c r="B154" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17899,38 +17899,38 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>368486</v>
+        <v>368729</v>
       </c>
       <c r="R154" t="n">
-        <v>6937968</v>
+        <v>6938156</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17989,10 +17989,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124622769</v>
+        <v>124627082</v>
       </c>
       <c r="B155" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18005,42 +18005,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>368769</v>
+        <v>368762</v>
       </c>
       <c r="R155" t="n">
-        <v>6938164</v>
+        <v>6938143</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18096,10 +18091,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124628575</v>
+        <v>124627400</v>
       </c>
       <c r="B156" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18112,37 +18107,42 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>368486</v>
+        <v>368733</v>
       </c>
       <c r="R156" t="n">
-        <v>6938016</v>
+        <v>6938143</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -20988,10 +20988,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124618931</v>
+        <v>124620724</v>
       </c>
       <c r="B182" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21000,41 +21000,41 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Fjällkällan, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368571</v>
+        <v>368610</v>
       </c>
       <c r="R182" t="n">
-        <v>6937516</v>
+        <v>6937558</v>
       </c>
       <c r="S182" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21090,10 +21090,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124619608</v>
+        <v>124630273</v>
       </c>
       <c r="B183" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21106,37 +21106,37 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368492</v>
+        <v>368585</v>
       </c>
       <c r="R183" t="n">
-        <v>6937572</v>
+        <v>6937532</v>
       </c>
       <c r="S183" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21192,10 +21192,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124630273</v>
+        <v>124618931</v>
       </c>
       <c r="B184" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21204,25 +21204,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -21232,13 +21232,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368585</v>
+        <v>368571</v>
       </c>
       <c r="R184" t="n">
-        <v>6937532</v>
+        <v>6937516</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124629552</v>
+        <v>124630509</v>
       </c>
       <c r="B185" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21310,37 +21310,37 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368487</v>
+        <v>368603</v>
       </c>
       <c r="R185" t="n">
-        <v>6937548</v>
+        <v>6937521</v>
       </c>
       <c r="S185" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21396,10 +21396,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124630509</v>
+        <v>124629552</v>
       </c>
       <c r="B186" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21412,37 +21412,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>368603</v>
+        <v>368487</v>
       </c>
       <c r="R186" t="n">
-        <v>6937521</v>
+        <v>6937548</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124620724</v>
+        <v>124619608</v>
       </c>
       <c r="B188" t="n">
         <v>91030</v>
@@ -21636,17 +21636,17 @@
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Fjällkällan, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368610</v>
+        <v>368492</v>
       </c>
       <c r="R188" t="n">
-        <v>6937558</v>
+        <v>6937572</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -5908,7 +5908,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124623242</v>
+        <v>124626137</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>368810</v>
+        <v>368833</v>
       </c>
       <c r="R48" t="n">
-        <v>6938210</v>
+        <v>6938244</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6015,10 +6015,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124622913</v>
+        <v>124623267</v>
       </c>
       <c r="B49" t="n">
-        <v>91030</v>
+        <v>78151</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6027,38 +6027,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>368781</v>
+        <v>368810</v>
       </c>
       <c r="R49" t="n">
-        <v>6938181</v>
+        <v>6938210</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6117,10 +6117,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124623267</v>
+        <v>124623242</v>
       </c>
       <c r="B50" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6129,28 +6129,33 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
@@ -6433,10 +6438,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124626137</v>
+        <v>124622913</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6449,39 +6454,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>368833</v>
+        <v>368781</v>
       </c>
       <c r="R53" t="n">
-        <v>6938244</v>
+        <v>6938181</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -17474,10 +17474,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>124628634</v>
+        <v>124627646</v>
       </c>
       <c r="B150" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17486,38 +17486,38 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>368486</v>
+        <v>368729</v>
       </c>
       <c r="R150" t="n">
-        <v>6937968</v>
+        <v>6938156</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17576,10 +17576,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>124628358</v>
+        <v>124627082</v>
       </c>
       <c r="B151" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17592,37 +17592,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>368522</v>
+        <v>368762</v>
       </c>
       <c r="R151" t="n">
-        <v>6938078</v>
+        <v>6938143</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17678,10 +17678,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124628575</v>
+        <v>124628634</v>
       </c>
       <c r="B152" t="n">
-        <v>78889</v>
+        <v>91030</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17694,34 +17694,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
         <v>368486</v>
       </c>
       <c r="R152" t="n">
-        <v>6938016</v>
+        <v>6937968</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17780,7 +17780,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124622769</v>
+        <v>124627400</v>
       </c>
       <c r="B153" t="n">
         <v>57513</v>
@@ -17816,19 +17816,19 @@
       <c r="I153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>368769</v>
+        <v>368733</v>
       </c>
       <c r="R153" t="n">
-        <v>6938164</v>
+        <v>6938143</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -17887,10 +17887,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124627646</v>
+        <v>124628358</v>
       </c>
       <c r="B154" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17899,25 +17899,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17927,10 +17927,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>368729</v>
+        <v>368522</v>
       </c>
       <c r="R154" t="n">
-        <v>6938156</v>
+        <v>6938078</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17989,10 +17989,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124627082</v>
+        <v>124622769</v>
       </c>
       <c r="B155" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18005,37 +18005,42 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>368762</v>
+        <v>368769</v>
       </c>
       <c r="R155" t="n">
-        <v>6938143</v>
+        <v>6938164</v>
       </c>
       <c r="S155" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18091,10 +18096,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124627400</v>
+        <v>124628575</v>
       </c>
       <c r="B156" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18107,42 +18112,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>368733</v>
+        <v>368486</v>
       </c>
       <c r="R156" t="n">
-        <v>6938143</v>
+        <v>6938016</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -21090,10 +21090,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124630273</v>
+        <v>124618703</v>
       </c>
       <c r="B183" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21106,21 +21106,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -21130,13 +21130,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368585</v>
+        <v>368568</v>
       </c>
       <c r="R183" t="n">
-        <v>6937532</v>
+        <v>6937489</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21192,10 +21192,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124618931</v>
+        <v>124629552</v>
       </c>
       <c r="B184" t="n">
-        <v>79920</v>
+        <v>82597</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21204,41 +21204,41 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368571</v>
+        <v>368487</v>
       </c>
       <c r="R184" t="n">
-        <v>6937516</v>
+        <v>6937548</v>
       </c>
       <c r="S184" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124630509</v>
+        <v>124618931</v>
       </c>
       <c r="B185" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21306,25 +21306,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21334,13 +21334,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368603</v>
+        <v>368571</v>
       </c>
       <c r="R185" t="n">
-        <v>6937521</v>
+        <v>6937516</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21396,10 +21396,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124629552</v>
+        <v>124619608</v>
       </c>
       <c r="B186" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21412,21 +21412,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -21436,10 +21436,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>368487</v>
+        <v>368492</v>
       </c>
       <c r="R186" t="n">
-        <v>6937548</v>
+        <v>6937572</v>
       </c>
       <c r="S186" t="n">
         <v>25</v>
@@ -21600,10 +21600,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124619608</v>
+        <v>124630273</v>
       </c>
       <c r="B188" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21616,37 +21616,37 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368492</v>
+        <v>368585</v>
       </c>
       <c r="R188" t="n">
-        <v>6937572</v>
+        <v>6937532</v>
       </c>
       <c r="S188" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21702,10 +21702,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124618703</v>
+        <v>124630509</v>
       </c>
       <c r="B189" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21718,21 +21718,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -21742,13 +21742,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368568</v>
+        <v>368603</v>
       </c>
       <c r="R189" t="n">
-        <v>6937489</v>
+        <v>6937521</v>
       </c>
       <c r="S189" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -5908,7 +5908,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124626137</v>
+        <v>124622908</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -5944,19 +5944,19 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>368833</v>
+        <v>368781</v>
       </c>
       <c r="R48" t="n">
-        <v>6938244</v>
+        <v>6938181</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6117,7 +6117,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124623242</v>
+        <v>124623496</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>368810</v>
+        <v>368782</v>
       </c>
       <c r="R50" t="n">
-        <v>6938210</v>
+        <v>6938260</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6224,10 +6224,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124623496</v>
+        <v>124622913</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6240,39 +6240,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>368782</v>
+        <v>368781</v>
       </c>
       <c r="R51" t="n">
-        <v>6938260</v>
+        <v>6938181</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6331,7 +6326,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124622908</v>
+        <v>124626137</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -6367,19 +6362,19 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>368781</v>
+        <v>368833</v>
       </c>
       <c r="R52" t="n">
-        <v>6938181</v>
+        <v>6938244</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6438,10 +6433,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124622913</v>
+        <v>124623242</v>
       </c>
       <c r="B53" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6454,34 +6449,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>368781</v>
+        <v>368810</v>
       </c>
       <c r="R53" t="n">
-        <v>6938181</v>
+        <v>6938210</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -17474,10 +17474,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>124627646</v>
+        <v>124628575</v>
       </c>
       <c r="B150" t="n">
-        <v>91457</v>
+        <v>78889</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17486,25 +17486,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1209</v>
+        <v>864</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17514,10 +17514,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>368729</v>
+        <v>368486</v>
       </c>
       <c r="R150" t="n">
-        <v>6938156</v>
+        <v>6938016</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17576,10 +17576,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>124627082</v>
+        <v>124628634</v>
       </c>
       <c r="B151" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17592,21 +17592,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17616,13 +17616,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>368762</v>
+        <v>368486</v>
       </c>
       <c r="R151" t="n">
-        <v>6938143</v>
+        <v>6937968</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17678,10 +17678,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124628634</v>
+        <v>124627400</v>
       </c>
       <c r="B152" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17694,37 +17694,42 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>368486</v>
+        <v>368733</v>
       </c>
       <c r="R152" t="n">
-        <v>6937968</v>
+        <v>6938143</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17780,10 +17785,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124627400</v>
+        <v>124627646</v>
       </c>
       <c r="B153" t="n">
-        <v>57513</v>
+        <v>91457</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17792,46 +17797,41 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>368733</v>
+        <v>368729</v>
       </c>
       <c r="R153" t="n">
-        <v>6938143</v>
+        <v>6938156</v>
       </c>
       <c r="S153" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17989,10 +17989,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124622769</v>
+        <v>124627082</v>
       </c>
       <c r="B155" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18005,42 +18005,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>368769</v>
+        <v>368762</v>
       </c>
       <c r="R155" t="n">
-        <v>6938164</v>
+        <v>6938143</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18096,10 +18091,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124628575</v>
+        <v>124622769</v>
       </c>
       <c r="B156" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18112,37 +18107,42 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>368486</v>
+        <v>368769</v>
       </c>
       <c r="R156" t="n">
-        <v>6938016</v>
+        <v>6938164</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124618703</v>
+        <v>124629552</v>
       </c>
       <c r="B183" t="n">
         <v>82597</v>
@@ -21126,14 +21126,14 @@
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368568</v>
+        <v>368487</v>
       </c>
       <c r="R183" t="n">
-        <v>6937489</v>
+        <v>6937548</v>
       </c>
       <c r="S183" t="n">
         <v>25</v>
@@ -21192,10 +21192,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124629552</v>
+        <v>124619608</v>
       </c>
       <c r="B184" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21208,21 +21208,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -21232,10 +21232,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368487</v>
+        <v>368492</v>
       </c>
       <c r="R184" t="n">
-        <v>6937548</v>
+        <v>6937572</v>
       </c>
       <c r="S184" t="n">
         <v>25</v>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124618931</v>
+        <v>124630273</v>
       </c>
       <c r="B185" t="n">
-        <v>79920</v>
+        <v>74901</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21306,25 +21306,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21334,13 +21334,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368571</v>
+        <v>368585</v>
       </c>
       <c r="R185" t="n">
-        <v>6937516</v>
+        <v>6937532</v>
       </c>
       <c r="S185" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21396,10 +21396,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124619608</v>
+        <v>124630509</v>
       </c>
       <c r="B186" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21412,37 +21412,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>368492</v>
+        <v>368603</v>
       </c>
       <c r="R186" t="n">
-        <v>6937572</v>
+        <v>6937521</v>
       </c>
       <c r="S186" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21498,10 +21498,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124630092</v>
+        <v>124618931</v>
       </c>
       <c r="B187" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21510,25 +21510,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21538,13 +21538,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>368556</v>
+        <v>368571</v>
       </c>
       <c r="R187" t="n">
-        <v>6937530</v>
+        <v>6937516</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21600,10 +21600,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124630273</v>
+        <v>124618703</v>
       </c>
       <c r="B188" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21616,21 +21616,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -21640,13 +21640,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368585</v>
+        <v>368568</v>
       </c>
       <c r="R188" t="n">
-        <v>6937532</v>
+        <v>6937489</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124630509</v>
+        <v>124630092</v>
       </c>
       <c r="B189" t="n">
         <v>74901</v>
@@ -21742,10 +21742,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368603</v>
+        <v>368556</v>
       </c>
       <c r="R189" t="n">
-        <v>6937521</v>
+        <v>6937530</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -6015,10 +6015,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124623267</v>
+        <v>124623496</v>
       </c>
       <c r="B49" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6027,38 +6027,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>368810</v>
+        <v>368782</v>
       </c>
       <c r="R49" t="n">
-        <v>6938210</v>
+        <v>6938260</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6117,10 +6122,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124623496</v>
+        <v>124623267</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6129,43 +6134,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>368782</v>
+        <v>368810</v>
       </c>
       <c r="R50" t="n">
-        <v>6938260</v>
+        <v>6938210</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -21192,10 +21192,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124619608</v>
+        <v>124630273</v>
       </c>
       <c r="B184" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21208,37 +21208,37 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368492</v>
+        <v>368585</v>
       </c>
       <c r="R184" t="n">
-        <v>6937572</v>
+        <v>6937532</v>
       </c>
       <c r="S184" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124630273</v>
+        <v>124619608</v>
       </c>
       <c r="B185" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21310,37 +21310,37 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368585</v>
+        <v>368492</v>
       </c>
       <c r="R185" t="n">
-        <v>6937532</v>
+        <v>6937572</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -6015,7 +6015,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124623496</v>
+        <v>124623242</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>368782</v>
+        <v>368810</v>
       </c>
       <c r="R49" t="n">
-        <v>6938260</v>
+        <v>6938210</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6122,10 +6122,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124623267</v>
+        <v>124626137</v>
       </c>
       <c r="B50" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6134,38 +6134,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>368810</v>
+        <v>368833</v>
       </c>
       <c r="R50" t="n">
-        <v>6938210</v>
+        <v>6938244</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6326,10 +6331,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124626137</v>
+        <v>124623267</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6338,43 +6343,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>368833</v>
+        <v>368810</v>
       </c>
       <c r="R52" t="n">
-        <v>6938244</v>
+        <v>6938210</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124623242</v>
+        <v>124623496</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>368810</v>
+        <v>368782</v>
       </c>
       <c r="R53" t="n">
-        <v>6938210</v>
+        <v>6938260</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -17474,10 +17474,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>124628575</v>
+        <v>124628358</v>
       </c>
       <c r="B150" t="n">
-        <v>78889</v>
+        <v>91030</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17490,21 +17490,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17514,10 +17514,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>368486</v>
+        <v>368522</v>
       </c>
       <c r="R150" t="n">
-        <v>6938016</v>
+        <v>6938078</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17576,10 +17576,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>124628634</v>
+        <v>124627400</v>
       </c>
       <c r="B151" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17592,37 +17592,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>368486</v>
+        <v>368733</v>
       </c>
       <c r="R151" t="n">
-        <v>6937968</v>
+        <v>6938143</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17678,10 +17683,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124627400</v>
+        <v>124627646</v>
       </c>
       <c r="B152" t="n">
-        <v>57513</v>
+        <v>91457</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17690,46 +17695,41 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>368733</v>
+        <v>368729</v>
       </c>
       <c r="R152" t="n">
-        <v>6938143</v>
+        <v>6938156</v>
       </c>
       <c r="S152" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17785,10 +17785,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124627646</v>
+        <v>124622769</v>
       </c>
       <c r="B153" t="n">
-        <v>91457</v>
+        <v>57513</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17797,41 +17797,46 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>368729</v>
+        <v>368769</v>
       </c>
       <c r="R153" t="n">
-        <v>6938156</v>
+        <v>6938164</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17887,10 +17892,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124628358</v>
+        <v>124628575</v>
       </c>
       <c r="B154" t="n">
-        <v>91030</v>
+        <v>78889</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17903,21 +17908,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17927,10 +17932,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>368522</v>
+        <v>368486</v>
       </c>
       <c r="R154" t="n">
-        <v>6938078</v>
+        <v>6938016</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18091,10 +18096,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124622769</v>
+        <v>124628634</v>
       </c>
       <c r="B156" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18107,42 +18112,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>368769</v>
+        <v>368486</v>
       </c>
       <c r="R156" t="n">
-        <v>6938164</v>
+        <v>6937968</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -20988,10 +20988,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124620724</v>
+        <v>124618703</v>
       </c>
       <c r="B182" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21004,37 +21004,37 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Fjällkällan, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368610</v>
+        <v>368568</v>
       </c>
       <c r="R182" t="n">
-        <v>6937558</v>
+        <v>6937489</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21090,10 +21090,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124629552</v>
+        <v>124618931</v>
       </c>
       <c r="B183" t="n">
-        <v>82597</v>
+        <v>79920</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21102,41 +21102,41 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368487</v>
+        <v>368571</v>
       </c>
       <c r="R183" t="n">
-        <v>6937548</v>
+        <v>6937516</v>
       </c>
       <c r="S183" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21192,10 +21192,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124630273</v>
+        <v>124620724</v>
       </c>
       <c r="B184" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21208,34 +21208,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Fjällkällan, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368585</v>
+        <v>368610</v>
       </c>
       <c r="R184" t="n">
-        <v>6937532</v>
+        <v>6937558</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124619608</v>
+        <v>124629552</v>
       </c>
       <c r="B185" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21310,21 +21310,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21334,10 +21334,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368492</v>
+        <v>368487</v>
       </c>
       <c r="R185" t="n">
-        <v>6937572</v>
+        <v>6937548</v>
       </c>
       <c r="S185" t="n">
         <v>25</v>
@@ -21396,7 +21396,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124630509</v>
+        <v>124630273</v>
       </c>
       <c r="B186" t="n">
         <v>74901</v>
@@ -21436,10 +21436,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>368603</v>
+        <v>368585</v>
       </c>
       <c r="R186" t="n">
-        <v>6937521</v>
+        <v>6937532</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21498,10 +21498,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124618931</v>
+        <v>124619608</v>
       </c>
       <c r="B187" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21510,41 +21510,41 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>368571</v>
+        <v>368492</v>
       </c>
       <c r="R187" t="n">
-        <v>6937516</v>
+        <v>6937572</v>
       </c>
       <c r="S187" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21600,10 +21600,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124618703</v>
+        <v>124630092</v>
       </c>
       <c r="B188" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21616,21 +21616,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -21640,13 +21640,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368568</v>
+        <v>368556</v>
       </c>
       <c r="R188" t="n">
-        <v>6937489</v>
+        <v>6937530</v>
       </c>
       <c r="S188" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124630092</v>
+        <v>124630509</v>
       </c>
       <c r="B189" t="n">
         <v>74901</v>
@@ -21742,10 +21742,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368556</v>
+        <v>368603</v>
       </c>
       <c r="R189" t="n">
-        <v>6937530</v>
+        <v>6937521</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -5908,7 +5908,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124622908</v>
+        <v>124623496</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -5944,19 +5944,19 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>368781</v>
+        <v>368782</v>
       </c>
       <c r="R48" t="n">
-        <v>6938181</v>
+        <v>6938260</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6015,10 +6015,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124623242</v>
+        <v>124623267</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6027,33 +6027,28 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
@@ -6122,7 +6117,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124626137</v>
+        <v>124622908</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6158,19 +6153,19 @@
       <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>368833</v>
+        <v>368781</v>
       </c>
       <c r="R50" t="n">
-        <v>6938244</v>
+        <v>6938181</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6229,10 +6224,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124622913</v>
+        <v>124623242</v>
       </c>
       <c r="B51" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6245,34 +6240,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>368781</v>
+        <v>368810</v>
       </c>
       <c r="R51" t="n">
-        <v>6938181</v>
+        <v>6938210</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6331,10 +6331,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124623267</v>
+        <v>124622913</v>
       </c>
       <c r="B52" t="n">
-        <v>78151</v>
+        <v>91030</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6343,38 +6343,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>368810</v>
+        <v>368781</v>
       </c>
       <c r="R52" t="n">
-        <v>6938210</v>
+        <v>6938181</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124623496</v>
+        <v>124626137</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>368782</v>
+        <v>368833</v>
       </c>
       <c r="R53" t="n">
-        <v>6938260</v>
+        <v>6938244</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -17474,7 +17474,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>124628358</v>
+        <v>124628634</v>
       </c>
       <c r="B150" t="n">
         <v>91030</v>
@@ -17510,14 +17510,14 @@
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>368522</v>
+        <v>368486</v>
       </c>
       <c r="R150" t="n">
-        <v>6938078</v>
+        <v>6937968</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17576,10 +17576,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>124627400</v>
+        <v>124628358</v>
       </c>
       <c r="B151" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17592,42 +17592,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>368733</v>
+        <v>368522</v>
       </c>
       <c r="R151" t="n">
-        <v>6938143</v>
+        <v>6938078</v>
       </c>
       <c r="S151" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17892,10 +17887,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124628575</v>
+        <v>124627400</v>
       </c>
       <c r="B154" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17908,37 +17903,42 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>368486</v>
+        <v>368733</v>
       </c>
       <c r="R154" t="n">
-        <v>6938016</v>
+        <v>6938143</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17994,10 +17994,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124627082</v>
+        <v>124628575</v>
       </c>
       <c r="B155" t="n">
-        <v>91299</v>
+        <v>78889</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18010,37 +18010,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>368762</v>
+        <v>368486</v>
       </c>
       <c r="R155" t="n">
-        <v>6938143</v>
+        <v>6938016</v>
       </c>
       <c r="S155" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124628634</v>
+        <v>124627082</v>
       </c>
       <c r="B156" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18112,21 +18112,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -18136,13 +18136,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>368486</v>
+        <v>368762</v>
       </c>
       <c r="R156" t="n">
-        <v>6937968</v>
+        <v>6938143</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -20988,10 +20988,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124618703</v>
+        <v>124618931</v>
       </c>
       <c r="B182" t="n">
-        <v>82597</v>
+        <v>79920</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21000,25 +21000,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -21028,13 +21028,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368568</v>
+        <v>368571</v>
       </c>
       <c r="R182" t="n">
-        <v>6937489</v>
+        <v>6937516</v>
       </c>
       <c r="S182" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21090,10 +21090,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124618931</v>
+        <v>124630092</v>
       </c>
       <c r="B183" t="n">
-        <v>79920</v>
+        <v>74901</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21102,25 +21102,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -21130,13 +21130,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368571</v>
+        <v>368556</v>
       </c>
       <c r="R183" t="n">
-        <v>6937516</v>
+        <v>6937530</v>
       </c>
       <c r="S183" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124629552</v>
+        <v>124618703</v>
       </c>
       <c r="B185" t="n">
         <v>82597</v>
@@ -21330,14 +21330,14 @@
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368487</v>
+        <v>368568</v>
       </c>
       <c r="R185" t="n">
-        <v>6937548</v>
+        <v>6937489</v>
       </c>
       <c r="S185" t="n">
         <v>25</v>
@@ -21396,10 +21396,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124630273</v>
+        <v>124629552</v>
       </c>
       <c r="B186" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21412,37 +21412,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>368585</v>
+        <v>368487</v>
       </c>
       <c r="R186" t="n">
-        <v>6937532</v>
+        <v>6937548</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21498,10 +21498,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124619608</v>
+        <v>124630509</v>
       </c>
       <c r="B187" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21514,37 +21514,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>368492</v>
+        <v>368603</v>
       </c>
       <c r="R187" t="n">
-        <v>6937572</v>
+        <v>6937521</v>
       </c>
       <c r="S187" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124630092</v>
+        <v>124630273</v>
       </c>
       <c r="B188" t="n">
         <v>74901</v>
@@ -21640,10 +21640,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368556</v>
+        <v>368585</v>
       </c>
       <c r="R188" t="n">
-        <v>6937530</v>
+        <v>6937532</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21702,10 +21702,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124630509</v>
+        <v>124619608</v>
       </c>
       <c r="B189" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21718,37 +21718,37 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368603</v>
+        <v>368492</v>
       </c>
       <c r="R189" t="n">
-        <v>6937521</v>
+        <v>6937572</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -5908,7 +5908,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124623496</v>
+        <v>124623242</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>368782</v>
+        <v>368810</v>
       </c>
       <c r="R48" t="n">
-        <v>6938260</v>
+        <v>6938210</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6015,10 +6015,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124623267</v>
+        <v>124622908</v>
       </c>
       <c r="B49" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6027,38 +6027,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>368810</v>
+        <v>368781</v>
       </c>
       <c r="R49" t="n">
-        <v>6938210</v>
+        <v>6938181</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6117,10 +6122,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124622908</v>
+        <v>124622913</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6133,29 +6138,24 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
@@ -6224,10 +6224,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124623242</v>
+        <v>124623267</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6236,33 +6236,28 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
@@ -6331,10 +6326,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124622913</v>
+        <v>124623496</v>
       </c>
       <c r="B52" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6347,34 +6342,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>368781</v>
+        <v>368782</v>
       </c>
       <c r="R52" t="n">
-        <v>6938181</v>
+        <v>6938260</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -17474,10 +17474,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>124628634</v>
+        <v>124627400</v>
       </c>
       <c r="B150" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17490,37 +17490,42 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>368486</v>
+        <v>368733</v>
       </c>
       <c r="R150" t="n">
-        <v>6937968</v>
+        <v>6938143</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17678,10 +17683,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124627646</v>
+        <v>124628575</v>
       </c>
       <c r="B152" t="n">
-        <v>91457</v>
+        <v>78889</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17690,25 +17695,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1209</v>
+        <v>864</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17718,10 +17723,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>368729</v>
+        <v>368486</v>
       </c>
       <c r="R152" t="n">
-        <v>6938156</v>
+        <v>6938016</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17887,10 +17892,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124627400</v>
+        <v>124628634</v>
       </c>
       <c r="B154" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17903,42 +17908,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>368733</v>
+        <v>368486</v>
       </c>
       <c r="R154" t="n">
-        <v>6938143</v>
+        <v>6937968</v>
       </c>
       <c r="S154" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17994,10 +17994,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124628575</v>
+        <v>124627082</v>
       </c>
       <c r="B155" t="n">
-        <v>78889</v>
+        <v>91299</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18010,37 +18010,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>368486</v>
+        <v>368762</v>
       </c>
       <c r="R155" t="n">
-        <v>6938016</v>
+        <v>6938143</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124627082</v>
+        <v>124627646</v>
       </c>
       <c r="B156" t="n">
-        <v>91299</v>
+        <v>91457</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18108,41 +18108,41 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>368762</v>
+        <v>368729</v>
       </c>
       <c r="R156" t="n">
-        <v>6938143</v>
+        <v>6938156</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -20988,10 +20988,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124618931</v>
+        <v>124630092</v>
       </c>
       <c r="B182" t="n">
-        <v>79920</v>
+        <v>74901</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21000,25 +21000,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -21028,13 +21028,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368571</v>
+        <v>368556</v>
       </c>
       <c r="R182" t="n">
-        <v>6937516</v>
+        <v>6937530</v>
       </c>
       <c r="S182" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21090,10 +21090,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124630092</v>
+        <v>124618931</v>
       </c>
       <c r="B183" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21102,25 +21102,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -21130,13 +21130,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368556</v>
+        <v>368571</v>
       </c>
       <c r="R183" t="n">
-        <v>6937530</v>
+        <v>6937516</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124618703</v>
+        <v>124630509</v>
       </c>
       <c r="B185" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21310,21 +21310,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21334,13 +21334,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368568</v>
+        <v>368603</v>
       </c>
       <c r="R185" t="n">
-        <v>6937489</v>
+        <v>6937521</v>
       </c>
       <c r="S185" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124630509</v>
+        <v>124630273</v>
       </c>
       <c r="B187" t="n">
         <v>74901</v>
@@ -21538,10 +21538,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>368603</v>
+        <v>368585</v>
       </c>
       <c r="R187" t="n">
-        <v>6937521</v>
+        <v>6937532</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21600,10 +21600,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124630273</v>
+        <v>124618703</v>
       </c>
       <c r="B188" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21616,21 +21616,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -21640,13 +21640,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368585</v>
+        <v>368568</v>
       </c>
       <c r="R188" t="n">
-        <v>6937532</v>
+        <v>6937489</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -21396,10 +21396,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124629552</v>
+        <v>124630273</v>
       </c>
       <c r="B186" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21412,37 +21412,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>368487</v>
+        <v>368585</v>
       </c>
       <c r="R186" t="n">
-        <v>6937548</v>
+        <v>6937532</v>
       </c>
       <c r="S186" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21498,10 +21498,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124630273</v>
+        <v>124629552</v>
       </c>
       <c r="B187" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21514,37 +21514,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>368585</v>
+        <v>368487</v>
       </c>
       <c r="R187" t="n">
-        <v>6937532</v>
+        <v>6937548</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -5908,10 +5908,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124623242</v>
+        <v>124622913</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5924,39 +5924,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>368810</v>
+        <v>368781</v>
       </c>
       <c r="R48" t="n">
-        <v>6938210</v>
+        <v>6938181</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6015,10 +6010,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124622908</v>
+        <v>124623267</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6027,43 +6022,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>368781</v>
+        <v>368810</v>
       </c>
       <c r="R49" t="n">
-        <v>6938181</v>
+        <v>6938210</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6122,10 +6112,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124622913</v>
+        <v>124626137</v>
       </c>
       <c r="B50" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6138,34 +6128,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>368781</v>
+        <v>368833</v>
       </c>
       <c r="R50" t="n">
-        <v>6938181</v>
+        <v>6938244</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6224,10 +6219,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124623267</v>
+        <v>124622908</v>
       </c>
       <c r="B51" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6236,38 +6231,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>368810</v>
+        <v>368781</v>
       </c>
       <c r="R51" t="n">
-        <v>6938210</v>
+        <v>6938181</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124626137</v>
+        <v>124623242</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>368833</v>
+        <v>368810</v>
       </c>
       <c r="R53" t="n">
-        <v>6938244</v>
+        <v>6938210</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -17474,10 +17474,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>124627400</v>
+        <v>124628575</v>
       </c>
       <c r="B150" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17490,42 +17490,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>368733</v>
+        <v>368486</v>
       </c>
       <c r="R150" t="n">
-        <v>6938143</v>
+        <v>6938016</v>
       </c>
       <c r="S150" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17683,10 +17678,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124628575</v>
+        <v>124627400</v>
       </c>
       <c r="B152" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17699,37 +17694,42 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>368486</v>
+        <v>368733</v>
       </c>
       <c r="R152" t="n">
-        <v>6938016</v>
+        <v>6938143</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17892,10 +17892,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124628634</v>
+        <v>124627082</v>
       </c>
       <c r="B154" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17908,21 +17908,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17932,13 +17932,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>368486</v>
+        <v>368762</v>
       </c>
       <c r="R154" t="n">
-        <v>6937968</v>
+        <v>6938143</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17994,10 +17994,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124627082</v>
+        <v>124628634</v>
       </c>
       <c r="B155" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18010,21 +18010,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -18034,13 +18034,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>368762</v>
+        <v>368486</v>
       </c>
       <c r="R155" t="n">
-        <v>6938143</v>
+        <v>6937968</v>
       </c>
       <c r="S155" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124630092</v>
+        <v>124630509</v>
       </c>
       <c r="B182" t="n">
         <v>74901</v>
@@ -21028,10 +21028,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368556</v>
+        <v>368603</v>
       </c>
       <c r="R182" t="n">
-        <v>6937530</v>
+        <v>6937521</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21090,10 +21090,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124618931</v>
+        <v>124619608</v>
       </c>
       <c r="B183" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21102,41 +21102,41 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368571</v>
+        <v>368492</v>
       </c>
       <c r="R183" t="n">
-        <v>6937516</v>
+        <v>6937572</v>
       </c>
       <c r="S183" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124630509</v>
+        <v>124618931</v>
       </c>
       <c r="B185" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21306,25 +21306,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21334,13 +21334,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368603</v>
+        <v>368571</v>
       </c>
       <c r="R185" t="n">
-        <v>6937521</v>
+        <v>6937516</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21396,10 +21396,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124630273</v>
+        <v>124618703</v>
       </c>
       <c r="B186" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21412,21 +21412,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -21436,13 +21436,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>368585</v>
+        <v>368568</v>
       </c>
       <c r="R186" t="n">
-        <v>6937532</v>
+        <v>6937489</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21498,10 +21498,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124629552</v>
+        <v>124630092</v>
       </c>
       <c r="B187" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21514,37 +21514,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>368487</v>
+        <v>368556</v>
       </c>
       <c r="R187" t="n">
-        <v>6937548</v>
+        <v>6937530</v>
       </c>
       <c r="S187" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21600,10 +21600,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124618703</v>
+        <v>124630273</v>
       </c>
       <c r="B188" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21616,21 +21616,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -21640,13 +21640,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368568</v>
+        <v>368585</v>
       </c>
       <c r="R188" t="n">
-        <v>6937489</v>
+        <v>6937532</v>
       </c>
       <c r="S188" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21702,10 +21702,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124619608</v>
+        <v>124629552</v>
       </c>
       <c r="B189" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21718,21 +21718,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -21742,10 +21742,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368492</v>
+        <v>368487</v>
       </c>
       <c r="R189" t="n">
-        <v>6937572</v>
+        <v>6937548</v>
       </c>
       <c r="S189" t="n">
         <v>25</v>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -5908,10 +5908,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124622913</v>
+        <v>124626137</v>
       </c>
       <c r="B48" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5924,34 +5924,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>368781</v>
+        <v>368833</v>
       </c>
       <c r="R48" t="n">
-        <v>6938181</v>
+        <v>6938244</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6112,7 +6117,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124626137</v>
+        <v>124623242</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6157,10 +6162,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>368833</v>
+        <v>368810</v>
       </c>
       <c r="R50" t="n">
-        <v>6938244</v>
+        <v>6938210</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6219,10 +6224,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124622908</v>
+        <v>124622913</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6235,29 +6240,24 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124623242</v>
+        <v>124622908</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6469,19 +6469,19 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>368810</v>
+        <v>368781</v>
       </c>
       <c r="R53" t="n">
-        <v>6938210</v>
+        <v>6938181</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -17474,10 +17474,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>124628575</v>
+        <v>124627400</v>
       </c>
       <c r="B150" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17490,37 +17490,42 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>368486</v>
+        <v>368733</v>
       </c>
       <c r="R150" t="n">
-        <v>6938016</v>
+        <v>6938143</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17576,10 +17581,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>124628358</v>
+        <v>124622769</v>
       </c>
       <c r="B151" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17592,37 +17597,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>368522</v>
+        <v>368769</v>
       </c>
       <c r="R151" t="n">
-        <v>6938078</v>
+        <v>6938164</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17678,10 +17688,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124627400</v>
+        <v>124627646</v>
       </c>
       <c r="B152" t="n">
-        <v>57513</v>
+        <v>91457</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17690,46 +17700,41 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>368733</v>
+        <v>368729</v>
       </c>
       <c r="R152" t="n">
-        <v>6938143</v>
+        <v>6938156</v>
       </c>
       <c r="S152" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17785,10 +17790,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124622769</v>
+        <v>124628358</v>
       </c>
       <c r="B153" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17801,42 +17806,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>368769</v>
+        <v>368522</v>
       </c>
       <c r="R153" t="n">
-        <v>6938164</v>
+        <v>6938078</v>
       </c>
       <c r="S153" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17892,10 +17892,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124627082</v>
+        <v>124628575</v>
       </c>
       <c r="B154" t="n">
-        <v>91299</v>
+        <v>78889</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17908,37 +17908,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>368762</v>
+        <v>368486</v>
       </c>
       <c r="R154" t="n">
-        <v>6938143</v>
+        <v>6938016</v>
       </c>
       <c r="S154" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124627646</v>
+        <v>124627082</v>
       </c>
       <c r="B156" t="n">
-        <v>91457</v>
+        <v>91299</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18108,41 +18108,41 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>368729</v>
+        <v>368762</v>
       </c>
       <c r="R156" t="n">
-        <v>6938156</v>
+        <v>6938143</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -20988,10 +20988,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124630509</v>
+        <v>124618703</v>
       </c>
       <c r="B182" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21004,21 +21004,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -21028,13 +21028,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368603</v>
+        <v>368568</v>
       </c>
       <c r="R182" t="n">
-        <v>6937521</v>
+        <v>6937489</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124619608</v>
+        <v>124620724</v>
       </c>
       <c r="B183" t="n">
         <v>91030</v>
@@ -21126,17 +21126,17 @@
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Hjd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368492</v>
+        <v>368610</v>
       </c>
       <c r="R183" t="n">
-        <v>6937572</v>
+        <v>6937558</v>
       </c>
       <c r="S183" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21192,10 +21192,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124620724</v>
+        <v>124630509</v>
       </c>
       <c r="B184" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21208,34 +21208,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Fjällkällan, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368610</v>
+        <v>368603</v>
       </c>
       <c r="R184" t="n">
-        <v>6937558</v>
+        <v>6937521</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124618931</v>
+        <v>124629552</v>
       </c>
       <c r="B185" t="n">
-        <v>79920</v>
+        <v>82597</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21306,41 +21306,41 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368571</v>
+        <v>368487</v>
       </c>
       <c r="R185" t="n">
-        <v>6937516</v>
+        <v>6937548</v>
       </c>
       <c r="S185" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21396,10 +21396,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124618703</v>
+        <v>124619608</v>
       </c>
       <c r="B186" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21412,34 +21412,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>368568</v>
+        <v>368492</v>
       </c>
       <c r="R186" t="n">
-        <v>6937489</v>
+        <v>6937572</v>
       </c>
       <c r="S186" t="n">
         <v>25</v>
@@ -21600,10 +21600,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124630273</v>
+        <v>124618931</v>
       </c>
       <c r="B188" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21612,25 +21612,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -21640,13 +21640,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368585</v>
+        <v>368571</v>
       </c>
       <c r="R188" t="n">
-        <v>6937532</v>
+        <v>6937516</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21702,10 +21702,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124629552</v>
+        <v>124630273</v>
       </c>
       <c r="B189" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21718,37 +21718,37 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368487</v>
+        <v>368585</v>
       </c>
       <c r="R189" t="n">
-        <v>6937548</v>
+        <v>6937532</v>
       </c>
       <c r="S189" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -5908,10 +5908,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124626137</v>
+        <v>124622913</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5924,39 +5924,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>368833</v>
+        <v>368781</v>
       </c>
       <c r="R48" t="n">
-        <v>6938244</v>
+        <v>6938181</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6117,7 +6112,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124623242</v>
+        <v>124626137</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6162,10 +6157,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>368810</v>
+        <v>368833</v>
       </c>
       <c r="R50" t="n">
-        <v>6938210</v>
+        <v>6938244</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6224,10 +6219,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124622913</v>
+        <v>124622908</v>
       </c>
       <c r="B51" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6240,24 +6235,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124622908</v>
+        <v>124623242</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6469,19 +6469,19 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>368781</v>
+        <v>368810</v>
       </c>
       <c r="R53" t="n">
-        <v>6938181</v>
+        <v>6938210</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -17688,10 +17688,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124627646</v>
+        <v>124628634</v>
       </c>
       <c r="B152" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17700,38 +17700,38 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>368729</v>
+        <v>368486</v>
       </c>
       <c r="R152" t="n">
-        <v>6938156</v>
+        <v>6937968</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17790,10 +17790,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124628358</v>
+        <v>124628575</v>
       </c>
       <c r="B153" t="n">
-        <v>91030</v>
+        <v>78889</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17806,21 +17806,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17830,10 +17830,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>368522</v>
+        <v>368486</v>
       </c>
       <c r="R153" t="n">
-        <v>6938078</v>
+        <v>6938016</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17892,10 +17892,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124628575</v>
+        <v>124627646</v>
       </c>
       <c r="B154" t="n">
-        <v>78889</v>
+        <v>91457</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17904,25 +17904,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>864</v>
+        <v>1209</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17932,10 +17932,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>368486</v>
+        <v>368729</v>
       </c>
       <c r="R154" t="n">
-        <v>6938016</v>
+        <v>6938156</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17994,10 +17994,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124628634</v>
+        <v>124627082</v>
       </c>
       <c r="B155" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18010,21 +18010,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -18034,13 +18034,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>368486</v>
+        <v>368762</v>
       </c>
       <c r="R155" t="n">
-        <v>6937968</v>
+        <v>6938143</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124627082</v>
+        <v>124628358</v>
       </c>
       <c r="B156" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18112,37 +18112,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>368762</v>
+        <v>368522</v>
       </c>
       <c r="R156" t="n">
-        <v>6938143</v>
+        <v>6938078</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -20988,10 +20988,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124618703</v>
+        <v>124619608</v>
       </c>
       <c r="B182" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21004,34 +21004,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368568</v>
+        <v>368492</v>
       </c>
       <c r="R182" t="n">
-        <v>6937489</v>
+        <v>6937572</v>
       </c>
       <c r="S182" t="n">
         <v>25</v>
@@ -21192,10 +21192,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124630509</v>
+        <v>124618931</v>
       </c>
       <c r="B184" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21204,25 +21204,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -21232,13 +21232,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368603</v>
+        <v>368571</v>
       </c>
       <c r="R184" t="n">
-        <v>6937521</v>
+        <v>6937516</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124629552</v>
+        <v>124618703</v>
       </c>
       <c r="B185" t="n">
         <v>82597</v>
@@ -21330,14 +21330,14 @@
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368487</v>
+        <v>368568</v>
       </c>
       <c r="R185" t="n">
-        <v>6937548</v>
+        <v>6937489</v>
       </c>
       <c r="S185" t="n">
         <v>25</v>
@@ -21396,10 +21396,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124619608</v>
+        <v>124630509</v>
       </c>
       <c r="B186" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21412,37 +21412,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>368492</v>
+        <v>368603</v>
       </c>
       <c r="R186" t="n">
-        <v>6937572</v>
+        <v>6937521</v>
       </c>
       <c r="S186" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21498,10 +21498,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124630092</v>
+        <v>124629552</v>
       </c>
       <c r="B187" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21514,37 +21514,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>368556</v>
+        <v>368487</v>
       </c>
       <c r="R187" t="n">
-        <v>6937530</v>
+        <v>6937548</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21600,10 +21600,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124618931</v>
+        <v>124630273</v>
       </c>
       <c r="B188" t="n">
-        <v>79920</v>
+        <v>74901</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21612,25 +21612,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -21640,13 +21640,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368571</v>
+        <v>368585</v>
       </c>
       <c r="R188" t="n">
-        <v>6937516</v>
+        <v>6937532</v>
       </c>
       <c r="S188" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124630273</v>
+        <v>124630092</v>
       </c>
       <c r="B189" t="n">
         <v>74901</v>
@@ -21742,10 +21742,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368585</v>
+        <v>368556</v>
       </c>
       <c r="R189" t="n">
-        <v>6937532</v>
+        <v>6937530</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -5908,10 +5908,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124622913</v>
+        <v>124622908</v>
       </c>
       <c r="B48" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5924,24 +5924,29 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
@@ -6010,10 +6015,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124623267</v>
+        <v>124622913</v>
       </c>
       <c r="B49" t="n">
-        <v>78151</v>
+        <v>91030</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6022,38 +6027,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>368810</v>
+        <v>368781</v>
       </c>
       <c r="R49" t="n">
-        <v>6938210</v>
+        <v>6938181</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6112,7 +6117,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124626137</v>
+        <v>124623496</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6157,10 +6162,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>368833</v>
+        <v>368782</v>
       </c>
       <c r="R50" t="n">
-        <v>6938244</v>
+        <v>6938260</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6219,7 +6224,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124622908</v>
+        <v>124626137</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -6255,19 +6260,19 @@
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>368781</v>
+        <v>368833</v>
       </c>
       <c r="R51" t="n">
-        <v>6938181</v>
+        <v>6938244</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6326,10 +6331,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124623496</v>
+        <v>124623267</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6338,43 +6343,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>368782</v>
+        <v>368810</v>
       </c>
       <c r="R52" t="n">
-        <v>6938260</v>
+        <v>6938210</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -17474,10 +17474,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>124627400</v>
+        <v>124628575</v>
       </c>
       <c r="B150" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17490,42 +17490,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>368733</v>
+        <v>368486</v>
       </c>
       <c r="R150" t="n">
-        <v>6938143</v>
+        <v>6938016</v>
       </c>
       <c r="S150" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17581,10 +17576,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>124622769</v>
+        <v>124627082</v>
       </c>
       <c r="B151" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17597,42 +17592,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>368769</v>
+        <v>368762</v>
       </c>
       <c r="R151" t="n">
-        <v>6938164</v>
+        <v>6938143</v>
       </c>
       <c r="S151" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17688,10 +17678,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124628634</v>
+        <v>124627646</v>
       </c>
       <c r="B152" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17700,38 +17690,38 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>368486</v>
+        <v>368729</v>
       </c>
       <c r="R152" t="n">
-        <v>6937968</v>
+        <v>6938156</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17790,10 +17780,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124628575</v>
+        <v>124628634</v>
       </c>
       <c r="B153" t="n">
-        <v>78889</v>
+        <v>91030</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17806,34 +17796,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
         <v>368486</v>
       </c>
       <c r="R153" t="n">
-        <v>6938016</v>
+        <v>6937968</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17892,10 +17882,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124627646</v>
+        <v>124628358</v>
       </c>
       <c r="B154" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17904,25 +17894,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17932,10 +17922,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>368729</v>
+        <v>368522</v>
       </c>
       <c r="R154" t="n">
-        <v>6938156</v>
+        <v>6938078</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17994,10 +17984,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124627082</v>
+        <v>124622769</v>
       </c>
       <c r="B155" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18010,37 +18000,42 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>368762</v>
+        <v>368769</v>
       </c>
       <c r="R155" t="n">
-        <v>6938143</v>
+        <v>6938164</v>
       </c>
       <c r="S155" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18096,10 +18091,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>124628358</v>
+        <v>124627400</v>
       </c>
       <c r="B156" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18112,37 +18107,42 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>368522</v>
+        <v>368733</v>
       </c>
       <c r="R156" t="n">
-        <v>6938078</v>
+        <v>6938143</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -20988,10 +20988,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124619608</v>
+        <v>124618703</v>
       </c>
       <c r="B182" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21004,34 +21004,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368492</v>
+        <v>368568</v>
       </c>
       <c r="R182" t="n">
-        <v>6937572</v>
+        <v>6937489</v>
       </c>
       <c r="S182" t="n">
         <v>25</v>
@@ -21090,10 +21090,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124620724</v>
+        <v>124630509</v>
       </c>
       <c r="B183" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21106,34 +21106,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Fjällkällan, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368610</v>
+        <v>368603</v>
       </c>
       <c r="R183" t="n">
-        <v>6937558</v>
+        <v>6937521</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21192,10 +21192,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124618931</v>
+        <v>124620724</v>
       </c>
       <c r="B184" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21204,41 +21204,41 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Fjällkällan, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368571</v>
+        <v>368610</v>
       </c>
       <c r="R184" t="n">
-        <v>6937516</v>
+        <v>6937558</v>
       </c>
       <c r="S184" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124618703</v>
+        <v>124619608</v>
       </c>
       <c r="B185" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21310,34 +21310,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368568</v>
+        <v>368492</v>
       </c>
       <c r="R185" t="n">
-        <v>6937489</v>
+        <v>6937572</v>
       </c>
       <c r="S185" t="n">
         <v>25</v>
@@ -21396,10 +21396,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124630509</v>
+        <v>124629552</v>
       </c>
       <c r="B186" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21412,37 +21412,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>368603</v>
+        <v>368487</v>
       </c>
       <c r="R186" t="n">
-        <v>6937521</v>
+        <v>6937548</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21498,10 +21498,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124629552</v>
+        <v>124630092</v>
       </c>
       <c r="B187" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21514,37 +21514,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>368487</v>
+        <v>368556</v>
       </c>
       <c r="R187" t="n">
-        <v>6937548</v>
+        <v>6937530</v>
       </c>
       <c r="S187" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21600,10 +21600,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124630273</v>
+        <v>124618931</v>
       </c>
       <c r="B188" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21612,25 +21612,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -21640,13 +21640,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368585</v>
+        <v>368571</v>
       </c>
       <c r="R188" t="n">
-        <v>6937532</v>
+        <v>6937516</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124630092</v>
+        <v>124630273</v>
       </c>
       <c r="B189" t="n">
         <v>74901</v>
@@ -21742,10 +21742,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368556</v>
+        <v>368585</v>
       </c>
       <c r="R189" t="n">
-        <v>6937530</v>
+        <v>6937532</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -5908,10 +5908,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124622908</v>
+        <v>124623267</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5920,43 +5920,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>368781</v>
+        <v>368810</v>
       </c>
       <c r="R48" t="n">
-        <v>6938181</v>
+        <v>6938210</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6015,10 +6010,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124622913</v>
+        <v>124626137</v>
       </c>
       <c r="B49" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6031,34 +6026,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>368781</v>
+        <v>368833</v>
       </c>
       <c r="R49" t="n">
-        <v>6938181</v>
+        <v>6938244</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6117,7 +6117,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124623496</v>
+        <v>124623242</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>368782</v>
+        <v>368810</v>
       </c>
       <c r="R50" t="n">
-        <v>6938260</v>
+        <v>6938210</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6224,10 +6224,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124626137</v>
+        <v>124622913</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6240,39 +6240,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>368833</v>
+        <v>368781</v>
       </c>
       <c r="R51" t="n">
-        <v>6938244</v>
+        <v>6938181</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6331,10 +6326,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124623267</v>
+        <v>124622908</v>
       </c>
       <c r="B52" t="n">
-        <v>78151</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6343,38 +6338,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>368810</v>
+        <v>368781</v>
       </c>
       <c r="R52" t="n">
-        <v>6938210</v>
+        <v>6938181</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124623242</v>
+        <v>124623496</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>368810</v>
+        <v>368782</v>
       </c>
       <c r="R53" t="n">
-        <v>6938210</v>
+        <v>6938260</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -17780,7 +17780,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124628634</v>
+        <v>124628358</v>
       </c>
       <c r="B153" t="n">
         <v>91030</v>
@@ -17816,14 +17816,14 @@
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>368486</v>
+        <v>368522</v>
       </c>
       <c r="R153" t="n">
-        <v>6937968</v>
+        <v>6938078</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17882,10 +17882,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124628358</v>
+        <v>124622769</v>
       </c>
       <c r="B154" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17898,37 +17898,42 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>368522</v>
+        <v>368769</v>
       </c>
       <c r="R154" t="n">
-        <v>6938078</v>
+        <v>6938164</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17984,10 +17989,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124622769</v>
+        <v>124628634</v>
       </c>
       <c r="B155" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18000,42 +18005,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>368769</v>
+        <v>368486</v>
       </c>
       <c r="R155" t="n">
-        <v>6938164</v>
+        <v>6937968</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -20988,10 +20988,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124618703</v>
+        <v>124630273</v>
       </c>
       <c r="B182" t="n">
-        <v>82597</v>
+        <v>74901</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21004,21 +21004,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -21028,13 +21028,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368568</v>
+        <v>368585</v>
       </c>
       <c r="R182" t="n">
-        <v>6937489</v>
+        <v>6937532</v>
       </c>
       <c r="S182" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21090,10 +21090,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124630509</v>
+        <v>124618931</v>
       </c>
       <c r="B183" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21102,25 +21102,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -21130,13 +21130,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368603</v>
+        <v>368571</v>
       </c>
       <c r="R183" t="n">
-        <v>6937521</v>
+        <v>6937516</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21192,10 +21192,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124620724</v>
+        <v>124630509</v>
       </c>
       <c r="B184" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21208,34 +21208,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Fjällkällan, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368610</v>
+        <v>368603</v>
       </c>
       <c r="R184" t="n">
-        <v>6937558</v>
+        <v>6937521</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124619608</v>
+        <v>124630092</v>
       </c>
       <c r="B185" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21310,37 +21310,37 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368492</v>
+        <v>368556</v>
       </c>
       <c r="R185" t="n">
-        <v>6937572</v>
+        <v>6937530</v>
       </c>
       <c r="S185" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21396,10 +21396,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124629552</v>
+        <v>124620724</v>
       </c>
       <c r="B186" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21412,37 +21412,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>368487</v>
+        <v>368610</v>
       </c>
       <c r="R186" t="n">
-        <v>6937548</v>
+        <v>6937558</v>
       </c>
       <c r="S186" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21498,10 +21498,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124630092</v>
+        <v>124619608</v>
       </c>
       <c r="B187" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21514,37 +21514,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>368556</v>
+        <v>368492</v>
       </c>
       <c r="R187" t="n">
-        <v>6937530</v>
+        <v>6937572</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21600,10 +21600,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124618931</v>
+        <v>124629552</v>
       </c>
       <c r="B188" t="n">
-        <v>79920</v>
+        <v>82597</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21612,41 +21612,41 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368571</v>
+        <v>368487</v>
       </c>
       <c r="R188" t="n">
-        <v>6937516</v>
+        <v>6937548</v>
       </c>
       <c r="S188" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21702,10 +21702,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124630273</v>
+        <v>124618703</v>
       </c>
       <c r="B189" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21718,21 +21718,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -21742,13 +21742,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368585</v>
+        <v>368568</v>
       </c>
       <c r="R189" t="n">
-        <v>6937532</v>
+        <v>6937489</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -5908,10 +5908,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124623267</v>
+        <v>124622913</v>
       </c>
       <c r="B48" t="n">
-        <v>78151</v>
+        <v>91030</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5920,38 +5920,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>368810</v>
+        <v>368781</v>
       </c>
       <c r="R48" t="n">
-        <v>6938210</v>
+        <v>6938181</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6010,7 +6010,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124626137</v>
+        <v>124623242</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -6055,10 +6055,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>368833</v>
+        <v>368810</v>
       </c>
       <c r="R49" t="n">
-        <v>6938244</v>
+        <v>6938210</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6117,10 +6117,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124623242</v>
+        <v>124623267</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>78151</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6129,33 +6129,28 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
@@ -6224,10 +6219,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124622913</v>
+        <v>124626137</v>
       </c>
       <c r="B51" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6240,34 +6235,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>368781</v>
+        <v>368833</v>
       </c>
       <c r="R51" t="n">
-        <v>6938181</v>
+        <v>6938244</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -17474,10 +17474,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>124628575</v>
+        <v>124627082</v>
       </c>
       <c r="B150" t="n">
-        <v>78889</v>
+        <v>91299</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17490,37 +17490,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>368486</v>
+        <v>368762</v>
       </c>
       <c r="R150" t="n">
-        <v>6938016</v>
+        <v>6938143</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17576,10 +17576,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>124627082</v>
+        <v>124628575</v>
       </c>
       <c r="B151" t="n">
-        <v>91299</v>
+        <v>78889</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17592,37 +17592,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>368762</v>
+        <v>368486</v>
       </c>
       <c r="R151" t="n">
-        <v>6938143</v>
+        <v>6938016</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17780,10 +17780,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124628358</v>
+        <v>124622769</v>
       </c>
       <c r="B153" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17796,37 +17796,42 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>368522</v>
+        <v>368769</v>
       </c>
       <c r="R153" t="n">
-        <v>6938078</v>
+        <v>6938164</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17882,10 +17887,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>124622769</v>
+        <v>124628634</v>
       </c>
       <c r="B154" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17898,42 +17903,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>368769</v>
+        <v>368486</v>
       </c>
       <c r="R154" t="n">
-        <v>6938164</v>
+        <v>6937968</v>
       </c>
       <c r="S154" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124628634</v>
+        <v>124628358</v>
       </c>
       <c r="B155" t="n">
         <v>91030</v>
@@ -18025,14 +18025,14 @@
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>368486</v>
+        <v>368522</v>
       </c>
       <c r="R155" t="n">
-        <v>6937968</v>
+        <v>6938078</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -21090,10 +21090,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124618931</v>
+        <v>124630509</v>
       </c>
       <c r="B183" t="n">
-        <v>79920</v>
+        <v>74901</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21102,25 +21102,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -21130,13 +21130,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368571</v>
+        <v>368603</v>
       </c>
       <c r="R183" t="n">
-        <v>6937516</v>
+        <v>6937521</v>
       </c>
       <c r="S183" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21192,10 +21192,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124630509</v>
+        <v>124618703</v>
       </c>
       <c r="B184" t="n">
-        <v>74901</v>
+        <v>82597</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21208,21 +21208,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -21232,13 +21232,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368603</v>
+        <v>368568</v>
       </c>
       <c r="R184" t="n">
-        <v>6937521</v>
+        <v>6937489</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124630092</v>
+        <v>124618931</v>
       </c>
       <c r="B185" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21306,25 +21306,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21334,13 +21334,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368556</v>
+        <v>368571</v>
       </c>
       <c r="R185" t="n">
-        <v>6937530</v>
+        <v>6937516</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21396,10 +21396,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124620724</v>
+        <v>124630092</v>
       </c>
       <c r="B186" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21412,34 +21412,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Fjällkällan, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>368610</v>
+        <v>368556</v>
       </c>
       <c r="R186" t="n">
-        <v>6937558</v>
+        <v>6937530</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21498,7 +21498,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124619608</v>
+        <v>124620724</v>
       </c>
       <c r="B187" t="n">
         <v>91030</v>
@@ -21534,17 +21534,17 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>368492</v>
+        <v>368610</v>
       </c>
       <c r="R187" t="n">
-        <v>6937572</v>
+        <v>6937558</v>
       </c>
       <c r="S187" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21702,10 +21702,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124618703</v>
+        <v>124619608</v>
       </c>
       <c r="B189" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21718,34 +21718,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368568</v>
+        <v>368492</v>
       </c>
       <c r="R189" t="n">
-        <v>6937489</v>
+        <v>6937572</v>
       </c>
       <c r="S189" t="n">
         <v>25</v>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -5908,10 +5908,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124622913</v>
+        <v>124626137</v>
       </c>
       <c r="B48" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5924,34 +5924,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>368781</v>
+        <v>368833</v>
       </c>
       <c r="R48" t="n">
-        <v>6938181</v>
+        <v>6938244</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6010,10 +6015,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124623242</v>
+        <v>124623496</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6055,10 +6060,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>368810</v>
+        <v>368782</v>
       </c>
       <c r="R49" t="n">
-        <v>6938210</v>
+        <v>6938260</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6117,10 +6122,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124623267</v>
+        <v>124622908</v>
       </c>
       <c r="B50" t="n">
-        <v>78151</v>
+        <v>57635</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6129,38 +6134,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>368810</v>
+        <v>368781</v>
       </c>
       <c r="R50" t="n">
-        <v>6938210</v>
+        <v>6938181</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6219,10 +6229,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124626137</v>
+        <v>124623267</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>78288</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6231,43 +6241,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>368833</v>
+        <v>368810</v>
       </c>
       <c r="R51" t="n">
-        <v>6938244</v>
+        <v>6938210</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6326,10 +6331,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124622908</v>
+        <v>124622913</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6342,29 +6347,24 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124623496</v>
+        <v>124623242</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>368782</v>
+        <v>368810</v>
       </c>
       <c r="R53" t="n">
-        <v>6938260</v>
+        <v>6938210</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -17474,10 +17474,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>124627082</v>
+        <v>124622769</v>
       </c>
       <c r="B150" t="n">
-        <v>91299</v>
+        <v>57635</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17490,37 +17490,42 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>368762</v>
+        <v>368769</v>
       </c>
       <c r="R150" t="n">
-        <v>6938143</v>
+        <v>6938164</v>
       </c>
       <c r="S150" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17576,10 +17581,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>124628575</v>
+        <v>124628358</v>
       </c>
       <c r="B151" t="n">
-        <v>78889</v>
+        <v>91184</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17592,21 +17597,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17616,10 +17621,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>368486</v>
+        <v>368522</v>
       </c>
       <c r="R151" t="n">
-        <v>6938016</v>
+        <v>6938078</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17678,10 +17683,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>124627646</v>
+        <v>124627082</v>
       </c>
       <c r="B152" t="n">
-        <v>91457</v>
+        <v>91459</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17690,41 +17695,41 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>368729</v>
+        <v>368762</v>
       </c>
       <c r="R152" t="n">
-        <v>6938156</v>
+        <v>6938143</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17780,10 +17785,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>124622769</v>
+        <v>124627646</v>
       </c>
       <c r="B153" t="n">
-        <v>57513</v>
+        <v>91617</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17792,46 +17797,41 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>368769</v>
+        <v>368729</v>
       </c>
       <c r="R153" t="n">
-        <v>6938164</v>
+        <v>6938156</v>
       </c>
       <c r="S153" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>124628634</v>
       </c>
       <c r="B154" t="n">
-        <v>91030</v>
+        <v>91184</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17989,10 +17989,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>124628358</v>
+        <v>124628575</v>
       </c>
       <c r="B155" t="n">
-        <v>91030</v>
+        <v>79026</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18005,21 +18005,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -18029,10 +18029,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>368522</v>
+        <v>368486</v>
       </c>
       <c r="R155" t="n">
-        <v>6938078</v>
+        <v>6938016</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18094,7 +18094,7 @@
         <v>124627400</v>
       </c>
       <c r="B156" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -20988,10 +20988,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124630273</v>
+        <v>124618703</v>
       </c>
       <c r="B182" t="n">
-        <v>74901</v>
+        <v>82737</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21004,21 +21004,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -21028,13 +21028,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368585</v>
+        <v>368568</v>
       </c>
       <c r="R182" t="n">
-        <v>6937532</v>
+        <v>6937489</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21090,10 +21090,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124630509</v>
+        <v>124630092</v>
       </c>
       <c r="B183" t="n">
-        <v>74901</v>
+        <v>75025</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21130,10 +21130,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368603</v>
+        <v>368556</v>
       </c>
       <c r="R183" t="n">
-        <v>6937521</v>
+        <v>6937530</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21192,10 +21192,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124618703</v>
+        <v>124618931</v>
       </c>
       <c r="B184" t="n">
-        <v>82597</v>
+        <v>80057</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21204,25 +21204,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -21232,13 +21232,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368568</v>
+        <v>368571</v>
       </c>
       <c r="R184" t="n">
-        <v>6937489</v>
+        <v>6937516</v>
       </c>
       <c r="S184" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21294,10 +21294,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124618931</v>
+        <v>124630273</v>
       </c>
       <c r="B185" t="n">
-        <v>79920</v>
+        <v>75025</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21306,25 +21306,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21334,13 +21334,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368571</v>
+        <v>368585</v>
       </c>
       <c r="R185" t="n">
-        <v>6937516</v>
+        <v>6937532</v>
       </c>
       <c r="S185" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21396,10 +21396,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124630092</v>
+        <v>124630509</v>
       </c>
       <c r="B186" t="n">
-        <v>74901</v>
+        <v>75025</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21436,10 +21436,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>368556</v>
+        <v>368603</v>
       </c>
       <c r="R186" t="n">
-        <v>6937530</v>
+        <v>6937521</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21498,10 +21498,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124620724</v>
+        <v>124619608</v>
       </c>
       <c r="B187" t="n">
-        <v>91030</v>
+        <v>91184</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21534,17 +21534,17 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Fjällkällan, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>368610</v>
+        <v>368492</v>
       </c>
       <c r="R187" t="n">
-        <v>6937558</v>
+        <v>6937572</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21600,10 +21600,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124629552</v>
+        <v>124620724</v>
       </c>
       <c r="B188" t="n">
-        <v>82597</v>
+        <v>91184</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21616,37 +21616,37 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368487</v>
+        <v>368610</v>
       </c>
       <c r="R188" t="n">
-        <v>6937548</v>
+        <v>6937558</v>
       </c>
       <c r="S188" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21702,10 +21702,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124619608</v>
+        <v>124629552</v>
       </c>
       <c r="B189" t="n">
-        <v>91030</v>
+        <v>82737</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21718,21 +21718,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -21742,10 +21742,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368492</v>
+        <v>368487</v>
       </c>
       <c r="R189" t="n">
-        <v>6937572</v>
+        <v>6937548</v>
       </c>
       <c r="S189" t="n">
         <v>25</v>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY189"/>
+  <dimension ref="A1:AY190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18198,54 +18198,48 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>103551484</v>
+        <v>125741282</v>
       </c>
       <c r="B157" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91627</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6440</v>
+        <v>4217</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>368486.8215149617</v>
+        <v>368540</v>
       </c>
       <c r="R157" t="n">
-        <v>6937547.960590951</v>
+        <v>6938067</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18269,22 +18263,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18311,10 +18295,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>103552447</v>
+        <v>103551484</v>
       </c>
       <c r="B158" t="n">
-        <v>81236</v>
+        <v>73693</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18327,21 +18311,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18352,10 +18336,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>368343.0240888702</v>
+        <v>368486.8215149617</v>
       </c>
       <c r="R158" t="n">
-        <v>6937619.248962435</v>
+        <v>6937547.960590951</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -18424,7 +18408,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>103551351</v>
+        <v>103552447</v>
       </c>
       <c r="B159" t="n">
         <v>81236</v>
@@ -18461,14 +18445,14 @@
       <c r="K159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Fjällkällan, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>368544.7253621799</v>
+        <v>368343.0240888702</v>
       </c>
       <c r="R159" t="n">
-        <v>6937480.078827508</v>
+        <v>6937619.248962435</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -18537,10 +18521,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>103552443</v>
+        <v>103551351</v>
       </c>
       <c r="B160" t="n">
-        <v>89410</v>
+        <v>81236</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18553,35 +18537,35 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>368343.0240888702</v>
+        <v>368544.7253621799</v>
       </c>
       <c r="R160" t="n">
-        <v>6937619.248962435</v>
+        <v>6937480.078827508</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -18650,10 +18634,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>103551383</v>
+        <v>103552443</v>
       </c>
       <c r="B161" t="n">
-        <v>73693</v>
+        <v>89410</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18666,35 +18650,35 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Fjällkällan, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>368529.5480735453</v>
+        <v>368343.0240888702</v>
       </c>
       <c r="R161" t="n">
-        <v>6937505.621947487</v>
+        <v>6937619.248962435</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -18763,10 +18747,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>103551330</v>
+        <v>103551383</v>
       </c>
       <c r="B162" t="n">
-        <v>89410</v>
+        <v>73693</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18779,21 +18763,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -18804,10 +18788,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>368540.902881454</v>
+        <v>368529.5480735453</v>
       </c>
       <c r="R162" t="n">
-        <v>6937476.997030124</v>
+        <v>6937505.621947487</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -18876,10 +18860,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>103552489</v>
+        <v>103551330</v>
       </c>
       <c r="B163" t="n">
-        <v>77588</v>
+        <v>89410</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18892,35 +18876,35 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>368284.1649953357</v>
+        <v>368540.902881454</v>
       </c>
       <c r="R163" t="n">
-        <v>6937639.597708987</v>
+        <v>6937476.997030124</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -18989,10 +18973,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>103551371</v>
+        <v>103552489</v>
       </c>
       <c r="B164" t="n">
-        <v>73693</v>
+        <v>77588</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19005,35 +18989,35 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Fjällkällan, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>368549.5342763296</v>
+        <v>368284.1649953357</v>
       </c>
       <c r="R164" t="n">
-        <v>6937508.063391008</v>
+        <v>6937639.597708987</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -19102,10 +19086,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>103552063</v>
+        <v>103551371</v>
       </c>
       <c r="B165" t="n">
-        <v>89410</v>
+        <v>73693</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19118,35 +19102,35 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>368470.4374931786</v>
+        <v>368549.5342763296</v>
       </c>
       <c r="R165" t="n">
-        <v>6937589.716979248</v>
+        <v>6937508.063391008</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -19215,7 +19199,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>103552476</v>
+        <v>103552063</v>
       </c>
       <c r="B166" t="n">
         <v>89410</v>
@@ -19256,10 +19240,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>368302.2204442195</v>
+        <v>368470.4374931786</v>
       </c>
       <c r="R166" t="n">
-        <v>6937616.711276339</v>
+        <v>6937589.716979248</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -19328,10 +19312,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>103552718</v>
+        <v>103552476</v>
       </c>
       <c r="B167" t="n">
-        <v>78596</v>
+        <v>89410</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19340,25 +19324,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -19369,10 +19353,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>368261.4510728566</v>
+        <v>368302.2204442195</v>
       </c>
       <c r="R167" t="n">
-        <v>6937673.291957859</v>
+        <v>6937616.711276339</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -19441,10 +19425,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>103552013</v>
+        <v>103552718</v>
       </c>
       <c r="B168" t="n">
-        <v>77506</v>
+        <v>78596</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19453,25 +19437,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -19482,10 +19466,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>368492.8700843463</v>
+        <v>368261.4510728566</v>
       </c>
       <c r="R168" t="n">
-        <v>6937572.200403474</v>
+        <v>6937673.291957859</v>
       </c>
       <c r="S168" t="n">
         <v>25</v>
@@ -19554,10 +19538,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>103551293</v>
+        <v>103552013</v>
       </c>
       <c r="B169" t="n">
-        <v>81236</v>
+        <v>77506</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19570,35 +19554,35 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Fjällkällan, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>368543.9347116721</v>
+        <v>368492.8700843463</v>
       </c>
       <c r="R169" t="n">
-        <v>6937471.796150875</v>
+        <v>6937572.200403474</v>
       </c>
       <c r="S169" t="n">
         <v>25</v>
@@ -19667,10 +19651,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>103551403</v>
+        <v>103551293</v>
       </c>
       <c r="B170" t="n">
-        <v>90079</v>
+        <v>81236</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19679,25 +19663,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>67</v>
+        <v>1312</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19708,10 +19692,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>368506.5068285703</v>
+        <v>368543.9347116721</v>
       </c>
       <c r="R170" t="n">
-        <v>6937519.467622276</v>
+        <v>6937471.796150875</v>
       </c>
       <c r="S170" t="n">
         <v>25</v>
@@ -19780,10 +19764,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>104010922</v>
+        <v>103551403</v>
       </c>
       <c r="B171" t="n">
-        <v>89410</v>
+        <v>90079</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19792,39 +19776,39 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5432</v>
+        <v>67</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>368616.8656954028</v>
+        <v>368506.5068285703</v>
       </c>
       <c r="R171" t="n">
-        <v>6937549.737503948</v>
+        <v>6937519.467622276</v>
       </c>
       <c r="S171" t="n">
         <v>25</v>
@@ -19851,7 +19835,7 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="Z171" t="inlineStr">
@@ -19861,7 +19845,7 @@
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr">
@@ -19893,7 +19877,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>104010192</v>
+        <v>104010922</v>
       </c>
       <c r="B172" t="n">
         <v>89410</v>
@@ -19934,10 +19918,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>368610.6193882866</v>
+        <v>368616.8656954028</v>
       </c>
       <c r="R172" t="n">
-        <v>6937555.527341085</v>
+        <v>6937549.737503948</v>
       </c>
       <c r="S172" t="n">
         <v>25</v>
@@ -20006,7 +19990,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>108344786</v>
+        <v>104010192</v>
       </c>
       <c r="B173" t="n">
         <v>89410</v>
@@ -20043,14 +20027,14 @@
       <c r="K173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>368542.7501837978</v>
+        <v>368610.6193882866</v>
       </c>
       <c r="R173" t="n">
-        <v>6937476.923851865</v>
+        <v>6937555.527341085</v>
       </c>
       <c r="S173" t="n">
         <v>25</v>
@@ -20077,7 +20061,7 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
@@ -20087,7 +20071,7 @@
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr">
@@ -20119,10 +20103,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>108344789</v>
+        <v>108344786</v>
       </c>
       <c r="B174" t="n">
-        <v>77506</v>
+        <v>89410</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -20135,21 +20119,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -20232,10 +20216,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>108383136</v>
+        <v>108344789</v>
       </c>
       <c r="B175" t="n">
-        <v>89410</v>
+        <v>77506</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -20248,21 +20232,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -20273,10 +20257,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>368567.7566228579</v>
+        <v>368542.7501837978</v>
       </c>
       <c r="R175" t="n">
-        <v>6937489.3280955</v>
+        <v>6937476.923851865</v>
       </c>
       <c r="S175" t="n">
         <v>25</v>
@@ -20303,7 +20287,7 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="Z175" t="inlineStr">
@@ -20313,7 +20297,7 @@
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr">
@@ -20345,10 +20329,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>108350248</v>
+        <v>108383136</v>
       </c>
       <c r="B176" t="n">
-        <v>57657</v>
+        <v>89410</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -20357,44 +20341,39 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>368438</v>
+        <v>368567.7566228579</v>
       </c>
       <c r="R176" t="n">
-        <v>6937579</v>
+        <v>6937489.3280955</v>
       </c>
       <c r="S176" t="n">
         <v>25</v>
@@ -20421,12 +20400,22 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20453,7 +20442,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>103552077</v>
+        <v>108350248</v>
       </c>
       <c r="B177" t="n">
         <v>57657</v>
@@ -20488,16 +20477,21 @@
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>368471</v>
+        <v>368438</v>
       </c>
       <c r="R177" t="n">
-        <v>6937590</v>
+        <v>6937579</v>
       </c>
       <c r="S177" t="n">
         <v>25</v>
@@ -20524,12 +20518,12 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20556,10 +20550,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119763370</v>
+        <v>103552077</v>
       </c>
       <c r="B178" t="n">
-        <v>57431</v>
+        <v>57657</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20572,16 +20566,16 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>103031</v>
+        <v>103015</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -20589,24 +20583,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>368574</v>
+        <v>368471</v>
       </c>
       <c r="R178" t="n">
-        <v>6937554</v>
+        <v>6937590</v>
       </c>
       <c r="S178" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -20630,12 +20621,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20662,10 +20653,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119763325</v>
+        <v>119763370</v>
       </c>
       <c r="B179" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20674,20 +20665,20 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -20695,22 +20686,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>368590</v>
+        <v>368574</v>
       </c>
       <c r="R179" t="n">
-        <v>6937543</v>
+        <v>6937554</v>
       </c>
       <c r="S179" t="n">
         <v>15</v>
@@ -20737,12 +20727,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20769,10 +20759,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119765744</v>
+        <v>119763325</v>
       </c>
       <c r="B180" t="n">
-        <v>91272</v>
+        <v>57320</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20781,41 +20771,46 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>368547</v>
+        <v>368590</v>
       </c>
       <c r="R180" t="n">
-        <v>6937589</v>
+        <v>6937543</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -20871,10 +20866,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119763350</v>
+        <v>119765744</v>
       </c>
       <c r="B181" t="n">
-        <v>57320</v>
+        <v>91272</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20883,56 +20878,41 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>368574</v>
+        <v>368547</v>
       </c>
       <c r="R181" t="n">
-        <v>6937554</v>
+        <v>6937589</v>
       </c>
       <c r="S181" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -20956,12 +20936,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20988,10 +20968,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124618703</v>
+        <v>119763350</v>
       </c>
       <c r="B182" t="n">
-        <v>82737</v>
+        <v>57320</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21004,37 +20984,52 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368568</v>
+        <v>368574</v>
       </c>
       <c r="R182" t="n">
-        <v>6937489</v>
+        <v>6937554</v>
       </c>
       <c r="S182" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21058,12 +21053,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21090,10 +21085,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124630092</v>
+        <v>124618703</v>
       </c>
       <c r="B183" t="n">
-        <v>75025</v>
+        <v>82737</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21106,21 +21101,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -21130,13 +21125,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368556</v>
+        <v>368568</v>
       </c>
       <c r="R183" t="n">
-        <v>6937530</v>
+        <v>6937489</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21192,10 +21187,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124618931</v>
+        <v>124630092</v>
       </c>
       <c r="B184" t="n">
-        <v>80057</v>
+        <v>75025</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21204,25 +21199,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -21232,13 +21227,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368571</v>
+        <v>368556</v>
       </c>
       <c r="R184" t="n">
-        <v>6937516</v>
+        <v>6937530</v>
       </c>
       <c r="S184" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21294,10 +21289,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124630273</v>
+        <v>124618931</v>
       </c>
       <c r="B185" t="n">
-        <v>75025</v>
+        <v>80057</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21306,25 +21301,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21334,13 +21329,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368585</v>
+        <v>368571</v>
       </c>
       <c r="R185" t="n">
-        <v>6937532</v>
+        <v>6937516</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21396,7 +21391,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124630509</v>
+        <v>124630273</v>
       </c>
       <c r="B186" t="n">
         <v>75025</v>
@@ -21436,10 +21431,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>368603</v>
+        <v>368585</v>
       </c>
       <c r="R186" t="n">
-        <v>6937521</v>
+        <v>6937532</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21498,10 +21493,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124619608</v>
+        <v>124630509</v>
       </c>
       <c r="B187" t="n">
-        <v>91184</v>
+        <v>75025</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21514,37 +21509,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>368492</v>
+        <v>368603</v>
       </c>
       <c r="R187" t="n">
-        <v>6937572</v>
+        <v>6937521</v>
       </c>
       <c r="S187" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21600,7 +21595,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124620724</v>
+        <v>124619608</v>
       </c>
       <c r="B188" t="n">
         <v>91184</v>
@@ -21636,17 +21631,17 @@
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Fjällkällan, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368610</v>
+        <v>368492</v>
       </c>
       <c r="R188" t="n">
-        <v>6937558</v>
+        <v>6937572</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21702,10 +21697,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124629552</v>
+        <v>124620724</v>
       </c>
       <c r="B189" t="n">
-        <v>82737</v>
+        <v>91184</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21718,37 +21713,37 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368487</v>
+        <v>368610</v>
       </c>
       <c r="R189" t="n">
-        <v>6937548</v>
+        <v>6937558</v>
       </c>
       <c r="S189" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21801,6 +21796,108 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>124629552</v>
+      </c>
+      <c r="B190" t="n">
+        <v>82737</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>368487</v>
+      </c>
+      <c r="R190" t="n">
+        <v>6937548</v>
+      </c>
+      <c r="S190" t="n">
+        <v>25</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -18201,7 +18201,7 @@
         <v>125741282</v>
       </c>
       <c r="B157" t="n">
-        <v>91627</v>
+        <v>91634</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -18201,7 +18201,7 @@
         <v>125741282</v>
       </c>
       <c r="B157" t="n">
-        <v>91634</v>
+        <v>91638</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -18201,7 +18201,7 @@
         <v>125741282</v>
       </c>
       <c r="B157" t="n">
-        <v>91638</v>
+        <v>91642</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -18201,7 +18201,7 @@
         <v>125741282</v>
       </c>
       <c r="B157" t="n">
-        <v>91642</v>
+        <v>91644</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -18201,7 +18201,7 @@
         <v>125741282</v>
       </c>
       <c r="B157" t="n">
-        <v>91644</v>
+        <v>91646</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -18201,7 +18201,7 @@
         <v>125741282</v>
       </c>
       <c r="B157" t="n">
-        <v>91646</v>
+        <v>91648</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -18201,7 +18201,7 @@
         <v>125741282</v>
       </c>
       <c r="B157" t="n">
-        <v>91648</v>
+        <v>91652</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY190"/>
+  <dimension ref="A1:AY197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18295,54 +18295,48 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>103551484</v>
+        <v>126542633</v>
       </c>
       <c r="B158" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>368486.8215149617</v>
+        <v>368552</v>
       </c>
       <c r="R158" t="n">
-        <v>6937547.960590951</v>
+        <v>6937959</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18366,22 +18360,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18408,54 +18392,48 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>103552447</v>
+        <v>126552528</v>
       </c>
       <c r="B159" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75073</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1312</v>
+        <v>6486</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>368343.0240888702</v>
+        <v>368546</v>
       </c>
       <c r="R159" t="n">
-        <v>6937619.248962435</v>
+        <v>6938052</v>
       </c>
       <c r="S159" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18479,22 +18457,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18509,27 +18477,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>103551351</v>
+        <v>126552534</v>
       </c>
       <c r="B160" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91259</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18537,38 +18500,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Fjällkällan, Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>368544.7253621799</v>
+        <v>368546</v>
       </c>
       <c r="R160" t="n">
-        <v>6937480.078827508</v>
+        <v>6938052</v>
       </c>
       <c r="S160" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18592,22 +18554,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18622,27 +18574,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>103552443</v>
+        <v>126552539</v>
       </c>
       <c r="B161" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91263</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18668,20 +18615,19 @@
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>368343.0240888702</v>
+        <v>368546</v>
       </c>
       <c r="R161" t="n">
-        <v>6937619.248962435</v>
+        <v>6938052</v>
       </c>
       <c r="S161" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18705,22 +18651,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18735,27 +18671,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>103551383</v>
+        <v>126552526</v>
       </c>
       <c r="B162" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75080</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18763,38 +18694,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Fjällkällan, Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>368529.5480735453</v>
+        <v>368546</v>
       </c>
       <c r="R162" t="n">
-        <v>6937505.621947487</v>
+        <v>6938052</v>
       </c>
       <c r="S162" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18818,22 +18748,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18848,27 +18768,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>103551330</v>
+        <v>126552542</v>
       </c>
       <c r="B163" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75075</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18876,38 +18791,37 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Fjällkällan, Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>368540.902881454</v>
+        <v>368546</v>
       </c>
       <c r="R163" t="n">
-        <v>6937476.997030124</v>
+        <v>6938052</v>
       </c>
       <c r="S163" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18931,22 +18845,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18961,66 +18865,60 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>103552489</v>
+        <v>126552531</v>
       </c>
       <c r="B164" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91699</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>864</v>
+        <v>1209</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>368284.1649953357</v>
+        <v>368546</v>
       </c>
       <c r="R164" t="n">
-        <v>6937639.597708987</v>
+        <v>6938052</v>
       </c>
       <c r="S164" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -19044,22 +18942,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19074,19 +18962,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>103551371</v>
+        <v>103551484</v>
       </c>
       <c r="B165" t="n">
         <v>73693</v>
@@ -19123,14 +19011,14 @@
       <c r="K165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Fjällkällan, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>368549.5342763296</v>
+        <v>368486.8215149617</v>
       </c>
       <c r="R165" t="n">
-        <v>6937508.063391008</v>
+        <v>6937547.960590951</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -19199,10 +19087,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>103552063</v>
+        <v>103552447</v>
       </c>
       <c r="B166" t="n">
-        <v>89410</v>
+        <v>81236</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19215,21 +19103,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -19240,10 +19128,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>368470.4374931786</v>
+        <v>368343.0240888702</v>
       </c>
       <c r="R166" t="n">
-        <v>6937589.716979248</v>
+        <v>6937619.248962435</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -19312,10 +19200,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>103552476</v>
+        <v>103551351</v>
       </c>
       <c r="B167" t="n">
-        <v>89410</v>
+        <v>81236</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19328,35 +19216,35 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>368302.2204442195</v>
+        <v>368544.7253621799</v>
       </c>
       <c r="R167" t="n">
-        <v>6937616.711276339</v>
+        <v>6937480.078827508</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -19425,10 +19313,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>103552718</v>
+        <v>103552443</v>
       </c>
       <c r="B168" t="n">
-        <v>78596</v>
+        <v>89410</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19437,25 +19325,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -19466,10 +19354,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>368261.4510728566</v>
+        <v>368343.0240888702</v>
       </c>
       <c r="R168" t="n">
-        <v>6937673.291957859</v>
+        <v>6937619.248962435</v>
       </c>
       <c r="S168" t="n">
         <v>25</v>
@@ -19538,10 +19426,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>103552013</v>
+        <v>103551383</v>
       </c>
       <c r="B169" t="n">
-        <v>77506</v>
+        <v>73693</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19554,35 +19442,35 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>368492.8700843463</v>
+        <v>368529.5480735453</v>
       </c>
       <c r="R169" t="n">
-        <v>6937572.200403474</v>
+        <v>6937505.621947487</v>
       </c>
       <c r="S169" t="n">
         <v>25</v>
@@ -19651,10 +19539,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>103551293</v>
+        <v>103551330</v>
       </c>
       <c r="B170" t="n">
-        <v>81236</v>
+        <v>89410</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19667,21 +19555,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19692,10 +19580,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>368543.9347116721</v>
+        <v>368540.902881454</v>
       </c>
       <c r="R170" t="n">
-        <v>6937471.796150875</v>
+        <v>6937476.997030124</v>
       </c>
       <c r="S170" t="n">
         <v>25</v>
@@ -19764,10 +19652,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>103551403</v>
+        <v>103552489</v>
       </c>
       <c r="B171" t="n">
-        <v>90079</v>
+        <v>77588</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19776,39 +19664,39 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>67</v>
+        <v>864</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Fjällkällan, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>368506.5068285703</v>
+        <v>368284.1649953357</v>
       </c>
       <c r="R171" t="n">
-        <v>6937519.467622276</v>
+        <v>6937639.597708987</v>
       </c>
       <c r="S171" t="n">
         <v>25</v>
@@ -19877,10 +19765,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>104010922</v>
+        <v>103551371</v>
       </c>
       <c r="B172" t="n">
-        <v>89410</v>
+        <v>73693</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19893,35 +19781,35 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>368616.8656954028</v>
+        <v>368549.5342763296</v>
       </c>
       <c r="R172" t="n">
-        <v>6937549.737503948</v>
+        <v>6937508.063391008</v>
       </c>
       <c r="S172" t="n">
         <v>25</v>
@@ -19948,7 +19836,7 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr">
@@ -19958,7 +19846,7 @@
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr">
@@ -19990,7 +19878,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>104010192</v>
+        <v>103552063</v>
       </c>
       <c r="B173" t="n">
         <v>89410</v>
@@ -20031,10 +19919,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>368610.6193882866</v>
+        <v>368470.4374931786</v>
       </c>
       <c r="R173" t="n">
-        <v>6937555.527341085</v>
+        <v>6937589.716979248</v>
       </c>
       <c r="S173" t="n">
         <v>25</v>
@@ -20061,7 +19949,7 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
@@ -20071,7 +19959,7 @@
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr">
@@ -20103,7 +19991,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>108344786</v>
+        <v>103552476</v>
       </c>
       <c r="B174" t="n">
         <v>89410</v>
@@ -20140,14 +20028,14 @@
       <c r="K174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>368542.7501837978</v>
+        <v>368302.2204442195</v>
       </c>
       <c r="R174" t="n">
-        <v>6937476.923851865</v>
+        <v>6937616.711276339</v>
       </c>
       <c r="S174" t="n">
         <v>25</v>
@@ -20174,7 +20062,7 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="Z174" t="inlineStr">
@@ -20184,7 +20072,7 @@
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr">
@@ -20216,10 +20104,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>108344789</v>
+        <v>103552718</v>
       </c>
       <c r="B175" t="n">
-        <v>77506</v>
+        <v>78596</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -20228,39 +20116,39 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>368542.7501837978</v>
+        <v>368261.4510728566</v>
       </c>
       <c r="R175" t="n">
-        <v>6937476.923851865</v>
+        <v>6937673.291957859</v>
       </c>
       <c r="S175" t="n">
         <v>25</v>
@@ -20287,7 +20175,7 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="Z175" t="inlineStr">
@@ -20297,7 +20185,7 @@
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr">
@@ -20329,10 +20217,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>108383136</v>
+        <v>103552013</v>
       </c>
       <c r="B176" t="n">
-        <v>89410</v>
+        <v>77506</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -20345,35 +20233,35 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>368567.7566228579</v>
+        <v>368492.8700843463</v>
       </c>
       <c r="R176" t="n">
-        <v>6937489.3280955</v>
+        <v>6937572.200403474</v>
       </c>
       <c r="S176" t="n">
         <v>25</v>
@@ -20400,7 +20288,7 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="Z176" t="inlineStr">
@@ -20410,7 +20298,7 @@
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr">
@@ -20442,10 +20330,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>108350248</v>
+        <v>103551293</v>
       </c>
       <c r="B177" t="n">
-        <v>57657</v>
+        <v>81236</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20454,44 +20342,39 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Fjällkällan, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>368438</v>
+        <v>368543.9347116721</v>
       </c>
       <c r="R177" t="n">
-        <v>6937579</v>
+        <v>6937471.796150875</v>
       </c>
       <c r="S177" t="n">
         <v>25</v>
@@ -20518,12 +20401,22 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20550,10 +20443,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>103552077</v>
+        <v>103551403</v>
       </c>
       <c r="B178" t="n">
-        <v>57657</v>
+        <v>90079</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20562,39 +20455,39 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>103015</v>
+        <v>67</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>368471</v>
+        <v>368506.5068285703</v>
       </c>
       <c r="R178" t="n">
-        <v>6937590</v>
+        <v>6937519.467622276</v>
       </c>
       <c r="S178" t="n">
         <v>25</v>
@@ -20624,9 +20517,19 @@
           <t>2022-09-14</t>
         </is>
       </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20653,10 +20556,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119763370</v>
+        <v>104010922</v>
       </c>
       <c r="B179" t="n">
-        <v>57431</v>
+        <v>89410</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20665,45 +20568,42 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>368574</v>
+        <v>368616.8656954028</v>
       </c>
       <c r="R179" t="n">
-        <v>6937554</v>
+        <v>6937549.737503948</v>
       </c>
       <c r="S179" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20727,12 +20627,22 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2022-10-09</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2022-10-09</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20759,10 +20669,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119763325</v>
+        <v>104010192</v>
       </c>
       <c r="B180" t="n">
-        <v>57320</v>
+        <v>89410</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20775,42 +20685,38 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>368590</v>
+        <v>368610.6193882866</v>
       </c>
       <c r="R180" t="n">
-        <v>6937543</v>
+        <v>6937555.527341085</v>
       </c>
       <c r="S180" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -20834,12 +20740,22 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2022-10-09</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2022-10-09</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20866,10 +20782,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119765744</v>
+        <v>108344786</v>
       </c>
       <c r="B181" t="n">
-        <v>91272</v>
+        <v>89410</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20878,41 +20794,42 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>368547</v>
+        <v>368542.7501837978</v>
       </c>
       <c r="R181" t="n">
-        <v>6937589</v>
+        <v>6937476.923851865</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -20936,12 +20853,22 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20968,10 +20895,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119763350</v>
+        <v>108344789</v>
       </c>
       <c r="B182" t="n">
-        <v>57320</v>
+        <v>77506</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20984,52 +20911,38 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="K182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368574</v>
+        <v>368542.7501837978</v>
       </c>
       <c r="R182" t="n">
-        <v>6937554</v>
+        <v>6937476.923851865</v>
       </c>
       <c r="S182" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21053,12 +20966,22 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21085,10 +21008,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124618703</v>
+        <v>108383136</v>
       </c>
       <c r="B183" t="n">
-        <v>82737</v>
+        <v>89410</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21101,34 +21024,35 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368568</v>
+        <v>368567.7566228579</v>
       </c>
       <c r="R183" t="n">
-        <v>6937489</v>
+        <v>6937489.3280955</v>
       </c>
       <c r="S183" t="n">
         <v>25</v>
@@ -21155,12 +21079,22 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21187,10 +21121,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124630092</v>
+        <v>108350248</v>
       </c>
       <c r="B184" t="n">
-        <v>75025</v>
+        <v>57657</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21199,41 +21133,47 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368556</v>
+        <v>368438</v>
       </c>
       <c r="R184" t="n">
-        <v>6937530</v>
+        <v>6937579</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21257,12 +21197,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21289,10 +21229,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124618931</v>
+        <v>103552077</v>
       </c>
       <c r="B185" t="n">
-        <v>80057</v>
+        <v>57657</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21305,37 +21245,38 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6462</v>
+        <v>103015</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368571</v>
+        <v>368471</v>
       </c>
       <c r="R185" t="n">
-        <v>6937516</v>
+        <v>6937590</v>
       </c>
       <c r="S185" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21359,12 +21300,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21391,10 +21332,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124630273</v>
+        <v>119763370</v>
       </c>
       <c r="B186" t="n">
-        <v>75025</v>
+        <v>57431</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21403,41 +21344,45 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>368585</v>
+        <v>368574</v>
       </c>
       <c r="R186" t="n">
-        <v>6937532</v>
+        <v>6937554</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21461,12 +21406,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21493,10 +21438,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124630509</v>
+        <v>119763325</v>
       </c>
       <c r="B187" t="n">
-        <v>75025</v>
+        <v>57320</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21509,37 +21454,42 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>368603</v>
+        <v>368590</v>
       </c>
       <c r="R187" t="n">
-        <v>6937521</v>
+        <v>6937543</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21563,12 +21513,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21595,10 +21545,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124619608</v>
+        <v>119765744</v>
       </c>
       <c r="B188" t="n">
-        <v>91184</v>
+        <v>91272</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21607,25 +21557,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -21635,13 +21585,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368492</v>
+        <v>368547</v>
       </c>
       <c r="R188" t="n">
-        <v>6937572</v>
+        <v>6937589</v>
       </c>
       <c r="S188" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21665,12 +21615,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21697,10 +21647,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124620724</v>
+        <v>119763350</v>
       </c>
       <c r="B189" t="n">
-        <v>91184</v>
+        <v>57320</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21713,37 +21663,52 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Fjällkällan, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368610</v>
+        <v>368574</v>
       </c>
       <c r="R189" t="n">
-        <v>6937558</v>
+        <v>6937554</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21767,12 +21732,12 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21799,7 +21764,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124629552</v>
+        <v>124618703</v>
       </c>
       <c r="B190" t="n">
         <v>82737</v>
@@ -21835,14 +21800,14 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>368487</v>
+        <v>368568</v>
       </c>
       <c r="R190" t="n">
-        <v>6937548</v>
+        <v>6937489</v>
       </c>
       <c r="S190" t="n">
         <v>25</v>
@@ -21898,6 +21863,720 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>124630092</v>
+      </c>
+      <c r="B191" t="n">
+        <v>75025</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Storkroken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>368556</v>
+      </c>
+      <c r="R191" t="n">
+        <v>6937530</v>
+      </c>
+      <c r="S191" t="n">
+        <v>10</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>124618931</v>
+      </c>
+      <c r="B192" t="n">
+        <v>80057</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Storkroken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>368571</v>
+      </c>
+      <c r="R192" t="n">
+        <v>6937516</v>
+      </c>
+      <c r="S192" t="n">
+        <v>12</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>124630273</v>
+      </c>
+      <c r="B193" t="n">
+        <v>75025</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Storkroken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>368585</v>
+      </c>
+      <c r="R193" t="n">
+        <v>6937532</v>
+      </c>
+      <c r="S193" t="n">
+        <v>10</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>124630509</v>
+      </c>
+      <c r="B194" t="n">
+        <v>75025</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Storkroken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>368603</v>
+      </c>
+      <c r="R194" t="n">
+        <v>6937521</v>
+      </c>
+      <c r="S194" t="n">
+        <v>10</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>124619608</v>
+      </c>
+      <c r="B195" t="n">
+        <v>91184</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>368492</v>
+      </c>
+      <c r="R195" t="n">
+        <v>6937572</v>
+      </c>
+      <c r="S195" t="n">
+        <v>25</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>124620724</v>
+      </c>
+      <c r="B196" t="n">
+        <v>91184</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Fjällkällan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>368610</v>
+      </c>
+      <c r="R196" t="n">
+        <v>6937558</v>
+      </c>
+      <c r="S196" t="n">
+        <v>10</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>124629552</v>
+      </c>
+      <c r="B197" t="n">
+        <v>82737</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>368487</v>
+      </c>
+      <c r="R197" t="n">
+        <v>6937548</v>
+      </c>
+      <c r="S197" t="n">
+        <v>25</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AD197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -18392,32 +18392,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126552528</v>
+        <v>126552534</v>
       </c>
       <c r="B159" t="n">
-        <v>75073</v>
+        <v>91259</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6486</v>
+        <v>1204</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18489,32 +18489,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126552534</v>
+        <v>126552528</v>
       </c>
       <c r="B160" t="n">
-        <v>91259</v>
+        <v>75073</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1204</v>
+        <v>6486</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -18298,7 +18298,7 @@
         <v>126542633</v>
       </c>
       <c r="B158" t="n">
-        <v>78343</v>
+        <v>78374</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18392,32 +18392,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126552534</v>
+        <v>126552528</v>
       </c>
       <c r="B159" t="n">
-        <v>91259</v>
+        <v>75133</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1204</v>
+        <v>6486</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18489,32 +18489,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126552528</v>
+        <v>126552534</v>
       </c>
       <c r="B160" t="n">
-        <v>75073</v>
+        <v>91333</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6486</v>
+        <v>1204</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18589,7 +18589,7 @@
         <v>126552539</v>
       </c>
       <c r="B161" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>126552526</v>
       </c>
       <c r="B162" t="n">
-        <v>75080</v>
+        <v>75140</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>126552542</v>
       </c>
       <c r="B163" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>126552531</v>
       </c>
       <c r="B164" t="n">
-        <v>91699</v>
+        <v>91773</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>126720863</v>
       </c>
       <c r="B165" t="n">
-        <v>91699</v>
+        <v>91773</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>126720865</v>
       </c>
       <c r="B166" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>126720867</v>
       </c>
       <c r="B167" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>126720869</v>
       </c>
       <c r="B168" t="n">
-        <v>75080</v>
+        <v>75140</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>126720866</v>
       </c>
       <c r="B169" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>126720870</v>
       </c>
       <c r="B170" t="n">
-        <v>91259</v>
+        <v>91333</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>126720868</v>
       </c>
       <c r="B171" t="n">
-        <v>80975</v>
+        <v>81006</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>126720873</v>
       </c>
       <c r="B205" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>126720872</v>
       </c>
       <c r="B206" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>126720871</v>
       </c>
       <c r="B207" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -18392,32 +18392,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126552528</v>
+        <v>126552534</v>
       </c>
       <c r="B159" t="n">
-        <v>75133</v>
+        <v>91339</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6486</v>
+        <v>1204</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18489,32 +18489,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126552534</v>
+        <v>126552528</v>
       </c>
       <c r="B160" t="n">
-        <v>91333</v>
+        <v>75136</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1204</v>
+        <v>6486</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18589,7 +18589,7 @@
         <v>126552539</v>
       </c>
       <c r="B161" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>126552526</v>
       </c>
       <c r="B162" t="n">
-        <v>75140</v>
+        <v>75143</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>126552542</v>
       </c>
       <c r="B163" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>126552531</v>
       </c>
       <c r="B164" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>126720863</v>
       </c>
       <c r="B165" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>126720865</v>
       </c>
       <c r="B166" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>126720867</v>
       </c>
       <c r="B167" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>126720869</v>
       </c>
       <c r="B168" t="n">
-        <v>75140</v>
+        <v>75143</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>126720866</v>
       </c>
       <c r="B169" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>126720870</v>
       </c>
       <c r="B170" t="n">
-        <v>91333</v>
+        <v>91339</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>126720868</v>
       </c>
       <c r="B171" t="n">
-        <v>81006</v>
+        <v>81009</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>126720873</v>
       </c>
       <c r="B205" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>126720872</v>
       </c>
       <c r="B206" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>126720871</v>
       </c>
       <c r="B207" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -18977,7 +18977,7 @@
         <v>126720863</v>
       </c>
       <c r="B165" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>126720866</v>
       </c>
       <c r="B169" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>126720870</v>
       </c>
       <c r="B170" t="n">
-        <v>91339</v>
+        <v>91340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>126720872</v>
       </c>
       <c r="B206" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>126720871</v>
       </c>
       <c r="B207" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -18977,7 +18977,7 @@
         <v>126720863</v>
       </c>
       <c r="B165" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>126720865</v>
       </c>
       <c r="B166" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>126720867</v>
       </c>
       <c r="B167" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>126720869</v>
       </c>
       <c r="B168" t="n">
-        <v>75143</v>
+        <v>75147</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>126720866</v>
       </c>
       <c r="B169" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>126720870</v>
       </c>
       <c r="B170" t="n">
-        <v>91340</v>
+        <v>91344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>126720868</v>
       </c>
       <c r="B171" t="n">
-        <v>81009</v>
+        <v>81013</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>126720873</v>
       </c>
       <c r="B205" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>126720872</v>
       </c>
       <c r="B206" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>126720871</v>
       </c>
       <c r="B207" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -18392,32 +18392,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126552534</v>
+        <v>126552528</v>
       </c>
       <c r="B159" t="n">
-        <v>91339</v>
+        <v>75133</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1204</v>
+        <v>6486</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18489,32 +18489,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126552528</v>
+        <v>126552534</v>
       </c>
       <c r="B160" t="n">
-        <v>75136</v>
+        <v>91333</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6486</v>
+        <v>1204</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18589,7 +18589,7 @@
         <v>126552539</v>
       </c>
       <c r="B161" t="n">
-        <v>91343</v>
+        <v>91337</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>126552526</v>
       </c>
       <c r="B162" t="n">
-        <v>75143</v>
+        <v>75140</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>126552542</v>
       </c>
       <c r="B163" t="n">
-        <v>75138</v>
+        <v>75135</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>126552531</v>
       </c>
       <c r="B164" t="n">
-        <v>91779</v>
+        <v>91773</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>126720863</v>
       </c>
       <c r="B165" t="n">
-        <v>91784</v>
+        <v>91773</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>126720865</v>
       </c>
       <c r="B166" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>126720867</v>
       </c>
       <c r="B167" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>126720869</v>
       </c>
       <c r="B168" t="n">
-        <v>75147</v>
+        <v>75140</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>126720866</v>
       </c>
       <c r="B169" t="n">
-        <v>91330</v>
+        <v>91319</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>126720870</v>
       </c>
       <c r="B170" t="n">
-        <v>91344</v>
+        <v>91333</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>126720868</v>
       </c>
       <c r="B171" t="n">
-        <v>81013</v>
+        <v>81006</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>126720873</v>
       </c>
       <c r="B205" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>126720872</v>
       </c>
       <c r="B206" t="n">
-        <v>91348</v>
+        <v>91337</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>126720871</v>
       </c>
       <c r="B207" t="n">
-        <v>98468</v>
+        <v>98457</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -18392,32 +18392,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126552528</v>
+        <v>126552534</v>
       </c>
       <c r="B159" t="n">
-        <v>75133</v>
+        <v>91339</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6486</v>
+        <v>1204</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18489,32 +18489,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126552534</v>
+        <v>126552528</v>
       </c>
       <c r="B160" t="n">
-        <v>91333</v>
+        <v>75136</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1204</v>
+        <v>6486</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18589,7 +18589,7 @@
         <v>126552539</v>
       </c>
       <c r="B161" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>126552526</v>
       </c>
       <c r="B162" t="n">
-        <v>75140</v>
+        <v>75143</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>126552542</v>
       </c>
       <c r="B163" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>126552531</v>
       </c>
       <c r="B164" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>126720863</v>
       </c>
       <c r="B165" t="n">
-        <v>91773</v>
+        <v>91784</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>126720865</v>
       </c>
       <c r="B166" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>126720867</v>
       </c>
       <c r="B167" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>126720869</v>
       </c>
       <c r="B168" t="n">
-        <v>75140</v>
+        <v>75147</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>126720866</v>
       </c>
       <c r="B169" t="n">
-        <v>91319</v>
+        <v>91330</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>126720870</v>
       </c>
       <c r="B170" t="n">
-        <v>91333</v>
+        <v>91344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>126720868</v>
       </c>
       <c r="B171" t="n">
-        <v>81006</v>
+        <v>81013</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>126720873</v>
       </c>
       <c r="B205" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>126720872</v>
       </c>
       <c r="B206" t="n">
-        <v>91337</v>
+        <v>91348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>126720871</v>
       </c>
       <c r="B207" t="n">
-        <v>98457</v>
+        <v>98468</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY209"/>
+  <dimension ref="A1:AY214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21177,10 +21177,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>103552719</v>
+        <v>135168177</v>
       </c>
       <c r="B207" t="n">
-        <v>58057</v>
+        <v>58136</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21188,38 +21188,41 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>368262</v>
+        <v>368530</v>
       </c>
       <c r="R207" t="n">
-        <v>6937673</v>
+        <v>6937444</v>
       </c>
       <c r="S207" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -21243,12 +21246,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -21263,19 +21266,23 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Flor Rhebergen</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY207" t="inlineStr"/>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr">
+        <is>
+          <t>Bumblebee Bootcamp 2026</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119763370</v>
+        <v>103552719</v>
       </c>
       <c r="B208" t="n">
         <v>58057</v>
@@ -21303,24 +21310,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>368574</v>
+        <v>368262</v>
       </c>
       <c r="R208" t="n">
-        <v>6937554</v>
+        <v>6937673</v>
       </c>
       <c r="S208" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -21344,12 +21348,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -21376,45 +21380,49 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>126720871</v>
+        <v>119763370</v>
       </c>
       <c r="B209" t="n">
-        <v>99140</v>
+        <v>58057</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>221952</v>
+        <v>103031</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Hållan, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>368571</v>
+        <v>368574</v>
       </c>
       <c r="R209" t="n">
-        <v>6937498</v>
+        <v>6937554</v>
       </c>
       <c r="S209" t="n">
         <v>15</v>
@@ -21441,12 +21449,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -21461,15 +21469,532 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>135168175</v>
+      </c>
+      <c r="B210" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>368594</v>
+      </c>
+      <c r="R210" t="n">
+        <v>6937423</v>
+      </c>
+      <c r="S210" t="n">
+        <v>10</v>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT210" t="inlineStr"/>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr">
+        <is>
+          <t>Bumblebee Bootcamp 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>135168206</v>
+      </c>
+      <c r="B211" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>368593</v>
+      </c>
+      <c r="R211" t="n">
+        <v>6937424</v>
+      </c>
+      <c r="S211" t="n">
+        <v>10</v>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT211" t="inlineStr"/>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr">
+        <is>
+          <t>Bumblebee Bootcamp 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>135168176</v>
+      </c>
+      <c r="B212" t="n">
+        <v>29429</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>103271</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Tajgahumla</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Bombus cingulatus</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Wahlberg, 1855</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>368613</v>
+      </c>
+      <c r="R212" t="n">
+        <v>6937421</v>
+      </c>
+      <c r="S212" t="n">
+        <v>10</v>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT212" t="inlineStr"/>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr">
+        <is>
+          <t>Bumblebee Bootcamp 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>135168182</v>
+      </c>
+      <c r="B213" t="n">
+        <v>29442</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>103274</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Lapphumla</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Bombus lapponicus</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1793)</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Härjedalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>368241</v>
+      </c>
+      <c r="R213" t="n">
+        <v>6937615</v>
+      </c>
+      <c r="S213" t="n">
+        <v>10</v>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT213" t="inlineStr"/>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>Bumblebee Bootcamp 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>126720871</v>
+      </c>
+      <c r="B214" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Hållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>368571</v>
+      </c>
+      <c r="R214" t="n">
+        <v>6937498</v>
+      </c>
+      <c r="S214" t="n">
+        <v>15</v>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT214" t="inlineStr"/>
+      <c r="AW214" t="inlineStr">
+        <is>
           <t>Marika Sjödin</t>
         </is>
       </c>
-      <c r="AX209" t="inlineStr">
+      <c r="AX214" t="inlineStr">
         <is>
           <t>Marika Sjödin</t>
         </is>
       </c>
-      <c r="AY209" t="inlineStr"/>
+      <c r="AY214" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY214"/>
+  <dimension ref="A1:AY215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11838,49 +11838,51 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>103555116</v>
+        <v>135520659</v>
       </c>
       <c r="B114" t="n">
-        <v>92632</v>
+        <v>92332</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3298</v>
+        <v>1505</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>368538</v>
+        <v>368591</v>
       </c>
       <c r="R114" t="n">
-        <v>6938063</v>
+        <v>6937990</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11904,12 +11906,27 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Artbestämd genom mikroskopering.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11918,28 +11935,19 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
-      <c r="AW114" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>103583585</v>
+        <v>103555116</v>
       </c>
       <c r="B115" t="n">
-        <v>92333</v>
+        <v>92632</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11947,21 +11955,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4217</v>
+        <v>3298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11972,10 +11980,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>368761</v>
+        <v>368538</v>
       </c>
       <c r="R115" t="n">
-        <v>6938087</v>
+        <v>6938063</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12002,12 +12010,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12034,7 +12042,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125741282</v>
+        <v>103583585</v>
       </c>
       <c r="B116" t="n">
         <v>92333</v>
@@ -12063,19 +12071,20 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>368540</v>
+        <v>368761</v>
       </c>
       <c r="R116" t="n">
-        <v>6938067</v>
+        <v>6938087</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12099,12 +12108,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12131,10 +12140,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>103556309</v>
+        <v>125741282</v>
       </c>
       <c r="B117" t="n">
-        <v>91872</v>
+        <v>92333</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12142,38 +12151,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>368617</v>
+        <v>368540</v>
       </c>
       <c r="R117" t="n">
-        <v>6938128</v>
+        <v>6938067</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12197,12 +12205,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12229,32 +12237,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>103553361</v>
+        <v>103556309</v>
       </c>
       <c r="B118" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12265,10 +12273,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>368383</v>
+        <v>368617</v>
       </c>
       <c r="R118" t="n">
-        <v>6937824</v>
+        <v>6938128</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12327,7 +12335,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>103553533</v>
+        <v>103553361</v>
       </c>
       <c r="B119" t="n">
         <v>79327</v>
@@ -12363,10 +12371,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>368513</v>
+        <v>368383</v>
       </c>
       <c r="R119" t="n">
-        <v>6937902</v>
+        <v>6937824</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12425,7 +12433,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>103553933</v>
+        <v>103553533</v>
       </c>
       <c r="B120" t="n">
         <v>79327</v>
@@ -12461,10 +12469,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>368549</v>
+        <v>368513</v>
       </c>
       <c r="R120" t="n">
-        <v>6937916</v>
+        <v>6937902</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12523,7 +12531,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>103554851</v>
+        <v>103553933</v>
       </c>
       <c r="B121" t="n">
         <v>79327</v>
@@ -12559,10 +12567,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>368592</v>
+        <v>368549</v>
       </c>
       <c r="R121" t="n">
-        <v>6937993</v>
+        <v>6937916</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -12621,7 +12629,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>103555000</v>
+        <v>103554851</v>
       </c>
       <c r="B122" t="n">
         <v>79327</v>
@@ -12657,10 +12665,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>368545</v>
+        <v>368592</v>
       </c>
       <c r="R122" t="n">
-        <v>6938024</v>
+        <v>6937993</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -12719,7 +12727,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>103555045</v>
+        <v>103555000</v>
       </c>
       <c r="B123" t="n">
         <v>79327</v>
@@ -12755,10 +12763,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>368521</v>
+        <v>368545</v>
       </c>
       <c r="R123" t="n">
-        <v>6938032</v>
+        <v>6938024</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -12817,7 +12825,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>103555142</v>
+        <v>103555045</v>
       </c>
       <c r="B124" t="n">
         <v>79327</v>
@@ -12853,10 +12861,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>368557</v>
+        <v>368521</v>
       </c>
       <c r="R124" t="n">
-        <v>6938080</v>
+        <v>6938032</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -12915,7 +12923,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>103555921</v>
+        <v>103555142</v>
       </c>
       <c r="B125" t="n">
         <v>79327</v>
@@ -12951,10 +12959,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>368559</v>
+        <v>368557</v>
       </c>
       <c r="R125" t="n">
-        <v>6938109</v>
+        <v>6938080</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13013,7 +13021,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>103556320</v>
+        <v>103555921</v>
       </c>
       <c r="B126" t="n">
         <v>79327</v>
@@ -13049,10 +13057,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>368617</v>
+        <v>368559</v>
       </c>
       <c r="R126" t="n">
-        <v>6938128</v>
+        <v>6938109</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13111,7 +13119,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>103556583</v>
+        <v>103556320</v>
       </c>
       <c r="B127" t="n">
         <v>79327</v>
@@ -13147,10 +13155,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>368783</v>
+        <v>368617</v>
       </c>
       <c r="R127" t="n">
-        <v>6938163</v>
+        <v>6938128</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -13209,7 +13217,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>103583508</v>
+        <v>103556583</v>
       </c>
       <c r="B128" t="n">
         <v>79327</v>
@@ -13245,10 +13253,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>368832</v>
+        <v>368783</v>
       </c>
       <c r="R128" t="n">
-        <v>6938160</v>
+        <v>6938163</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -13275,12 +13283,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13307,7 +13315,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>103583588</v>
+        <v>103583508</v>
       </c>
       <c r="B129" t="n">
         <v>79327</v>
@@ -13343,10 +13351,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>368761</v>
+        <v>368832</v>
       </c>
       <c r="R129" t="n">
-        <v>6938087</v>
+        <v>6938160</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -13405,7 +13413,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>104009257</v>
+        <v>103583588</v>
       </c>
       <c r="B130" t="n">
         <v>79327</v>
@@ -13441,10 +13449,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>368595</v>
+        <v>368761</v>
       </c>
       <c r="R130" t="n">
-        <v>6938137</v>
+        <v>6938087</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -13471,12 +13479,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13503,7 +13511,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>104009459</v>
+        <v>104009257</v>
       </c>
       <c r="B131" t="n">
         <v>79327</v>
@@ -13539,10 +13547,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>368543</v>
+        <v>368595</v>
       </c>
       <c r="R131" t="n">
-        <v>6938089</v>
+        <v>6938137</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -13601,7 +13609,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>104009610</v>
+        <v>104009459</v>
       </c>
       <c r="B132" t="n">
         <v>79327</v>
@@ -13637,10 +13645,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>368585</v>
+        <v>368543</v>
       </c>
       <c r="R132" t="n">
-        <v>6937954</v>
+        <v>6938089</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -13699,7 +13707,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>107032434</v>
+        <v>104009610</v>
       </c>
       <c r="B133" t="n">
         <v>79327</v>
@@ -13731,14 +13739,14 @@
       <c r="K133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>368805</v>
+        <v>368585</v>
       </c>
       <c r="R133" t="n">
-        <v>6938127</v>
+        <v>6937954</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -13765,12 +13773,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13797,7 +13805,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>107032475</v>
+        <v>107032434</v>
       </c>
       <c r="B134" t="n">
         <v>79327</v>
@@ -13833,10 +13841,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>368831</v>
+        <v>368805</v>
       </c>
       <c r="R134" t="n">
-        <v>6938144</v>
+        <v>6938127</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -13895,7 +13903,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>108034481</v>
+        <v>107032475</v>
       </c>
       <c r="B135" t="n">
         <v>79327</v>
@@ -13923,11 +13931,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -13935,10 +13939,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>368691</v>
+        <v>368831</v>
       </c>
       <c r="R135" t="n">
-        <v>6938070</v>
+        <v>6938144</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -13965,22 +13969,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2023-04-11</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2023-04-11</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -13995,19 +13989,19 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>108343324</v>
+        <v>108034481</v>
       </c>
       <c r="B136" t="n">
         <v>79327</v>
@@ -14035,7 +14029,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -14043,10 +14041,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>368624</v>
+        <v>368691</v>
       </c>
       <c r="R136" t="n">
-        <v>6938137</v>
+        <v>6938070</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -14073,12 +14071,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2023-04-11</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2023-04-11</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14093,19 +14101,19 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>108344291</v>
+        <v>108343324</v>
       </c>
       <c r="B137" t="n">
         <v>79327</v>
@@ -14141,10 +14149,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>368734</v>
+        <v>368624</v>
       </c>
       <c r="R137" t="n">
-        <v>6937927</v>
+        <v>6938137</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -14203,7 +14211,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126720865</v>
+        <v>108344291</v>
       </c>
       <c r="B138" t="n">
         <v>79327</v>
@@ -14232,19 +14240,20 @@
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hållan, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>368554</v>
+        <v>368734</v>
       </c>
       <c r="R138" t="n">
-        <v>6937954</v>
+        <v>6937927</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14268,12 +14277,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14288,19 +14297,19 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126720867</v>
+        <v>126720865</v>
       </c>
       <c r="B139" t="n">
         <v>79327</v>
@@ -14335,10 +14344,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>368564</v>
+        <v>368554</v>
       </c>
       <c r="R139" t="n">
-        <v>6937945</v>
+        <v>6937954</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -14397,49 +14406,48 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>103553543</v>
+        <v>126720867</v>
       </c>
       <c r="B140" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Hållan, Hjd</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>368513</v>
+        <v>368564</v>
       </c>
       <c r="R140" t="n">
-        <v>6937902</v>
+        <v>6937945</v>
       </c>
       <c r="S140" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14463,12 +14471,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14483,19 +14491,19 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>103554121</v>
+        <v>103553543</v>
       </c>
       <c r="B141" t="n">
         <v>83307</v>
@@ -14531,10 +14539,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>368562</v>
+        <v>368513</v>
       </c>
       <c r="R141" t="n">
-        <v>6937928</v>
+        <v>6937902</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -14593,7 +14601,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>103554871</v>
+        <v>103554121</v>
       </c>
       <c r="B142" t="n">
         <v>83307</v>
@@ -14629,10 +14637,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>368574</v>
+        <v>368562</v>
       </c>
       <c r="R142" t="n">
-        <v>6938020</v>
+        <v>6937928</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -14691,7 +14699,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>103554998</v>
+        <v>103554871</v>
       </c>
       <c r="B143" t="n">
         <v>83307</v>
@@ -14727,10 +14735,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>368545</v>
+        <v>368574</v>
       </c>
       <c r="R143" t="n">
-        <v>6938024</v>
+        <v>6938020</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -14789,7 +14797,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>103555154</v>
+        <v>103554998</v>
       </c>
       <c r="B144" t="n">
         <v>83307</v>
@@ -14825,10 +14833,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>368557</v>
+        <v>368545</v>
       </c>
       <c r="R144" t="n">
-        <v>6938080</v>
+        <v>6938024</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -14887,7 +14895,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>103583530</v>
+        <v>103555154</v>
       </c>
       <c r="B145" t="n">
         <v>83307</v>
@@ -14923,10 +14931,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>368831</v>
+        <v>368557</v>
       </c>
       <c r="R145" t="n">
-        <v>6938129</v>
+        <v>6938080</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -14953,12 +14961,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -14985,7 +14993,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>104006712</v>
+        <v>103583530</v>
       </c>
       <c r="B146" t="n">
         <v>83307</v>
@@ -15021,10 +15029,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>368628</v>
+        <v>368831</v>
       </c>
       <c r="R146" t="n">
-        <v>6937972</v>
+        <v>6938129</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -15051,12 +15059,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15083,7 +15091,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>104009232</v>
+        <v>104006712</v>
       </c>
       <c r="B147" t="n">
         <v>83307</v>
@@ -15119,10 +15127,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>368595</v>
+        <v>368628</v>
       </c>
       <c r="R147" t="n">
-        <v>6938137</v>
+        <v>6937972</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -15181,7 +15189,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>107032413</v>
+        <v>104009232</v>
       </c>
       <c r="B148" t="n">
         <v>83307</v>
@@ -15213,14 +15221,14 @@
       <c r="K148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>368790</v>
+        <v>368595</v>
       </c>
       <c r="R148" t="n">
-        <v>6938110</v>
+        <v>6938137</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -15247,12 +15255,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15279,7 +15287,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>108035481</v>
+        <v>107032413</v>
       </c>
       <c r="B149" t="n">
         <v>83307</v>
@@ -15315,10 +15323,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>368592</v>
+        <v>368790</v>
       </c>
       <c r="R149" t="n">
-        <v>6938058</v>
+        <v>6938110</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -15345,22 +15353,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2023-04-11</t>
-        </is>
-      </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>15:27</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2023-04-11</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>15:27</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15375,19 +15373,19 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126552542</v>
+        <v>108035481</v>
       </c>
       <c r="B150" t="n">
         <v>83307</v>
@@ -15416,19 +15414,20 @@
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>368546</v>
+        <v>368592</v>
       </c>
       <c r="R150" t="n">
-        <v>6938052</v>
+        <v>6938058</v>
       </c>
       <c r="S150" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15452,12 +15451,22 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2023-04-11</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2023-04-11</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15472,44 +15481,44 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126552528</v>
+        <v>126552542</v>
       </c>
       <c r="B151" t="n">
-        <v>83305</v>
+        <v>83307</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6486</v>
+        <v>6440</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15581,54 +15590,48 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>103556085</v>
+        <v>126552528</v>
       </c>
       <c r="B152" t="n">
-        <v>57950</v>
+        <v>83305</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100049</v>
+        <v>6486</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>368630</v>
+        <v>368546</v>
       </c>
       <c r="R152" t="n">
-        <v>6938124</v>
+        <v>6938052</v>
       </c>
       <c r="S152" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -15652,12 +15655,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15672,19 +15675,19 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>103556383</v>
+        <v>103556085</v>
       </c>
       <c r="B153" t="n">
         <v>57950</v>
@@ -15716,7 +15719,7 @@
       <c r="K153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -15725,10 +15728,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>368649</v>
+        <v>368630</v>
       </c>
       <c r="R153" t="n">
-        <v>6938126</v>
+        <v>6938124</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -15787,27 +15790,27 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>103556071</v>
+        <v>103556383</v>
       </c>
       <c r="B154" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -15819,7 +15822,7 @@
       <c r="K154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -15828,10 +15831,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>368630</v>
+        <v>368649</v>
       </c>
       <c r="R154" t="n">
-        <v>6938124</v>
+        <v>6938126</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -15890,7 +15893,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>103556476</v>
+        <v>103556071</v>
       </c>
       <c r="B155" t="n">
         <v>57953</v>
@@ -15931,10 +15934,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>368736</v>
+        <v>368630</v>
       </c>
       <c r="R155" t="n">
-        <v>6938144</v>
+        <v>6938124</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -15993,7 +15996,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>103557552</v>
+        <v>103556476</v>
       </c>
       <c r="B156" t="n">
         <v>57953</v>
@@ -16034,10 +16037,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>368776</v>
+        <v>368736</v>
       </c>
       <c r="R156" t="n">
-        <v>6938142</v>
+        <v>6938144</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -16096,7 +16099,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>103566805</v>
+        <v>103557552</v>
       </c>
       <c r="B157" t="n">
         <v>57953</v>
@@ -16124,24 +16127,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -16150,10 +16140,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>368676</v>
+        <v>368776</v>
       </c>
       <c r="R157" t="n">
-        <v>6938161</v>
+        <v>6938142</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -16180,12 +16170,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16212,7 +16202,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>103583511</v>
+        <v>103566805</v>
       </c>
       <c r="B158" t="n">
         <v>57953</v>
@@ -16240,11 +16230,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -16253,10 +16256,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>368821</v>
+        <v>368676</v>
       </c>
       <c r="R158" t="n">
-        <v>6938156</v>
+        <v>6938161</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -16283,12 +16286,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16315,7 +16318,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>103583654</v>
+        <v>103583511</v>
       </c>
       <c r="B159" t="n">
         <v>57953</v>
@@ -16356,10 +16359,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>368739</v>
+        <v>368821</v>
       </c>
       <c r="R159" t="n">
-        <v>6938142</v>
+        <v>6938156</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -16418,7 +16421,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>103583677</v>
+        <v>103583654</v>
       </c>
       <c r="B160" t="n">
         <v>57953</v>
@@ -16450,7 +16453,7 @@
       <c r="K160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -16459,10 +16462,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>368791</v>
+        <v>368739</v>
       </c>
       <c r="R160" t="n">
-        <v>6938146</v>
+        <v>6938142</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -16521,7 +16524,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>104009214</v>
+        <v>103583677</v>
       </c>
       <c r="B161" t="n">
         <v>57953</v>
@@ -16553,7 +16556,7 @@
       <c r="K161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -16562,10 +16565,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>368595</v>
+        <v>368791</v>
       </c>
       <c r="R161" t="n">
-        <v>6938137</v>
+        <v>6938146</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -16592,12 +16595,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16624,7 +16627,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>104009269</v>
+        <v>104009214</v>
       </c>
       <c r="B162" t="n">
         <v>57953</v>
@@ -16665,10 +16668,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>368576</v>
+        <v>368595</v>
       </c>
       <c r="R162" t="n">
-        <v>6938147</v>
+        <v>6938137</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -16727,7 +16730,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>106461233</v>
+        <v>104009269</v>
       </c>
       <c r="B163" t="n">
         <v>57953</v>
@@ -16757,26 +16760,24 @@
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Backvallen, Hållan, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>368783</v>
+        <v>368576</v>
       </c>
       <c r="R163" t="n">
-        <v>6938045</v>
+        <v>6938147</v>
       </c>
       <c r="S163" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -16800,17 +16801,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2023-02-05</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2023-02-05</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -16837,7 +16833,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>107032448</v>
+        <v>106461233</v>
       </c>
       <c r="B164" t="n">
         <v>57953</v>
@@ -16867,24 +16863,26 @@
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Backvallen, Hållan, Hjd</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>368823</v>
+        <v>368783</v>
       </c>
       <c r="R164" t="n">
-        <v>6938137</v>
+        <v>6938045</v>
       </c>
       <c r="S164" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -16908,12 +16906,17 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2023-02-05</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2023-02-05</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -16940,7 +16943,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>108344232</v>
+        <v>107032448</v>
       </c>
       <c r="B165" t="n">
         <v>57953</v>
@@ -16972,7 +16975,7 @@
       <c r="K165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -16981,10 +16984,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>368771</v>
+        <v>368823</v>
       </c>
       <c r="R165" t="n">
-        <v>6938052</v>
+        <v>6938137</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -17011,12 +17014,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17043,7 +17046,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>108379916</v>
+        <v>108344232</v>
       </c>
       <c r="B166" t="n">
         <v>57953</v>
@@ -17075,7 +17078,7 @@
       <c r="K166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -17084,10 +17087,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>368769</v>
+        <v>368771</v>
       </c>
       <c r="R166" t="n">
-        <v>6938109</v>
+        <v>6938052</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -17114,12 +17117,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17146,7 +17149,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>108380113</v>
+        <v>108379916</v>
       </c>
       <c r="B167" t="n">
         <v>57953</v>
@@ -17178,7 +17181,7 @@
       <c r="K167" t="inlineStr"/>
       <c r="M167" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -17187,10 +17190,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>368781</v>
+        <v>368769</v>
       </c>
       <c r="R167" t="n">
-        <v>6938123</v>
+        <v>6938109</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -17249,7 +17252,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>108380229</v>
+        <v>108380113</v>
       </c>
       <c r="B168" t="n">
         <v>57953</v>
@@ -17290,10 +17293,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>368775</v>
+        <v>368781</v>
       </c>
       <c r="R168" t="n">
-        <v>6938136</v>
+        <v>6938123</v>
       </c>
       <c r="S168" t="n">
         <v>25</v>
@@ -17352,7 +17355,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>124622472</v>
+        <v>108380229</v>
       </c>
       <c r="B169" t="n">
         <v>57953</v>
@@ -17381,6 +17384,7 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
       <c r="M169" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -17392,13 +17396,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>368802</v>
+        <v>368775</v>
       </c>
       <c r="R169" t="n">
-        <v>6938048</v>
+        <v>6938136</v>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -17422,12 +17426,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17454,7 +17458,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>124622769</v>
+        <v>124622472</v>
       </c>
       <c r="B170" t="n">
         <v>57953</v>
@@ -17485,19 +17489,19 @@
       <c r="I170" t="inlineStr"/>
       <c r="M170" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>368769</v>
+        <v>368802</v>
       </c>
       <c r="R170" t="n">
-        <v>6938164</v>
+        <v>6938048</v>
       </c>
       <c r="S170" t="n">
         <v>15</v>
@@ -17556,7 +17560,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>124627400</v>
+        <v>124622769</v>
       </c>
       <c r="B171" t="n">
         <v>57953</v>
@@ -17587,19 +17591,19 @@
       <c r="I171" t="inlineStr"/>
       <c r="M171" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>368733</v>
+        <v>368769</v>
       </c>
       <c r="R171" t="n">
-        <v>6938143</v>
+        <v>6938164</v>
       </c>
       <c r="S171" t="n">
         <v>15</v>
@@ -17658,7 +17662,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>124627817</v>
+        <v>124627400</v>
       </c>
       <c r="B172" t="n">
         <v>57953</v>
@@ -17698,13 +17702,13 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>368651</v>
+        <v>368733</v>
       </c>
       <c r="R172" t="n">
-        <v>6938152</v>
+        <v>6938143</v>
       </c>
       <c r="S172" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -17760,7 +17764,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125696719</v>
+        <v>124627817</v>
       </c>
       <c r="B173" t="n">
         <v>57953</v>
@@ -17789,27 +17793,24 @@
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>368750</v>
+        <v>368651</v>
       </c>
       <c r="R173" t="n">
-        <v>6937906</v>
+        <v>6938152</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -17833,27 +17834,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Ringhack i granar, fanns äldre i närheten också</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -17868,66 +17854,68 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Martin Blomberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Martin Blomberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>108093599</v>
+        <v>125696719</v>
       </c>
       <c r="B174" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>368632</v>
+        <v>368750</v>
       </c>
       <c r="R174" t="n">
-        <v>6938091</v>
+        <v>6937906</v>
       </c>
       <c r="S174" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -17951,22 +17939,27 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2023-04-13</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2023-04-13</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Ringhack i granar, fanns äldre i närheten också</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -17981,58 +17974,63 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Martin Blomberg</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Martin Blomberg</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>103583633</v>
+        <v>108093599</v>
       </c>
       <c r="B175" t="n">
-        <v>58114</v>
+        <v>57141</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>368744</v>
+        <v>368632</v>
       </c>
       <c r="R175" t="n">
-        <v>6938086</v>
+        <v>6938091</v>
       </c>
       <c r="S175" t="n">
         <v>25</v>
@@ -18059,12 +18057,22 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2023-04-13</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2023-04-13</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18079,22 +18087,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>103555271</v>
+        <v>103583633</v>
       </c>
       <c r="B176" t="n">
-        <v>58057</v>
+        <v>58114</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18102,21 +18110,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18127,10 +18135,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>368561</v>
+        <v>368744</v>
       </c>
       <c r="R176" t="n">
-        <v>6938105</v>
+        <v>6938086</v>
       </c>
       <c r="S176" t="n">
         <v>25</v>
@@ -18157,12 +18165,12 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18189,7 +18197,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>103555834</v>
+        <v>103555271</v>
       </c>
       <c r="B177" t="n">
         <v>58057</v>
@@ -18217,31 +18225,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>368552</v>
+        <v>368561</v>
       </c>
       <c r="R177" t="n">
-        <v>6938098</v>
+        <v>6938105</v>
       </c>
       <c r="S177" t="n">
         <v>25</v>
@@ -18300,7 +18295,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>103556323</v>
+        <v>103555834</v>
       </c>
       <c r="B178" t="n">
         <v>58057</v>
@@ -18328,18 +18323,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>368617</v>
+        <v>368552</v>
       </c>
       <c r="R178" t="n">
-        <v>6938128</v>
+        <v>6938098</v>
       </c>
       <c r="S178" t="n">
         <v>25</v>
@@ -18398,7 +18406,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>108379968</v>
+        <v>103556323</v>
       </c>
       <c r="B179" t="n">
         <v>58057</v>
@@ -18426,29 +18434,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>368776</v>
+        <v>368617</v>
       </c>
       <c r="R179" t="n">
-        <v>6938113</v>
+        <v>6938128</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>
@@ -18475,12 +18472,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -18507,27 +18504,27 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>103553784</v>
+        <v>108379968</v>
       </c>
       <c r="B180" t="n">
-        <v>5199</v>
+        <v>58057</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>105930</v>
+        <v>103031</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -18535,23 +18532,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>368513</v>
+        <v>368776</v>
       </c>
       <c r="R180" t="n">
-        <v>6937902</v>
+        <v>6938113</v>
       </c>
       <c r="S180" t="n">
         <v>25</v>
@@ -18578,12 +18581,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -18610,7 +18613,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>103554466</v>
+        <v>103553784</v>
       </c>
       <c r="B181" t="n">
         <v>5199</v>
@@ -18651,10 +18654,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>368592</v>
+        <v>368513</v>
       </c>
       <c r="R181" t="n">
-        <v>6937951</v>
+        <v>6937902</v>
       </c>
       <c r="S181" t="n">
         <v>25</v>
@@ -18713,48 +18716,54 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>126720868</v>
+        <v>103554466</v>
       </c>
       <c r="B182" t="n">
-        <v>81332</v>
+        <v>5199</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>229436</v>
+        <v>105930</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Hållan, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368572</v>
+        <v>368592</v>
       </c>
       <c r="R182" t="n">
-        <v>6937942</v>
+        <v>6937951</v>
       </c>
       <c r="S182" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -18778,12 +18787,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -18798,61 +18807,60 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>103551403</v>
+        <v>126720868</v>
       </c>
       <c r="B183" t="n">
-        <v>92637</v>
+        <v>81332</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>67</v>
+        <v>229436</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Fjällkällan, Härjedalen, Hjd</t>
+          <t>Hållan, Hjd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368506</v>
+        <v>368572</v>
       </c>
       <c r="R183" t="n">
-        <v>6937519</v>
+        <v>6937942</v>
       </c>
       <c r="S183" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -18876,12 +18884,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -18896,58 +18904,58 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>103552489</v>
+        <v>103551403</v>
       </c>
       <c r="B184" t="n">
-        <v>79406</v>
+        <v>92637</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>864</v>
+        <v>67</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368284</v>
+        <v>368506</v>
       </c>
       <c r="R184" t="n">
-        <v>6937639</v>
+        <v>6937519</v>
       </c>
       <c r="S184" t="n">
         <v>25</v>
@@ -19006,10 +19014,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>103551293</v>
+        <v>103552489</v>
       </c>
       <c r="B185" t="n">
-        <v>83173</v>
+        <v>79406</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19017,35 +19025,35 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Fjällkällan, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368544</v>
+        <v>368284</v>
       </c>
       <c r="R185" t="n">
-        <v>6937472</v>
+        <v>6937639</v>
       </c>
       <c r="S185" t="n">
         <v>25</v>
@@ -19104,7 +19112,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>103551351</v>
+        <v>103551293</v>
       </c>
       <c r="B186" t="n">
         <v>83173</v>
@@ -19140,10 +19148,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>368545</v>
+        <v>368544</v>
       </c>
       <c r="R186" t="n">
-        <v>6937480</v>
+        <v>6937472</v>
       </c>
       <c r="S186" t="n">
         <v>25</v>
@@ -19202,7 +19210,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>103552447</v>
+        <v>103551351</v>
       </c>
       <c r="B187" t="n">
         <v>83173</v>
@@ -19234,14 +19242,14 @@
       <c r="K187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>368344</v>
+        <v>368545</v>
       </c>
       <c r="R187" t="n">
-        <v>6937620</v>
+        <v>6937480</v>
       </c>
       <c r="S187" t="n">
         <v>25</v>
@@ -19300,7 +19308,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124618703</v>
+        <v>103552447</v>
       </c>
       <c r="B188" t="n">
         <v>83173</v>
@@ -19329,16 +19337,17 @@
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368568</v>
+        <v>368344</v>
       </c>
       <c r="R188" t="n">
-        <v>6937489</v>
+        <v>6937620</v>
       </c>
       <c r="S188" t="n">
         <v>25</v>
@@ -19365,12 +19374,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -19397,7 +19406,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124629552</v>
+        <v>124618703</v>
       </c>
       <c r="B189" t="n">
         <v>83173</v>
@@ -19428,14 +19437,14 @@
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368487</v>
+        <v>368568</v>
       </c>
       <c r="R189" t="n">
-        <v>6937548</v>
+        <v>6937489</v>
       </c>
       <c r="S189" t="n">
         <v>25</v>
@@ -19494,32 +19503,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119765744</v>
+        <v>124629552</v>
       </c>
       <c r="B190" t="n">
-        <v>92632</v>
+        <v>83173</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19529,13 +19538,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>368547</v>
+        <v>368487</v>
       </c>
       <c r="R190" t="n">
-        <v>6937589</v>
+        <v>6937548</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -19559,12 +19568,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -19591,49 +19600,48 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>103552013</v>
+        <v>119765744</v>
       </c>
       <c r="B191" t="n">
-        <v>79327</v>
+        <v>92632</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>368492</v>
+        <v>368547</v>
       </c>
       <c r="R191" t="n">
-        <v>6937572</v>
+        <v>6937589</v>
       </c>
       <c r="S191" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -19657,12 +19665,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -19689,7 +19697,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>104011170</v>
+        <v>103552013</v>
       </c>
       <c r="B192" t="n">
         <v>79327</v>
@@ -19721,14 +19729,14 @@
       <c r="K192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Backvallen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>368637</v>
+        <v>368492</v>
       </c>
       <c r="R192" t="n">
-        <v>6937460</v>
+        <v>6937572</v>
       </c>
       <c r="S192" t="n">
         <v>25</v>
@@ -19755,12 +19763,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -19787,7 +19795,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>108344789</v>
+        <v>104011170</v>
       </c>
       <c r="B193" t="n">
         <v>79327</v>
@@ -19819,14 +19827,14 @@
       <c r="K193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Backvallen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>368543</v>
+        <v>368637</v>
       </c>
       <c r="R193" t="n">
-        <v>6937476</v>
+        <v>6937460</v>
       </c>
       <c r="S193" t="n">
         <v>25</v>
@@ -19853,12 +19861,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -19885,7 +19893,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126720873</v>
+        <v>108344789</v>
       </c>
       <c r="B194" t="n">
         <v>79327</v>
@@ -19914,19 +19922,20 @@
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Hållan, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>368580</v>
+        <v>368543</v>
       </c>
       <c r="R194" t="n">
-        <v>6937494</v>
+        <v>6937476</v>
       </c>
       <c r="S194" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -19950,12 +19959,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -19970,61 +19979,60 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>103551371</v>
+        <v>126720873</v>
       </c>
       <c r="B195" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Fjällkällan, Härjedalen, Hjd</t>
+          <t>Hållan, Hjd</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>368550</v>
+        <v>368580</v>
       </c>
       <c r="R195" t="n">
-        <v>6937508</v>
+        <v>6937494</v>
       </c>
       <c r="S195" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -20048,12 +20056,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20068,19 +20076,19 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>103551383</v>
+        <v>103551371</v>
       </c>
       <c r="B196" t="n">
         <v>83307</v>
@@ -20116,10 +20124,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>368529</v>
+        <v>368550</v>
       </c>
       <c r="R196" t="n">
-        <v>6937505</v>
+        <v>6937508</v>
       </c>
       <c r="S196" t="n">
         <v>25</v>
@@ -20178,7 +20186,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>103551484</v>
+        <v>103551383</v>
       </c>
       <c r="B197" t="n">
         <v>83307</v>
@@ -20210,14 +20218,14 @@
       <c r="K197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>368487</v>
+        <v>368529</v>
       </c>
       <c r="R197" t="n">
-        <v>6937548</v>
+        <v>6937505</v>
       </c>
       <c r="S197" t="n">
         <v>25</v>
@@ -20276,7 +20284,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124630092</v>
+        <v>103551484</v>
       </c>
       <c r="B198" t="n">
         <v>83307</v>
@@ -20305,19 +20313,20 @@
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>368556</v>
+        <v>368487</v>
       </c>
       <c r="R198" t="n">
-        <v>6937530</v>
+        <v>6937548</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -20341,12 +20350,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -20373,7 +20382,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124630273</v>
+        <v>124630092</v>
       </c>
       <c r="B199" t="n">
         <v>83307</v>
@@ -20408,10 +20417,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>368585</v>
+        <v>368556</v>
       </c>
       <c r="R199" t="n">
-        <v>6937532</v>
+        <v>6937530</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20470,7 +20479,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124630509</v>
+        <v>124630273</v>
       </c>
       <c r="B200" t="n">
         <v>83307</v>
@@ -20505,10 +20514,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>368603</v>
+        <v>368585</v>
       </c>
       <c r="R200" t="n">
-        <v>6937521</v>
+        <v>6937532</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20567,49 +20576,48 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>103552718</v>
+        <v>124630509</v>
       </c>
       <c r="B201" t="n">
-        <v>80461</v>
+        <v>83307</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>368262</v>
+        <v>368603</v>
       </c>
       <c r="R201" t="n">
-        <v>6937673</v>
+        <v>6937521</v>
       </c>
       <c r="S201" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -20633,12 +20641,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -20665,7 +20673,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124618931</v>
+        <v>103552718</v>
       </c>
       <c r="B202" t="n">
         <v>80461</v>
@@ -20694,19 +20702,20 @@
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>368571</v>
+        <v>368262</v>
       </c>
       <c r="R202" t="n">
-        <v>6937516</v>
+        <v>6937673</v>
       </c>
       <c r="S202" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -20730,12 +20739,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -20762,53 +20771,48 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119763325</v>
+        <v>124618931</v>
       </c>
       <c r="B203" t="n">
-        <v>57953</v>
+        <v>80461</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>368590</v>
+        <v>368571</v>
       </c>
       <c r="R203" t="n">
-        <v>6937543</v>
+        <v>6937516</v>
       </c>
       <c r="S203" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -20832,12 +20836,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -20864,7 +20868,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119763342</v>
+        <v>119763325</v>
       </c>
       <c r="B204" t="n">
         <v>57953</v>
@@ -20893,31 +20897,21 @@
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>368574</v>
+        <v>368590</v>
       </c>
       <c r="R204" t="n">
-        <v>6937554</v>
+        <v>6937543</v>
       </c>
       <c r="S204" t="n">
         <v>15</v>
@@ -20944,12 +20938,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -20976,27 +20970,27 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>103552077</v>
+        <v>119763342</v>
       </c>
       <c r="B205" t="n">
-        <v>58327</v>
+        <v>57953</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -21005,20 +20999,34 @@
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>368471</v>
+        <v>368574</v>
       </c>
       <c r="R205" t="n">
-        <v>6937590</v>
+        <v>6937554</v>
       </c>
       <c r="S205" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -21042,12 +21050,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -21074,7 +21082,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>108350248</v>
+        <v>103552077</v>
       </c>
       <c r="B206" t="n">
         <v>58327</v>
@@ -21104,21 +21112,16 @@
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>368438</v>
+        <v>368471</v>
       </c>
       <c r="R206" t="n">
-        <v>6937579</v>
+        <v>6937590</v>
       </c>
       <c r="S206" t="n">
         <v>25</v>
@@ -21145,12 +21148,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -21177,52 +21180,54 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>135168177</v>
+        <v>108350248</v>
       </c>
       <c r="B207" t="n">
-        <v>58136</v>
+        <v>58327</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>368530</v>
+        <v>368438</v>
       </c>
       <c r="R207" t="n">
-        <v>6937444</v>
+        <v>6937579</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -21246,12 +21251,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -21266,26 +21271,22 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Flor Rhebergen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Flor Rhebergen</t>
-        </is>
-      </c>
-      <c r="AY207" t="inlineStr">
-        <is>
-          <t>Bumblebee Bootcamp 2026</t>
-        </is>
-      </c>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>103552719</v>
+        <v>135168177</v>
       </c>
       <c r="B208" t="n">
-        <v>58057</v>
+        <v>58136</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21293,38 +21294,41 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>368262</v>
+        <v>368530</v>
       </c>
       <c r="R208" t="n">
-        <v>6937673</v>
+        <v>6937444</v>
       </c>
       <c r="S208" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -21348,12 +21352,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -21368,19 +21372,23 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Flor Rhebergen</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY208" t="inlineStr"/>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr">
+        <is>
+          <t>Bumblebee Bootcamp 2026</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119763370</v>
+        <v>103552719</v>
       </c>
       <c r="B209" t="n">
         <v>58057</v>
@@ -21408,24 +21416,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>368574</v>
+        <v>368262</v>
       </c>
       <c r="R209" t="n">
-        <v>6937554</v>
+        <v>6937673</v>
       </c>
       <c r="S209" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -21449,12 +21454,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -21481,10 +21486,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>135168175</v>
+        <v>119763370</v>
       </c>
       <c r="B210" t="n">
-        <v>58079</v>
+        <v>58057</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21520,13 +21525,13 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>368594</v>
+        <v>368574</v>
       </c>
       <c r="R210" t="n">
-        <v>6937423</v>
+        <v>6937554</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -21550,12 +21555,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -21570,23 +21575,19 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Flor Rhebergen</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Flor Rhebergen</t>
-        </is>
-      </c>
-      <c r="AY210" t="inlineStr">
-        <is>
-          <t>Bumblebee Bootcamp 2026</t>
-        </is>
-      </c>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>135168206</v>
+        <v>135168175</v>
       </c>
       <c r="B211" t="n">
         <v>58079</v>
@@ -21616,7 +21617,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -21625,10 +21626,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>368593</v>
+        <v>368594</v>
       </c>
       <c r="R211" t="n">
-        <v>6937424</v>
+        <v>6937423</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21691,10 +21692,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>135168176</v>
+        <v>135168206</v>
       </c>
       <c r="B212" t="n">
-        <v>29429</v>
+        <v>58079</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21702,26 +21703,26 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>103271</v>
+        <v>103031</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Tajgahumla</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Bombus cingulatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Wahlberg, 1855</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -21730,10 +21731,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>368613</v>
+        <v>368593</v>
       </c>
       <c r="R212" t="n">
-        <v>6937421</v>
+        <v>6937424</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21796,10 +21797,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>135168182</v>
+        <v>135168176</v>
       </c>
       <c r="B213" t="n">
-        <v>29442</v>
+        <v>29429</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21807,21 +21808,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>103274</v>
+        <v>103271</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Lapphumla</t>
+          <t>Tajgahumla</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Bombus lapponicus</t>
+          <t>Bombus cingulatus</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fabricius, 1793)</t>
+          <t>Wahlberg, 1855</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -21835,10 +21836,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>368241</v>
+        <v>368613</v>
       </c>
       <c r="R213" t="n">
-        <v>6937615</v>
+        <v>6937421</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21901,48 +21902,52 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>126720871</v>
+        <v>135168182</v>
       </c>
       <c r="B214" t="n">
-        <v>99140</v>
+        <v>29442</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>221952</v>
+        <v>103274</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lapphumla</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bombus lapponicus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr"/>
+          <t>(Fabricius, 1793)</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Hållan, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>368571</v>
+        <v>368241</v>
       </c>
       <c r="R214" t="n">
-        <v>6937498</v>
+        <v>6937615</v>
       </c>
       <c r="S214" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -21966,12 +21971,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -21986,15 +21991,116 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr">
+        <is>
+          <t>Bumblebee Bootcamp 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>126720871</v>
+      </c>
+      <c r="B215" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Hållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>368571</v>
+      </c>
+      <c r="R215" t="n">
+        <v>6937498</v>
+      </c>
+      <c r="S215" t="n">
+        <v>15</v>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT215" t="inlineStr"/>
+      <c r="AW215" t="inlineStr">
+        <is>
           <t>Marika Sjödin</t>
         </is>
       </c>
-      <c r="AX214" t="inlineStr">
+      <c r="AX215" t="inlineStr">
         <is>
           <t>Marika Sjödin</t>
         </is>
       </c>
-      <c r="AY214" t="inlineStr"/>
+      <c r="AY215" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -11940,6 +11940,16 @@
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Linn Helker Nygren</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Linn Helker Nygren</t>
+        </is>
+      </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY215"/>
+  <dimension ref="A1:AZ215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96509426</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556914</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557130</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103586164</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556865</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557097</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557237</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1455,6 +1495,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124623267</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108007472</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1665,6 +1715,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108007510</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1773,6 +1828,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108092261</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1871,6 +1931,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568328</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1969,6 +2034,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556868</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2067,6 +2137,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557510</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2165,6 +2240,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566573</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2263,6 +2343,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568390</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2361,6 +2446,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103586094</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2473,6 +2563,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108006998</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2571,6 +2666,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108343818</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2669,6 +2769,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568309</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2767,6 +2872,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96509295</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2865,6 +2975,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556926</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2963,6 +3078,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557041</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3061,6 +3181,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557088</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3159,6 +3284,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557102</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3257,6 +3387,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557178</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3355,6 +3490,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568335</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3453,6 +3593,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583698</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3551,6 +3696,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103586224</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3649,6 +3799,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103586253</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3747,6 +3902,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103586285</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3845,6 +4005,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103586333</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3943,6 +4108,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108006908</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4055,6 +4225,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108006982</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4167,6 +4342,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108007126</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4265,6 +4445,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108343819</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4363,6 +4548,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96509223</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4461,6 +4651,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96509350</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4559,6 +4754,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96509434</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4657,6 +4857,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96509542</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4755,6 +4960,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556918</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4853,6 +5063,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557176</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4951,6 +5166,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557512</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5049,6 +5269,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103568537</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5147,6 +5372,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103586093</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5245,6 +5475,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103586146</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5343,6 +5578,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103586213</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5441,6 +5681,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103586321</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5549,6 +5794,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108007108</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5652,6 +5902,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556615</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5755,6 +6010,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556794</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5867,6 +6127,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557035</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5970,6 +6235,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557084</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6073,6 +6343,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557270</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6176,6 +6451,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566533</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6279,6 +6559,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103586350</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6382,6 +6667,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103586371</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6495,6 +6785,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108007420</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6598,6 +6893,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108343699</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6700,6 +7000,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124622908</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6802,6 +7107,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124623242</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6904,6 +7214,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124623496</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7006,6 +7321,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124626137</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7109,6 +7429,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103586089</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7207,6 +7532,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556881</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7305,6 +7635,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103553987</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7407,6 +7742,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556378</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7505,6 +7845,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104006722</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7603,6 +7948,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032342</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7700,6 +8050,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126542633</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7797,6 +8152,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124627082</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7895,6 +8255,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555098</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7993,6 +8358,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556406</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8090,6 +8460,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124628575</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8188,6 +8563,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103554977</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8286,6 +8666,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103628105</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8394,6 +8779,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108093914</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8492,6 +8882,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108382638</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8589,6 +8984,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126720866</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8687,6 +9087,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103554756</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8785,6 +9190,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555184</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8883,6 +9293,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555838</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8980,6 +9395,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126552534</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9077,6 +9497,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126720870</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9175,6 +9600,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103554798</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9273,6 +9703,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103554878</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9371,6 +9806,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556289</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9469,6 +9909,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566975</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9567,6 +10012,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103628163</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9675,6 +10125,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108093901</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9773,6 +10228,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108382618</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9870,6 +10330,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124627646</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9967,6 +10432,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124628163</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10064,6 +10534,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126552531</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10161,6 +10636,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126720863</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10259,6 +10739,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103553407</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10357,6 +10842,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555002</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10455,6 +10945,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555048</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10553,6 +11048,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555189</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10651,6 +11151,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555970</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10749,6 +11254,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556411</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10847,6 +11357,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566943</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10945,6 +11460,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583568</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11043,6 +11563,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104006728</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11141,6 +11666,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104009978</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11239,6 +11769,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032267</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11337,6 +11872,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032384</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11445,6 +11985,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108092290</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11543,6 +12088,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103554349</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11641,6 +12191,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104006719</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11738,6 +12293,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126552526</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11835,6 +12395,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126720869</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11951,6 +12516,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135520659</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12049,6 +12619,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555116</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12147,6 +12722,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583585</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12244,6 +12824,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125741282</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12342,6 +12927,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556309</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12440,6 +13030,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103553361</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12538,6 +13133,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103553533</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12636,6 +13236,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103553933</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12734,6 +13339,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103554851</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12832,6 +13442,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555000</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12930,6 +13545,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555045</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13028,6 +13648,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555142</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13126,6 +13751,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555921</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13224,6 +13854,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556320</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13322,6 +13957,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556583</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13420,6 +14060,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583508</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13518,6 +14163,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583588</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13616,6 +14266,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104009257</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13714,6 +14369,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104009459</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13812,6 +14472,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104009610</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13910,6 +14575,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032434</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14008,6 +14678,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032475</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14120,6 +14795,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108034481</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14218,6 +14898,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108343324</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14316,6 +15001,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108344291</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14413,6 +15103,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126720865</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14510,6 +15205,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126720867</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14608,6 +15308,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103553543</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14706,6 +15411,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103554121</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14804,6 +15514,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103554871</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14902,6 +15617,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103554998</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15000,6 +15720,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555154</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15098,6 +15823,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583530</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15196,6 +15926,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104006712</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15294,6 +16029,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104009232</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15392,6 +16132,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032413</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15500,6 +16245,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108035481</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15597,6 +16347,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126552542</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15694,6 +16449,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126552528</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15797,6 +16557,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556085</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15900,6 +16665,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556383</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16003,6 +16773,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556071</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16106,6 +16881,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556476</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16209,6 +16989,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103557552</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16325,6 +17110,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103566805</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16428,6 +17218,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583511</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16531,6 +17326,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583654</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16634,6 +17434,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583677</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16737,6 +17542,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104009214</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16840,6 +17650,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104009269</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16950,6 +17765,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106461233</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17053,6 +17873,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107032448</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17156,6 +17981,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108344232</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17259,6 +18089,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108379916</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17362,6 +18197,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108380113</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17465,6 +18305,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108380229</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17567,6 +18412,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124622472</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17669,6 +18519,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124622769</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17771,6 +18626,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124627400</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17873,6 +18733,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124627817</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17993,6 +18858,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125696719</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18106,6 +18976,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108093599</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18204,6 +19079,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103583633</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18302,6 +19182,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555271</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18413,6 +19298,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555834</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18511,6 +19401,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556323</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18620,6 +19515,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108379968</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18723,6 +19623,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103553784</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18826,6 +19731,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103554466</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18923,6 +19833,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126720868</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19021,6 +19936,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103551403</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19119,6 +20039,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103552489</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19217,6 +20142,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103551293</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19315,6 +20245,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103551351</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19413,6 +20348,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103552447</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19510,6 +20450,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124618703</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19607,6 +20552,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124629552</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19704,6 +20654,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119765744</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19802,6 +20757,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103552013</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19900,6 +20860,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104011170</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19998,6 +20963,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108344789</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20095,6 +21065,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126720873</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20193,6 +21168,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103551371</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20291,6 +21271,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103551383</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20389,6 +21374,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103551484</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20486,6 +21476,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124630092</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20583,6 +21578,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124630273</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20680,6 +21680,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124630509</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20778,6 +21783,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103552718</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20875,6 +21885,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124618931</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -20977,6 +21992,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119763325</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21089,6 +22109,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119763342</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21187,6 +22212,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103552077</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21290,6 +22320,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108350248</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21395,6 +22430,11 @@
           <t>Bumblebee Bootcamp 2026</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135168177</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21493,6 +22533,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103552719</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21594,6 +22639,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119763370</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21699,6 +22749,11 @@
           <t>Bumblebee Bootcamp 2026</t>
         </is>
       </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135168175</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21804,6 +22859,11 @@
           <t>Bumblebee Bootcamp 2026</t>
         </is>
       </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135168206</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21909,6 +22969,11 @@
           <t>Bumblebee Bootcamp 2026</t>
         </is>
       </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135168176</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -22014,6 +23079,11 @@
           <t>Bumblebee Bootcamp 2026</t>
         </is>
       </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135168182</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -22111,8 +23181,229 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126720871</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -12406,7 +12406,7 @@
         <v>135520659</v>
       </c>
       <c r="B114" t="n">
-        <v>92332</v>
+        <v>92374</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>135168177</v>
       </c>
       <c r="B208" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>135168175</v>
       </c>
       <c r="B211" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>135168206</v>
       </c>
       <c r="B212" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>135168176</v>
       </c>
       <c r="B213" t="n">
-        <v>29429</v>
+        <v>29432</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>135168182</v>
       </c>
       <c r="B214" t="n">
-        <v>29442</v>
+        <v>29445</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -12406,7 +12406,7 @@
         <v>135520659</v>
       </c>
       <c r="B114" t="n">
-        <v>92374</v>
+        <v>92401</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ209"/>
+  <dimension ref="A1:AZ210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12403,49 +12403,51 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>103555116</v>
+        <v>135520659</v>
       </c>
       <c r="B114" t="n">
-        <v>92632</v>
+        <v>92406</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3298</v>
+        <v>1505</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>368538</v>
+        <v>368591</v>
       </c>
       <c r="R114" t="n">
-        <v>6938063</v>
+        <v>6937990</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12469,12 +12471,27 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Artbestämd genom mikroskopering.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12483,33 +12500,34 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Linn Helker Nygren</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Linn Helker Nygren</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103555116</t>
+          <t>https://artportalen.se/Sighting/135520659</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>103583585</v>
+        <v>103555116</v>
       </c>
       <c r="B115" t="n">
-        <v>92333</v>
+        <v>92632</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12517,21 +12535,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4217</v>
+        <v>3298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12542,10 +12560,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>368761</v>
+        <v>368538</v>
       </c>
       <c r="R115" t="n">
-        <v>6938087</v>
+        <v>6938063</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12572,12 +12590,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12603,13 +12621,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103583585</t>
+          <t>https://artportalen.se/Sighting/103555116</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125741282</v>
+        <v>103583585</v>
       </c>
       <c r="B116" t="n">
         <v>92333</v>
@@ -12638,19 +12656,20 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>368540</v>
+        <v>368761</v>
       </c>
       <c r="R116" t="n">
-        <v>6938067</v>
+        <v>6938087</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12674,12 +12693,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12705,16 +12724,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125741282</t>
+          <t>https://artportalen.se/Sighting/103583585</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>103556309</v>
+        <v>125741282</v>
       </c>
       <c r="B117" t="n">
-        <v>91872</v>
+        <v>92333</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12722,38 +12741,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>368617</v>
+        <v>368540</v>
       </c>
       <c r="R117" t="n">
-        <v>6938128</v>
+        <v>6938067</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12777,12 +12795,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12808,38 +12826,38 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103556309</t>
+          <t>https://artportalen.se/Sighting/125741282</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>103553361</v>
+        <v>103556309</v>
       </c>
       <c r="B118" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12850,10 +12868,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>368383</v>
+        <v>368617</v>
       </c>
       <c r="R118" t="n">
-        <v>6937824</v>
+        <v>6938128</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12911,13 +12929,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103553361</t>
+          <t>https://artportalen.se/Sighting/103556309</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>103553533</v>
+        <v>103553361</v>
       </c>
       <c r="B119" t="n">
         <v>79327</v>
@@ -12953,10 +12971,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>368513</v>
+        <v>368383</v>
       </c>
       <c r="R119" t="n">
-        <v>6937902</v>
+        <v>6937824</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13014,13 +13032,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103553533</t>
+          <t>https://artportalen.se/Sighting/103553361</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>103553933</v>
+        <v>103553533</v>
       </c>
       <c r="B120" t="n">
         <v>79327</v>
@@ -13056,10 +13074,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>368549</v>
+        <v>368513</v>
       </c>
       <c r="R120" t="n">
-        <v>6937916</v>
+        <v>6937902</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13117,13 +13135,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103553933</t>
+          <t>https://artportalen.se/Sighting/103553533</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>103554851</v>
+        <v>103553933</v>
       </c>
       <c r="B121" t="n">
         <v>79327</v>
@@ -13159,10 +13177,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>368592</v>
+        <v>368549</v>
       </c>
       <c r="R121" t="n">
-        <v>6937993</v>
+        <v>6937916</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13220,13 +13238,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103554851</t>
+          <t>https://artportalen.se/Sighting/103553933</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>103555000</v>
+        <v>103554851</v>
       </c>
       <c r="B122" t="n">
         <v>79327</v>
@@ -13262,10 +13280,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>368545</v>
+        <v>368592</v>
       </c>
       <c r="R122" t="n">
-        <v>6938024</v>
+        <v>6937993</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13323,13 +13341,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103555000</t>
+          <t>https://artportalen.se/Sighting/103554851</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>103555045</v>
+        <v>103555000</v>
       </c>
       <c r="B123" t="n">
         <v>79327</v>
@@ -13365,10 +13383,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>368521</v>
+        <v>368545</v>
       </c>
       <c r="R123" t="n">
-        <v>6938032</v>
+        <v>6938024</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13426,13 +13444,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103555045</t>
+          <t>https://artportalen.se/Sighting/103555000</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>103555142</v>
+        <v>103555045</v>
       </c>
       <c r="B124" t="n">
         <v>79327</v>
@@ -13468,10 +13486,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>368557</v>
+        <v>368521</v>
       </c>
       <c r="R124" t="n">
-        <v>6938080</v>
+        <v>6938032</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13529,13 +13547,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103555142</t>
+          <t>https://artportalen.se/Sighting/103555045</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>103555921</v>
+        <v>103555142</v>
       </c>
       <c r="B125" t="n">
         <v>79327</v>
@@ -13571,10 +13589,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>368559</v>
+        <v>368557</v>
       </c>
       <c r="R125" t="n">
-        <v>6938109</v>
+        <v>6938080</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13632,13 +13650,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103555921</t>
+          <t>https://artportalen.se/Sighting/103555142</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>103556320</v>
+        <v>103555921</v>
       </c>
       <c r="B126" t="n">
         <v>79327</v>
@@ -13674,10 +13692,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>368617</v>
+        <v>368559</v>
       </c>
       <c r="R126" t="n">
-        <v>6938128</v>
+        <v>6938109</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13735,13 +13753,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103556320</t>
+          <t>https://artportalen.se/Sighting/103555921</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>103556583</v>
+        <v>103556320</v>
       </c>
       <c r="B127" t="n">
         <v>79327</v>
@@ -13777,10 +13795,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>368783</v>
+        <v>368617</v>
       </c>
       <c r="R127" t="n">
-        <v>6938163</v>
+        <v>6938128</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -13838,13 +13856,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103556583</t>
+          <t>https://artportalen.se/Sighting/103556320</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>103583508</v>
+        <v>103556583</v>
       </c>
       <c r="B128" t="n">
         <v>79327</v>
@@ -13880,10 +13898,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>368832</v>
+        <v>368783</v>
       </c>
       <c r="R128" t="n">
-        <v>6938160</v>
+        <v>6938163</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -13910,12 +13928,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13941,13 +13959,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103583508</t>
+          <t>https://artportalen.se/Sighting/103556583</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>103583588</v>
+        <v>103583508</v>
       </c>
       <c r="B129" t="n">
         <v>79327</v>
@@ -13983,10 +14001,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>368761</v>
+        <v>368832</v>
       </c>
       <c r="R129" t="n">
-        <v>6938087</v>
+        <v>6938160</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14044,13 +14062,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103583588</t>
+          <t>https://artportalen.se/Sighting/103583508</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>104009257</v>
+        <v>103583588</v>
       </c>
       <c r="B130" t="n">
         <v>79327</v>
@@ -14086,10 +14104,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>368595</v>
+        <v>368761</v>
       </c>
       <c r="R130" t="n">
-        <v>6938137</v>
+        <v>6938087</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14116,12 +14134,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14147,13 +14165,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104009257</t>
+          <t>https://artportalen.se/Sighting/103583588</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>104009459</v>
+        <v>104009257</v>
       </c>
       <c r="B131" t="n">
         <v>79327</v>
@@ -14189,10 +14207,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>368543</v>
+        <v>368595</v>
       </c>
       <c r="R131" t="n">
-        <v>6938089</v>
+        <v>6938137</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14250,13 +14268,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104009459</t>
+          <t>https://artportalen.se/Sighting/104009257</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>104009610</v>
+        <v>104009459</v>
       </c>
       <c r="B132" t="n">
         <v>79327</v>
@@ -14292,10 +14310,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>368585</v>
+        <v>368543</v>
       </c>
       <c r="R132" t="n">
-        <v>6937954</v>
+        <v>6938089</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14353,13 +14371,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104009610</t>
+          <t>https://artportalen.se/Sighting/104009459</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>107032434</v>
+        <v>104009610</v>
       </c>
       <c r="B133" t="n">
         <v>79327</v>
@@ -14391,14 +14409,14 @@
       <c r="K133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>368805</v>
+        <v>368585</v>
       </c>
       <c r="R133" t="n">
-        <v>6938127</v>
+        <v>6937954</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14425,12 +14443,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14456,13 +14474,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107032434</t>
+          <t>https://artportalen.se/Sighting/104009610</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>107032475</v>
+        <v>107032434</v>
       </c>
       <c r="B134" t="n">
         <v>79327</v>
@@ -14498,10 +14516,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>368831</v>
+        <v>368805</v>
       </c>
       <c r="R134" t="n">
-        <v>6938144</v>
+        <v>6938127</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14559,13 +14577,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107032475</t>
+          <t>https://artportalen.se/Sighting/107032434</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>108034481</v>
+        <v>107032475</v>
       </c>
       <c r="B135" t="n">
         <v>79327</v>
@@ -14593,11 +14611,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14605,10 +14619,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>368691</v>
+        <v>368831</v>
       </c>
       <c r="R135" t="n">
-        <v>6938070</v>
+        <v>6938144</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14635,22 +14649,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2023-04-11</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2023-04-11</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14665,24 +14669,24 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108034481</t>
+          <t>https://artportalen.se/Sighting/107032475</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>108343324</v>
+        <v>108034481</v>
       </c>
       <c r="B136" t="n">
         <v>79327</v>
@@ -14710,7 +14714,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -14718,10 +14726,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>368624</v>
+        <v>368691</v>
       </c>
       <c r="R136" t="n">
-        <v>6938137</v>
+        <v>6938070</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -14748,12 +14756,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2023-04-11</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2023-04-11</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14768,24 +14786,24 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108343324</t>
+          <t>https://artportalen.se/Sighting/108034481</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>108344291</v>
+        <v>108343324</v>
       </c>
       <c r="B137" t="n">
         <v>79327</v>
@@ -14821,10 +14839,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>368734</v>
+        <v>368624</v>
       </c>
       <c r="R137" t="n">
-        <v>6937927</v>
+        <v>6938137</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -14882,13 +14900,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108344291</t>
+          <t>https://artportalen.se/Sighting/108343324</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126720865</v>
+        <v>108344291</v>
       </c>
       <c r="B138" t="n">
         <v>79327</v>
@@ -14917,19 +14935,20 @@
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hållan, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>368554</v>
+        <v>368734</v>
       </c>
       <c r="R138" t="n">
-        <v>6937954</v>
+        <v>6937927</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14953,12 +14972,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14973,24 +14992,24 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126720865</t>
+          <t>https://artportalen.se/Sighting/108344291</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126720867</v>
+        <v>126720865</v>
       </c>
       <c r="B139" t="n">
         <v>79327</v>
@@ -15025,10 +15044,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>368564</v>
+        <v>368554</v>
       </c>
       <c r="R139" t="n">
-        <v>6937945</v>
+        <v>6937954</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15086,55 +15105,54 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126720867</t>
+          <t>https://artportalen.se/Sighting/126720865</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>103553543</v>
+        <v>126720867</v>
       </c>
       <c r="B140" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Hållan, Hjd</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>368513</v>
+        <v>368564</v>
       </c>
       <c r="R140" t="n">
-        <v>6937902</v>
+        <v>6937945</v>
       </c>
       <c r="S140" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15158,12 +15176,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15178,24 +15196,24 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103553543</t>
+          <t>https://artportalen.se/Sighting/126720867</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>103554121</v>
+        <v>103553543</v>
       </c>
       <c r="B141" t="n">
         <v>83307</v>
@@ -15231,10 +15249,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>368562</v>
+        <v>368513</v>
       </c>
       <c r="R141" t="n">
-        <v>6937928</v>
+        <v>6937902</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15292,13 +15310,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103554121</t>
+          <t>https://artportalen.se/Sighting/103553543</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>103554871</v>
+        <v>103554121</v>
       </c>
       <c r="B142" t="n">
         <v>83307</v>
@@ -15334,10 +15352,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>368574</v>
+        <v>368562</v>
       </c>
       <c r="R142" t="n">
-        <v>6938020</v>
+        <v>6937928</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15395,13 +15413,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103554871</t>
+          <t>https://artportalen.se/Sighting/103554121</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>103554998</v>
+        <v>103554871</v>
       </c>
       <c r="B143" t="n">
         <v>83307</v>
@@ -15437,10 +15455,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>368545</v>
+        <v>368574</v>
       </c>
       <c r="R143" t="n">
-        <v>6938024</v>
+        <v>6938020</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15498,13 +15516,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103554998</t>
+          <t>https://artportalen.se/Sighting/103554871</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>103555154</v>
+        <v>103554998</v>
       </c>
       <c r="B144" t="n">
         <v>83307</v>
@@ -15540,10 +15558,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>368557</v>
+        <v>368545</v>
       </c>
       <c r="R144" t="n">
-        <v>6938080</v>
+        <v>6938024</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15601,13 +15619,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103555154</t>
+          <t>https://artportalen.se/Sighting/103554998</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>103583530</v>
+        <v>103555154</v>
       </c>
       <c r="B145" t="n">
         <v>83307</v>
@@ -15643,10 +15661,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>368831</v>
+        <v>368557</v>
       </c>
       <c r="R145" t="n">
-        <v>6938129</v>
+        <v>6938080</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -15673,12 +15691,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15704,13 +15722,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103583530</t>
+          <t>https://artportalen.se/Sighting/103555154</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>104006712</v>
+        <v>103583530</v>
       </c>
       <c r="B146" t="n">
         <v>83307</v>
@@ -15746,10 +15764,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>368628</v>
+        <v>368831</v>
       </c>
       <c r="R146" t="n">
-        <v>6937972</v>
+        <v>6938129</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -15776,12 +15794,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15807,13 +15825,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104006712</t>
+          <t>https://artportalen.se/Sighting/103583530</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>104009232</v>
+        <v>104006712</v>
       </c>
       <c r="B147" t="n">
         <v>83307</v>
@@ -15849,10 +15867,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>368595</v>
+        <v>368628</v>
       </c>
       <c r="R147" t="n">
-        <v>6938137</v>
+        <v>6937972</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -15910,13 +15928,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104009232</t>
+          <t>https://artportalen.se/Sighting/104006712</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>107032413</v>
+        <v>104009232</v>
       </c>
       <c r="B148" t="n">
         <v>83307</v>
@@ -15948,14 +15966,14 @@
       <c r="K148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>368790</v>
+        <v>368595</v>
       </c>
       <c r="R148" t="n">
-        <v>6938110</v>
+        <v>6938137</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -15982,12 +16000,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16013,13 +16031,13 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107032413</t>
+          <t>https://artportalen.se/Sighting/104009232</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>108035481</v>
+        <v>107032413</v>
       </c>
       <c r="B149" t="n">
         <v>83307</v>
@@ -16055,10 +16073,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>368592</v>
+        <v>368790</v>
       </c>
       <c r="R149" t="n">
-        <v>6938058</v>
+        <v>6938110</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -16085,22 +16103,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2023-04-11</t>
-        </is>
-      </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>15:27</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2023-04-11</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>15:27</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16115,24 +16123,24 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108035481</t>
+          <t>https://artportalen.se/Sighting/107032413</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126552542</v>
+        <v>108035481</v>
       </c>
       <c r="B150" t="n">
         <v>83307</v>
@@ -16161,19 +16169,20 @@
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>368546</v>
+        <v>368592</v>
       </c>
       <c r="R150" t="n">
-        <v>6938052</v>
+        <v>6938058</v>
       </c>
       <c r="S150" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16197,12 +16206,22 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2023-04-11</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2023-04-11</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16217,49 +16236,49 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126552542</t>
+          <t>https://artportalen.se/Sighting/108035481</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126552528</v>
+        <v>126552542</v>
       </c>
       <c r="B151" t="n">
-        <v>83305</v>
+        <v>83307</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6486</v>
+        <v>6440</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16330,60 +16349,54 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126552528</t>
+          <t>https://artportalen.se/Sighting/126552542</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>103556085</v>
+        <v>126552528</v>
       </c>
       <c r="B152" t="n">
-        <v>57950</v>
+        <v>83305</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100049</v>
+        <v>6486</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>368630</v>
+        <v>368546</v>
       </c>
       <c r="R152" t="n">
-        <v>6938124</v>
+        <v>6938052</v>
       </c>
       <c r="S152" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16407,12 +16420,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16427,24 +16440,24 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103556085</t>
+          <t>https://artportalen.se/Sighting/126552528</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>103556383</v>
+        <v>103556085</v>
       </c>
       <c r="B153" t="n">
         <v>57950</v>
@@ -16476,7 +16489,7 @@
       <c r="K153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -16485,10 +16498,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>368649</v>
+        <v>368630</v>
       </c>
       <c r="R153" t="n">
-        <v>6938126</v>
+        <v>6938124</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -16546,33 +16559,33 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103556383</t>
+          <t>https://artportalen.se/Sighting/103556085</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>103556071</v>
+        <v>103556383</v>
       </c>
       <c r="B154" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -16584,7 +16597,7 @@
       <c r="K154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -16593,10 +16606,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>368630</v>
+        <v>368649</v>
       </c>
       <c r="R154" t="n">
-        <v>6938124</v>
+        <v>6938126</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -16654,13 +16667,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103556071</t>
+          <t>https://artportalen.se/Sighting/103556383</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>103556476</v>
+        <v>103556071</v>
       </c>
       <c r="B155" t="n">
         <v>57953</v>
@@ -16701,10 +16714,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>368736</v>
+        <v>368630</v>
       </c>
       <c r="R155" t="n">
-        <v>6938144</v>
+        <v>6938124</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -16762,13 +16775,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103556476</t>
+          <t>https://artportalen.se/Sighting/103556071</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>103557552</v>
+        <v>103556476</v>
       </c>
       <c r="B156" t="n">
         <v>57953</v>
@@ -16809,10 +16822,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>368776</v>
+        <v>368736</v>
       </c>
       <c r="R156" t="n">
-        <v>6938142</v>
+        <v>6938144</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -16870,13 +16883,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103557552</t>
+          <t>https://artportalen.se/Sighting/103556476</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>103566805</v>
+        <v>103557552</v>
       </c>
       <c r="B157" t="n">
         <v>57953</v>
@@ -16904,24 +16917,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -16930,10 +16930,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>368676</v>
+        <v>368776</v>
       </c>
       <c r="R157" t="n">
-        <v>6938161</v>
+        <v>6938142</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -16960,12 +16960,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16991,13 +16991,13 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103566805</t>
+          <t>https://artportalen.se/Sighting/103557552</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>103583511</v>
+        <v>103566805</v>
       </c>
       <c r="B158" t="n">
         <v>57953</v>
@@ -17025,11 +17025,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -17038,10 +17051,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>368821</v>
+        <v>368676</v>
       </c>
       <c r="R158" t="n">
-        <v>6938156</v>
+        <v>6938161</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -17068,12 +17081,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17099,13 +17112,13 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103583511</t>
+          <t>https://artportalen.se/Sighting/103566805</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>103583654</v>
+        <v>103583511</v>
       </c>
       <c r="B159" t="n">
         <v>57953</v>
@@ -17146,10 +17159,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>368739</v>
+        <v>368821</v>
       </c>
       <c r="R159" t="n">
-        <v>6938142</v>
+        <v>6938156</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -17207,13 +17220,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103583654</t>
+          <t>https://artportalen.se/Sighting/103583511</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>103583677</v>
+        <v>103583654</v>
       </c>
       <c r="B160" t="n">
         <v>57953</v>
@@ -17245,7 +17258,7 @@
       <c r="K160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -17254,10 +17267,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>368791</v>
+        <v>368739</v>
       </c>
       <c r="R160" t="n">
-        <v>6938146</v>
+        <v>6938142</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -17315,13 +17328,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103583677</t>
+          <t>https://artportalen.se/Sighting/103583654</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>104009214</v>
+        <v>103583677</v>
       </c>
       <c r="B161" t="n">
         <v>57953</v>
@@ -17353,7 +17366,7 @@
       <c r="K161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -17362,10 +17375,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>368595</v>
+        <v>368791</v>
       </c>
       <c r="R161" t="n">
-        <v>6938137</v>
+        <v>6938146</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -17392,12 +17405,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17423,13 +17436,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104009214</t>
+          <t>https://artportalen.se/Sighting/103583677</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>104009269</v>
+        <v>104009214</v>
       </c>
       <c r="B162" t="n">
         <v>57953</v>
@@ -17470,10 +17483,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>368576</v>
+        <v>368595</v>
       </c>
       <c r="R162" t="n">
-        <v>6938147</v>
+        <v>6938137</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -17531,13 +17544,13 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104009269</t>
+          <t>https://artportalen.se/Sighting/104009214</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>106461233</v>
+        <v>104009269</v>
       </c>
       <c r="B163" t="n">
         <v>57953</v>
@@ -17567,26 +17580,24 @@
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Backvallen, Hållan, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>368783</v>
+        <v>368576</v>
       </c>
       <c r="R163" t="n">
-        <v>6938045</v>
+        <v>6938147</v>
       </c>
       <c r="S163" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17610,17 +17621,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2023-02-05</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2023-02-05</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17646,13 +17652,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106461233</t>
+          <t>https://artportalen.se/Sighting/104009269</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>107032448</v>
+        <v>106461233</v>
       </c>
       <c r="B164" t="n">
         <v>57953</v>
@@ -17682,24 +17688,26 @@
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Backvallen, Hållan, Hjd</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>368823</v>
+        <v>368783</v>
       </c>
       <c r="R164" t="n">
-        <v>6938137</v>
+        <v>6938045</v>
       </c>
       <c r="S164" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17723,12 +17731,17 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2023-02-05</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2023-02-05</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17754,13 +17767,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107032448</t>
+          <t>https://artportalen.se/Sighting/106461233</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>108344232</v>
+        <v>107032448</v>
       </c>
       <c r="B165" t="n">
         <v>57953</v>
@@ -17792,7 +17805,7 @@
       <c r="K165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -17801,10 +17814,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>368771</v>
+        <v>368823</v>
       </c>
       <c r="R165" t="n">
-        <v>6938052</v>
+        <v>6938137</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -17831,12 +17844,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17862,13 +17875,13 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108344232</t>
+          <t>https://artportalen.se/Sighting/107032448</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>108379916</v>
+        <v>108344232</v>
       </c>
       <c r="B166" t="n">
         <v>57953</v>
@@ -17900,7 +17913,7 @@
       <c r="K166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -17909,10 +17922,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>368769</v>
+        <v>368771</v>
       </c>
       <c r="R166" t="n">
-        <v>6938109</v>
+        <v>6938052</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -17939,12 +17952,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17970,13 +17983,13 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108379916</t>
+          <t>https://artportalen.se/Sighting/108344232</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>108380113</v>
+        <v>108379916</v>
       </c>
       <c r="B167" t="n">
         <v>57953</v>
@@ -18008,7 +18021,7 @@
       <c r="K167" t="inlineStr"/>
       <c r="M167" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -18017,10 +18030,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>368781</v>
+        <v>368769</v>
       </c>
       <c r="R167" t="n">
-        <v>6938123</v>
+        <v>6938109</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -18078,13 +18091,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108380113</t>
+          <t>https://artportalen.se/Sighting/108379916</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>108380229</v>
+        <v>108380113</v>
       </c>
       <c r="B168" t="n">
         <v>57953</v>
@@ -18125,10 +18138,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>368775</v>
+        <v>368781</v>
       </c>
       <c r="R168" t="n">
-        <v>6938136</v>
+        <v>6938123</v>
       </c>
       <c r="S168" t="n">
         <v>25</v>
@@ -18186,13 +18199,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108380229</t>
+          <t>https://artportalen.se/Sighting/108380113</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>124622472</v>
+        <v>108380229</v>
       </c>
       <c r="B169" t="n">
         <v>57953</v>
@@ -18221,6 +18234,7 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
       <c r="M169" t="inlineStr">
         <is>
           <t>äldre spår</t>
@@ -18232,13 +18246,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>368802</v>
+        <v>368775</v>
       </c>
       <c r="R169" t="n">
-        <v>6938048</v>
+        <v>6938136</v>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18262,12 +18276,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18293,13 +18307,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124622472</t>
+          <t>https://artportalen.se/Sighting/108380229</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>124622769</v>
+        <v>124622472</v>
       </c>
       <c r="B170" t="n">
         <v>57953</v>
@@ -18330,19 +18344,19 @@
       <c r="I170" t="inlineStr"/>
       <c r="M170" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>368769</v>
+        <v>368802</v>
       </c>
       <c r="R170" t="n">
-        <v>6938164</v>
+        <v>6938048</v>
       </c>
       <c r="S170" t="n">
         <v>15</v>
@@ -18400,13 +18414,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124622769</t>
+          <t>https://artportalen.se/Sighting/124622472</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>124627400</v>
+        <v>124622769</v>
       </c>
       <c r="B171" t="n">
         <v>57953</v>
@@ -18437,19 +18451,19 @@
       <c r="I171" t="inlineStr"/>
       <c r="M171" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>368733</v>
+        <v>368769</v>
       </c>
       <c r="R171" t="n">
-        <v>6938143</v>
+        <v>6938164</v>
       </c>
       <c r="S171" t="n">
         <v>15</v>
@@ -18507,13 +18521,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124627400</t>
+          <t>https://artportalen.se/Sighting/124622769</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>124627817</v>
+        <v>124627400</v>
       </c>
       <c r="B172" t="n">
         <v>57953</v>
@@ -18553,13 +18567,13 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>368651</v>
+        <v>368733</v>
       </c>
       <c r="R172" t="n">
-        <v>6938152</v>
+        <v>6938143</v>
       </c>
       <c r="S172" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18614,13 +18628,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124627817</t>
+          <t>https://artportalen.se/Sighting/124627400</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125696719</v>
+        <v>124627817</v>
       </c>
       <c r="B173" t="n">
         <v>57953</v>
@@ -18649,27 +18663,24 @@
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>368750</v>
+        <v>368651</v>
       </c>
       <c r="R173" t="n">
-        <v>6937906</v>
+        <v>6938152</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18693,27 +18704,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Ringhack i granar, fanns äldre i närheten också</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18728,71 +18724,73 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Martin Blomberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Martin Blomberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125696719</t>
+          <t>https://artportalen.se/Sighting/124627817</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>108093599</v>
+        <v>125696719</v>
       </c>
       <c r="B174" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>368632</v>
+        <v>368750</v>
       </c>
       <c r="R174" t="n">
-        <v>6938091</v>
+        <v>6937906</v>
       </c>
       <c r="S174" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18816,22 +18814,27 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2023-04-13</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2023-04-13</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Ringhack i granar, fanns äldre i närheten också</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18846,63 +18849,68 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Martin Blomberg</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Per Bengtson</t>
+          <t>Martin Blomberg</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108093599</t>
+          <t>https://artportalen.se/Sighting/125696719</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>103583633</v>
+        <v>108093599</v>
       </c>
       <c r="B175" t="n">
-        <v>58114</v>
+        <v>57141</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>368744</v>
+        <v>368632</v>
       </c>
       <c r="R175" t="n">
-        <v>6938086</v>
+        <v>6938091</v>
       </c>
       <c r="S175" t="n">
         <v>25</v>
@@ -18929,12 +18937,22 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2023-04-13</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2023-04-13</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18949,27 +18967,27 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Per Bengtson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103583633</t>
+          <t>https://artportalen.se/Sighting/108093599</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>103555271</v>
+        <v>103583633</v>
       </c>
       <c r="B176" t="n">
-        <v>58057</v>
+        <v>58114</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18977,21 +18995,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19002,10 +19020,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>368561</v>
+        <v>368744</v>
       </c>
       <c r="R176" t="n">
-        <v>6938105</v>
+        <v>6938086</v>
       </c>
       <c r="S176" t="n">
         <v>25</v>
@@ -19032,12 +19050,12 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19063,13 +19081,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103555271</t>
+          <t>https://artportalen.se/Sighting/103583633</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>103555834</v>
+        <v>103555271</v>
       </c>
       <c r="B177" t="n">
         <v>58057</v>
@@ -19097,31 +19115,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>368552</v>
+        <v>368561</v>
       </c>
       <c r="R177" t="n">
-        <v>6938098</v>
+        <v>6938105</v>
       </c>
       <c r="S177" t="n">
         <v>25</v>
@@ -19179,13 +19184,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103555834</t>
+          <t>https://artportalen.se/Sighting/103555271</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>103556323</v>
+        <v>103555834</v>
       </c>
       <c r="B178" t="n">
         <v>58057</v>
@@ -19213,18 +19218,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>368617</v>
+        <v>368552</v>
       </c>
       <c r="R178" t="n">
-        <v>6938128</v>
+        <v>6938098</v>
       </c>
       <c r="S178" t="n">
         <v>25</v>
@@ -19282,13 +19300,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103556323</t>
+          <t>https://artportalen.se/Sighting/103555834</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>108379968</v>
+        <v>103556323</v>
       </c>
       <c r="B179" t="n">
         <v>58057</v>
@@ -19316,29 +19334,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Backvallen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>368776</v>
+        <v>368617</v>
       </c>
       <c r="R179" t="n">
-        <v>6938113</v>
+        <v>6938128</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>
@@ -19365,12 +19372,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19396,33 +19403,33 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108379968</t>
+          <t>https://artportalen.se/Sighting/103556323</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>103553784</v>
+        <v>108379968</v>
       </c>
       <c r="B180" t="n">
-        <v>5199</v>
+        <v>58057</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>105930</v>
+        <v>103031</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -19430,23 +19437,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Backvallen, Hjd</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>368513</v>
+        <v>368776</v>
       </c>
       <c r="R180" t="n">
-        <v>6937902</v>
+        <v>6938113</v>
       </c>
       <c r="S180" t="n">
         <v>25</v>
@@ -19473,12 +19486,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19504,13 +19517,13 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103553784</t>
+          <t>https://artportalen.se/Sighting/108379968</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>103554466</v>
+        <v>103553784</v>
       </c>
       <c r="B181" t="n">
         <v>5199</v>
@@ -19551,10 +19564,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>368592</v>
+        <v>368513</v>
       </c>
       <c r="R181" t="n">
-        <v>6937951</v>
+        <v>6937902</v>
       </c>
       <c r="S181" t="n">
         <v>25</v>
@@ -19612,54 +19625,60 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103554466</t>
+          <t>https://artportalen.se/Sighting/103553784</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>126720868</v>
+        <v>103554466</v>
       </c>
       <c r="B182" t="n">
-        <v>81332</v>
+        <v>5199</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>229436</v>
+        <v>105930</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Halmgul örnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Ochrolechia alboflavescens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Wulfen) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Hållan, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>368572</v>
+        <v>368592</v>
       </c>
       <c r="R182" t="n">
-        <v>6937942</v>
+        <v>6937951</v>
       </c>
       <c r="S182" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19683,12 +19702,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19703,66 +19722,65 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126720868</t>
+          <t>https://artportalen.se/Sighting/103554466</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>103551403</v>
+        <v>126720868</v>
       </c>
       <c r="B183" t="n">
-        <v>92637</v>
+        <v>81332</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>67</v>
+        <v>229436</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Fjällkällan, Härjedalen, Hjd</t>
+          <t>Hållan, Hjd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>368506</v>
+        <v>368572</v>
       </c>
       <c r="R183" t="n">
-        <v>6937519</v>
+        <v>6937942</v>
       </c>
       <c r="S183" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -19786,12 +19804,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19806,63 +19824,63 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103551403</t>
+          <t>https://artportalen.se/Sighting/126720868</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>103552489</v>
+        <v>103551403</v>
       </c>
       <c r="B184" t="n">
-        <v>79406</v>
+        <v>92637</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>864</v>
+        <v>67</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>368284</v>
+        <v>368506</v>
       </c>
       <c r="R184" t="n">
-        <v>6937639</v>
+        <v>6937519</v>
       </c>
       <c r="S184" t="n">
         <v>25</v>
@@ -19920,16 +19938,16 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103552489</t>
+          <t>https://artportalen.se/Sighting/103551403</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>103551293</v>
+        <v>103552489</v>
       </c>
       <c r="B185" t="n">
-        <v>83173</v>
+        <v>79406</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19937,35 +19955,35 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Fjällkällan, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>368544</v>
+        <v>368284</v>
       </c>
       <c r="R185" t="n">
-        <v>6937472</v>
+        <v>6937639</v>
       </c>
       <c r="S185" t="n">
         <v>25</v>
@@ -20023,13 +20041,13 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103551293</t>
+          <t>https://artportalen.se/Sighting/103552489</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>103551351</v>
+        <v>103551293</v>
       </c>
       <c r="B186" t="n">
         <v>83173</v>
@@ -20065,10 +20083,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>368545</v>
+        <v>368544</v>
       </c>
       <c r="R186" t="n">
-        <v>6937480</v>
+        <v>6937472</v>
       </c>
       <c r="S186" t="n">
         <v>25</v>
@@ -20126,13 +20144,13 @@
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103551351</t>
+          <t>https://artportalen.se/Sighting/103551293</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>103552447</v>
+        <v>103551351</v>
       </c>
       <c r="B187" t="n">
         <v>83173</v>
@@ -20164,14 +20182,14 @@
       <c r="K187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>368344</v>
+        <v>368545</v>
       </c>
       <c r="R187" t="n">
-        <v>6937620</v>
+        <v>6937480</v>
       </c>
       <c r="S187" t="n">
         <v>25</v>
@@ -20229,13 +20247,13 @@
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103552447</t>
+          <t>https://artportalen.se/Sighting/103551351</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124618703</v>
+        <v>103552447</v>
       </c>
       <c r="B188" t="n">
         <v>83173</v>
@@ -20264,16 +20282,17 @@
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>368568</v>
+        <v>368344</v>
       </c>
       <c r="R188" t="n">
-        <v>6937489</v>
+        <v>6937620</v>
       </c>
       <c r="S188" t="n">
         <v>25</v>
@@ -20300,12 +20319,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20331,13 +20350,13 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124618703</t>
+          <t>https://artportalen.se/Sighting/103552447</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124629552</v>
+        <v>124618703</v>
       </c>
       <c r="B189" t="n">
         <v>83173</v>
@@ -20368,14 +20387,14 @@
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>368487</v>
+        <v>368568</v>
       </c>
       <c r="R189" t="n">
-        <v>6937548</v>
+        <v>6937489</v>
       </c>
       <c r="S189" t="n">
         <v>25</v>
@@ -20433,38 +20452,38 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124629552</t>
+          <t>https://artportalen.se/Sighting/124618703</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119765744</v>
+        <v>124629552</v>
       </c>
       <c r="B190" t="n">
-        <v>92632</v>
+        <v>83173</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20474,13 +20493,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>368547</v>
+        <v>368487</v>
       </c>
       <c r="R190" t="n">
-        <v>6937589</v>
+        <v>6937548</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20504,12 +20523,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20535,55 +20554,54 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119765744</t>
+          <t>https://artportalen.se/Sighting/124629552</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>103552013</v>
+        <v>119765744</v>
       </c>
       <c r="B191" t="n">
-        <v>79327</v>
+        <v>92632</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>368492</v>
+        <v>368547</v>
       </c>
       <c r="R191" t="n">
-        <v>6937572</v>
+        <v>6937589</v>
       </c>
       <c r="S191" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20607,12 +20625,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20638,13 +20656,13 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103552013</t>
+          <t>https://artportalen.se/Sighting/119765744</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>104011170</v>
+        <v>103552013</v>
       </c>
       <c r="B192" t="n">
         <v>79327</v>
@@ -20676,14 +20694,14 @@
       <c r="K192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Backvallen, Härjedalen, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>368637</v>
+        <v>368492</v>
       </c>
       <c r="R192" t="n">
-        <v>6937460</v>
+        <v>6937572</v>
       </c>
       <c r="S192" t="n">
         <v>25</v>
@@ -20710,12 +20728,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20741,13 +20759,13 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104011170</t>
+          <t>https://artportalen.se/Sighting/103552013</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>108344789</v>
+        <v>104011170</v>
       </c>
       <c r="B193" t="n">
         <v>79327</v>
@@ -20779,14 +20797,14 @@
       <c r="K193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Backvallen, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>368543</v>
+        <v>368637</v>
       </c>
       <c r="R193" t="n">
-        <v>6937476</v>
+        <v>6937460</v>
       </c>
       <c r="S193" t="n">
         <v>25</v>
@@ -20813,12 +20831,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20844,13 +20862,13 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108344789</t>
+          <t>https://artportalen.se/Sighting/104011170</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126720873</v>
+        <v>108344789</v>
       </c>
       <c r="B194" t="n">
         <v>79327</v>
@@ -20879,19 +20897,20 @@
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Hållan, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>368580</v>
+        <v>368543</v>
       </c>
       <c r="R194" t="n">
-        <v>6937494</v>
+        <v>6937476</v>
       </c>
       <c r="S194" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -20915,12 +20934,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20935,66 +20954,65 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126720873</t>
+          <t>https://artportalen.se/Sighting/108344789</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>103551371</v>
+        <v>126720873</v>
       </c>
       <c r="B195" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Fjällkällan, Härjedalen, Hjd</t>
+          <t>Hållan, Hjd</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>368550</v>
+        <v>368580</v>
       </c>
       <c r="R195" t="n">
-        <v>6937508</v>
+        <v>6937494</v>
       </c>
       <c r="S195" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21018,12 +21036,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21038,24 +21056,24 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103551371</t>
+          <t>https://artportalen.se/Sighting/126720873</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>103551383</v>
+        <v>103551371</v>
       </c>
       <c r="B196" t="n">
         <v>83307</v>
@@ -21091,10 +21109,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>368529</v>
+        <v>368550</v>
       </c>
       <c r="R196" t="n">
-        <v>6937505</v>
+        <v>6937508</v>
       </c>
       <c r="S196" t="n">
         <v>25</v>
@@ -21152,13 +21170,13 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103551383</t>
+          <t>https://artportalen.se/Sighting/103551371</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>103551484</v>
+        <v>103551383</v>
       </c>
       <c r="B197" t="n">
         <v>83307</v>
@@ -21190,14 +21208,14 @@
       <c r="K197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Fjällkällan, Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>368487</v>
+        <v>368529</v>
       </c>
       <c r="R197" t="n">
-        <v>6937548</v>
+        <v>6937505</v>
       </c>
       <c r="S197" t="n">
         <v>25</v>
@@ -21255,13 +21273,13 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103551484</t>
+          <t>https://artportalen.se/Sighting/103551383</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124630092</v>
+        <v>103551484</v>
       </c>
       <c r="B198" t="n">
         <v>83307</v>
@@ -21290,19 +21308,20 @@
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>368556</v>
+        <v>368487</v>
       </c>
       <c r="R198" t="n">
-        <v>6937530</v>
+        <v>6937548</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21326,12 +21345,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21357,13 +21376,13 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124630092</t>
+          <t>https://artportalen.se/Sighting/103551484</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124630273</v>
+        <v>124630092</v>
       </c>
       <c r="B199" t="n">
         <v>83307</v>
@@ -21398,10 +21417,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>368585</v>
+        <v>368556</v>
       </c>
       <c r="R199" t="n">
-        <v>6937532</v>
+        <v>6937530</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21459,13 +21478,13 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124630273</t>
+          <t>https://artportalen.se/Sighting/124630092</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124630509</v>
+        <v>124630273</v>
       </c>
       <c r="B200" t="n">
         <v>83307</v>
@@ -21500,10 +21519,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>368603</v>
+        <v>368585</v>
       </c>
       <c r="R200" t="n">
-        <v>6937521</v>
+        <v>6937532</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21561,55 +21580,54 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124630509</t>
+          <t>https://artportalen.se/Sighting/124630273</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>103552718</v>
+        <v>124630509</v>
       </c>
       <c r="B201" t="n">
-        <v>80461</v>
+        <v>83307</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>368262</v>
+        <v>368603</v>
       </c>
       <c r="R201" t="n">
-        <v>6937673</v>
+        <v>6937521</v>
       </c>
       <c r="S201" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21633,12 +21651,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21664,13 +21682,13 @@
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103552718</t>
+          <t>https://artportalen.se/Sighting/124630509</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124618931</v>
+        <v>103552718</v>
       </c>
       <c r="B202" t="n">
         <v>80461</v>
@@ -21699,19 +21717,20 @@
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>368571</v>
+        <v>368262</v>
       </c>
       <c r="R202" t="n">
-        <v>6937516</v>
+        <v>6937673</v>
       </c>
       <c r="S202" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -21735,12 +21754,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21766,59 +21785,54 @@
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124618931</t>
+          <t>https://artportalen.se/Sighting/103552718</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119763325</v>
+        <v>124618931</v>
       </c>
       <c r="B203" t="n">
-        <v>57953</v>
+        <v>80461</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>368590</v>
+        <v>368571</v>
       </c>
       <c r="R203" t="n">
-        <v>6937543</v>
+        <v>6937516</v>
       </c>
       <c r="S203" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -21842,12 +21856,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21873,13 +21887,13 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119763325</t>
+          <t>https://artportalen.se/Sighting/124618931</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119763342</v>
+        <v>119763325</v>
       </c>
       <c r="B204" t="n">
         <v>57953</v>
@@ -21908,31 +21922,21 @@
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>368574</v>
+        <v>368590</v>
       </c>
       <c r="R204" t="n">
-        <v>6937554</v>
+        <v>6937543</v>
       </c>
       <c r="S204" t="n">
         <v>15</v>
@@ -21959,12 +21963,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21990,33 +21994,33 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119763342</t>
+          <t>https://artportalen.se/Sighting/119763325</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>103552077</v>
+        <v>119763342</v>
       </c>
       <c r="B205" t="n">
-        <v>58327</v>
+        <v>57953</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -22025,20 +22029,34 @@
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>368471</v>
+        <v>368574</v>
       </c>
       <c r="R205" t="n">
-        <v>6937590</v>
+        <v>6937554</v>
       </c>
       <c r="S205" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -22062,12 +22080,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22093,13 +22111,13 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103552077</t>
+          <t>https://artportalen.se/Sighting/119763342</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>108350248</v>
+        <v>103552077</v>
       </c>
       <c r="B206" t="n">
         <v>58327</v>
@@ -22129,21 +22147,16 @@
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Storkroken, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>368438</v>
+        <v>368471</v>
       </c>
       <c r="R206" t="n">
-        <v>6937579</v>
+        <v>6937590</v>
       </c>
       <c r="S206" t="n">
         <v>25</v>
@@ -22170,12 +22183,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22201,33 +22214,33 @@
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108350248</t>
+          <t>https://artportalen.se/Sighting/103552077</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>103552719</v>
+        <v>108350248</v>
       </c>
       <c r="B207" t="n">
-        <v>58057</v>
+        <v>58327</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>103031</v>
+        <v>103015</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -22237,16 +22250,21 @@
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Storkroken, Hjd</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>368262</v>
+        <v>368438</v>
       </c>
       <c r="R207" t="n">
-        <v>6937673</v>
+        <v>6937579</v>
       </c>
       <c r="S207" t="n">
         <v>25</v>
@@ -22273,12 +22291,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22304,13 +22322,13 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103552719</t>
+          <t>https://artportalen.se/Sighting/108350248</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119763370</v>
+        <v>103552719</v>
       </c>
       <c r="B208" t="n">
         <v>58057</v>
@@ -22338,24 +22356,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>368574</v>
+        <v>368262</v>
       </c>
       <c r="R208" t="n">
-        <v>6937554</v>
+        <v>6937673</v>
       </c>
       <c r="S208" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -22379,12 +22394,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22410,51 +22425,55 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119763370</t>
+          <t>https://artportalen.se/Sighting/103552719</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>126720871</v>
+        <v>119763370</v>
       </c>
       <c r="B209" t="n">
-        <v>99140</v>
+        <v>58057</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>221952</v>
+        <v>103031</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Hållan, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>368571</v>
+        <v>368574</v>
       </c>
       <c r="R209" t="n">
-        <v>6937498</v>
+        <v>6937554</v>
       </c>
       <c r="S209" t="n">
         <v>15</v>
@@ -22481,12 +22500,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22501,16 +22520,118 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119763370</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>126720871</v>
+      </c>
+      <c r="B210" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Hållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>368571</v>
+      </c>
+      <c r="R210" t="n">
+        <v>6937498</v>
+      </c>
+      <c r="S210" t="n">
+        <v>15</v>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT210" t="inlineStr"/>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126720871</t>
         </is>
@@ -22726,6 +22847,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -12406,7 +12406,7 @@
         <v>135520659</v>
       </c>
       <c r="B114" t="n">
-        <v>92406</v>
+        <v>92408</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -12406,7 +12406,7 @@
         <v>135520659</v>
       </c>
       <c r="B114" t="n">
-        <v>92408</v>
+        <v>92421</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 33058-2022 artfynd.xlsx
+++ b/artfynd/A 33058-2022 artfynd.xlsx
@@ -12406,7 +12406,7 @@
         <v>135520659</v>
       </c>
       <c r="B114" t="n">
-        <v>92421</v>
+        <v>92422</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
